--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -63,15 +63,84 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Dealer Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL ANGLE MARKETING INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>X-DOT CONNECTION INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3 UNIT 103, BATONG MALAKE, Los Baños, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06900-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1177-099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
-    <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
     <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
   </x:si>
   <x:si>
@@ -82,6 +151,36 @@
   </x:si>
   <x:si>
     <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#95 CZ 28 3RD, FLOOR SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-16-05-1938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1162-745</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Service Center Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>257-G SM City Molino Molino Road, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1194-347</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -160,6 +259,13 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
@@ -171,13 +277,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -414,7 +513,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -443,47 +542,50 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -530,51 +632,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -946,19 +1072,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46090.2418287037</x:v>
       </x:c>
       <x:c r="I6" s="12">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46090.2418518519</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511203</x:v>
       </x:c>
       <x:c r="K6" s="13" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>19</x:v>
@@ -966,76 +1092,362 @@
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I7" s="12">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>22</x:v>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
-        <x:v>1</x:v>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>42</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
-        <x:v>1</x:v>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="20" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="29" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2007,13 +2419,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -133,6 +133,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0775 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
@@ -1248,176 +1260,203 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="D11" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="H11" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="H12" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="H13" s="16">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I13" s="17">
-        <x:v>46094</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46093.3109375</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="20" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="22" t="s"/>
     </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>2</x:v>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="23" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
       <x:c r="E19" s="27" t="s"/>
       <x:c r="F19" s="28" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
       <x:c r="E20" s="27" t="s"/>
       <x:c r="F20" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
@@ -1428,7 +1467,7 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
@@ -1437,18 +1476,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
-        <x:v>8</x:v>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="29" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2422,14 +2471,14 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="March 2026" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -72,6 +36,18 @@
     <x:t>NEW</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06919-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1179-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
     <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -81,9 +57,6 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -99,12 +72,36 @@
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
+    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBLITZ MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 23- 019R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1095-163</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -123,6 +120,39 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3 03714 ROBINSONS PLACE DASMARIÑAS, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-018R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1094-777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-468R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1161-717</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -133,6 +163,15 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-471R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1108-762</x:t>
   </x:si>
   <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
@@ -214,7 +253,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -241,12 +280,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -254,6 +287,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -268,13 +322,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -319,12 +366,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -336,14 +383,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -525,7 +572,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -536,183 +583,208 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -976,535 +1048,770 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46093.3049884259</x:v>
+      <x:c r="L6" s="15">
+        <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="L7" s="17">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I8" s="17">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K8" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="19">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H8" s="20">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I9" s="17">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="B9" s="19" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I9" s="22">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="L9" s="20">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="H10" s="13">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I10" s="23">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="15">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
+      <x:c r="B11" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="F11" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I11" s="23">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="L11" s="15">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
+      <x:c r="B12" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>46</x:v>
+      <x:c r="C12" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I12" s="23">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="15">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="B13" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I13" s="23">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="L13" s="15">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
+      <x:c r="B14" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I14" s="23">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="15">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I15" s="23">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I16" s="23">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I17" s="23">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="G18" s="11" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="H18" s="13">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I18" s="23">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="C19" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="D19" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="F19" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I19" s="13">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K19" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="15">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I20" s="23">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="15">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
         <x:v>46092.9637847222</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I21" s="23">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J21" s="12" t="n">
         <x:v>1511219</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K21" s="14" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L21" s="15">
         <x:v>46093.3109375</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>19</x:v>
+      <x:c r="M21" s="11" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="24" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="26" t="s"/>
     </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
-        <x:v>59</x:v>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="27" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C25" s="28" t="s"/>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="28" t="s"/>
+      <x:c r="F25" s="29" t="s">
+        <x:v>72</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>2</x:v>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="31" t="s"/>
+      <x:c r="D26" s="31" t="s"/>
+      <x:c r="E26" s="31" t="s"/>
+      <x:c r="F26" s="32" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>4</x:v>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="s"/>
+      <x:c r="D27" s="31" t="s"/>
+      <x:c r="E27" s="31" t="s"/>
+      <x:c r="F27" s="32" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C28" s="31" t="s"/>
+      <x:c r="D28" s="31" t="s"/>
+      <x:c r="E28" s="31" t="s"/>
+      <x:c r="F28" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C29" s="31" t="s"/>
+      <x:c r="D29" s="31" t="s"/>
+      <x:c r="E29" s="31" t="s"/>
+      <x:c r="F29" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="30" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C30" s="31" t="s"/>
+      <x:c r="D30" s="31" t="s"/>
+      <x:c r="E30" s="31" t="s"/>
+      <x:c r="F30" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
-        <x:v>9</x:v>
+    <x:row r="31" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B31" s="33" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C31" s="34" t="s"/>
+      <x:c r="D31" s="34" t="s"/>
+      <x:c r="E31" s="34" t="s"/>
+      <x:c r="F31" s="35" t="n">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2471,14 +2778,14 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B17:F17"/>
-    <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B24:F24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,9 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
-  <x:si>
-    <x:t>{{Name}}</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+  <x:si>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIEL GENNE PUYO</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -653,7 +656,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="42">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -689,6 +692,54 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -700,6 +751,10 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -708,36 +763,8 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1033,7 +1060,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1111,24 +1140,24 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46090.2558217593</x:v>
@@ -1146,30 +1175,30 @@
         <x:v>46097.2890740741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E7" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F7" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H7" s="17">
         <x:v>46090.2418287037</x:v>
@@ -1187,29 +1216,29 @@
         <x:v>46093.3049884259</x:v>
       </x:c>
       <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="19" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="19" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="19" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="19" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F8" s="19" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G8" s="19" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H8" s="20">
         <x:v>46090.2109953704</x:v>
@@ -1227,27 +1256,27 @@
         <x:v>46093.3080092593</x:v>
       </x:c>
       <x:c r="M8" s="19" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="19" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="19" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="19" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="19" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H9" s="20">
         <x:v>46083.2322337963</x:v>
@@ -1265,555 +1294,581 @@
         <x:v>46097.149525463</x:v>
       </x:c>
       <x:c r="M9" s="19" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="B10" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C10" s="23" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="D10" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E10" s="23" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="F10" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="G10" s="23" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H10" s="25">
         <x:v>46069.3514814815</x:v>
       </x:c>
-      <x:c r="I10" s="23">
+      <x:c r="I10" s="26">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="24" t="n">
         <x:v>1511194</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="28">
         <x:v>46097.2437384259</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M10" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="B11" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="D11" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E11" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="F11" s="23" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="G11" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H11" s="25">
         <x:v>46084.2250115741</x:v>
       </x:c>
-      <x:c r="I11" s="23">
+      <x:c r="I11" s="26">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="24" t="n">
         <x:v>1511224</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="28">
         <x:v>46093.3804398148</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M11" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="B12" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C12" s="23" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E12" s="23" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="F12" s="23" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="G12" s="23" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H12" s="25">
         <x:v>46084.2189236111</x:v>
       </x:c>
-      <x:c r="I12" s="23">
+      <x:c r="I12" s="26">
         <x:v>46133</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="24" t="n">
         <x:v>1511223</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="28">
         <x:v>46093.3723842593</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M12" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="B13" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D13" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E13" s="23" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="F13" s="23" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="G13" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H13" s="25">
         <x:v>46069.3573032407</x:v>
       </x:c>
-      <x:c r="I13" s="23">
+      <x:c r="I13" s="26">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="24" t="n">
         <x:v>1511193</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="28">
         <x:v>46097.2426388889</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M13" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="B14" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="D14" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E14" s="23" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="F14" s="23" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="G14" s="23" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H14" s="25">
         <x:v>46069.3341087963</x:v>
       </x:c>
-      <x:c r="I14" s="23">
+      <x:c r="I14" s="26">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="24" t="n">
         <x:v>1511195</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="K14" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="15">
+      <x:c r="L14" s="28">
         <x:v>46097.2447337963</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M14" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="B15" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="D15" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="F15" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="G15" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H15" s="25">
         <x:v>46084.1512962963</x:v>
       </x:c>
-      <x:c r="I15" s="23">
+      <x:c r="I15" s="26">
         <x:v>46102</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="24" t="n">
         <x:v>1511211</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="K15" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="15">
+      <x:c r="L15" s="28">
         <x:v>46097.2494560185</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M15" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="B16" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="D16" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="F16" s="23" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="G16" s="23" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H16" s="25">
         <x:v>46084.3311921296</x:v>
       </x:c>
-      <x:c r="I16" s="23">
+      <x:c r="I16" s="26">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="24" t="n">
         <x:v>1511222</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K16" s="27" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L16" s="15">
+      <x:c r="L16" s="28">
         <x:v>46093.366875</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M16" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="B17" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="F17" s="23" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="G17" s="23" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H17" s="25">
         <x:v>46073.1135069444</x:v>
       </x:c>
-      <x:c r="I17" s="23">
+      <x:c r="I17" s="26">
         <x:v>45751</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="24" t="n">
         <x:v>1511213</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="K17" s="27" t="n">
         <x:v>7530</x:v>
       </x:c>
-      <x:c r="L17" s="15">
+      <x:c r="L17" s="28">
         <x:v>46097.2511342593</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M17" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="B18" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="D18" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="F18" s="23" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="G18" s="23" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H18" s="25">
         <x:v>46092.1012731481</x:v>
       </x:c>
-      <x:c r="I18" s="23">
+      <x:c r="I18" s="26">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="24" t="n">
         <x:v>1511231</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="K18" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="15">
+      <x:c r="L18" s="28">
         <x:v>46097.1408217593</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M18" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="B19" s="23" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="C19" s="23" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
+      <x:c r="D19" s="24" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="s">
+      <x:c r="F19" s="23" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H19" s="13">
+      <x:c r="G19" s="23" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H19" s="25">
         <x:v>46084.3419444444</x:v>
       </x:c>
-      <x:c r="I19" s="13">
+      <x:c r="I19" s="25">
         <x:v>46084.3419560185</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
+      <x:c r="J19" s="24" t="n">
         <x:v>1507967</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="K19" s="27" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L19" s="15">
+      <x:c r="L19" s="28">
         <x:v>46090.3480902778</x:v>
       </x:c>
-      <x:c r="M19" s="11" t="s">
-        <x:v>59</x:v>
+      <x:c r="M19" s="23" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="B20" s="23" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="C20" s="23" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="D20" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="F20" s="23" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H20" s="13">
+      <x:c r="G20" s="23" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H20" s="25">
         <x:v>46084.1579513889</x:v>
       </x:c>
-      <x:c r="I20" s="23">
+      <x:c r="I20" s="26">
         <x:v>46145</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
+      <x:c r="J20" s="24" t="n">
         <x:v>1511226</x:v>
       </x:c>
-      <x:c r="K20" s="14" t="n">
+      <x:c r="K20" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="15">
+      <x:c r="L20" s="28">
         <x:v>46093.4169212963</x:v>
       </x:c>
-      <x:c r="M20" s="11" t="s">
-        <x:v>7</x:v>
+      <x:c r="M20" s="23" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="B21" s="23" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="C21" s="23" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
+      <x:c r="D21" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="s">
+      <x:c r="F21" s="23" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H21" s="13">
+      <x:c r="G21" s="23" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H21" s="25">
         <x:v>46092.9637847222</x:v>
       </x:c>
-      <x:c r="I21" s="23">
+      <x:c r="I21" s="26">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="n">
+      <x:c r="J21" s="24" t="n">
         <x:v>1511219</x:v>
       </x:c>
-      <x:c r="K21" s="14" t="n">
+      <x:c r="K21" s="27" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L21" s="15">
+      <x:c r="L21" s="28">
         <x:v>46093.3109375</x:v>
       </x:c>
-      <x:c r="M21" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="24" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="26" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="27" t="s">
+      <x:c r="M21" s="23" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B22" s="29" t="s"/>
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="29" t="s"/>
+      <x:c r="G22" s="29" t="s"/>
+      <x:c r="H22" s="29" t="s"/>
+      <x:c r="I22" s="29" t="s"/>
+      <x:c r="J22" s="29" t="s"/>
+      <x:c r="K22" s="29" t="s"/>
+      <x:c r="L22" s="29" t="s"/>
+      <x:c r="M22" s="29" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B23" s="29" t="s"/>
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="29" t="s"/>
+      <x:c r="G23" s="29" t="s"/>
+      <x:c r="H23" s="29" t="s"/>
+      <x:c r="I23" s="29" t="s"/>
+      <x:c r="J23" s="29" t="s"/>
+      <x:c r="K23" s="29" t="s"/>
+      <x:c r="L23" s="29" t="s"/>
+      <x:c r="M23" s="29" t="s"/>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="30" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="28" t="s"/>
-      <x:c r="F25" s="29" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="30" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="31" t="s"/>
       <x:c r="D26" s="31" t="s"/>
-      <x:c r="E26" s="31" t="s"/>
-      <x:c r="F26" s="32" t="n">
+      <x:c r="E26" s="32" t="s"/>
+      <x:c r="F26" s="32" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B27" s="33" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C27" s="34" t="s"/>
+      <x:c r="D27" s="34" t="s"/>
+      <x:c r="E27" s="34" t="s"/>
+      <x:c r="F27" s="35" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="36" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C28" s="37" t="s"/>
+      <x:c r="D28" s="37" t="s"/>
+      <x:c r="E28" s="37" t="s"/>
+      <x:c r="F28" s="38" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="30" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="31" t="s"/>
-      <x:c r="D27" s="31" t="s"/>
-      <x:c r="E27" s="31" t="s"/>
-      <x:c r="F27" s="32" t="n">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="36" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C29" s="37" t="s"/>
+      <x:c r="D29" s="37" t="s"/>
+      <x:c r="E29" s="37" t="s"/>
+      <x:c r="F29" s="38" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="30" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C28" s="31" t="s"/>
-      <x:c r="D28" s="31" t="s"/>
-      <x:c r="E28" s="31" t="s"/>
-      <x:c r="F28" s="32" t="n">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="36" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C30" s="37" t="s"/>
+      <x:c r="D30" s="37" t="s"/>
+      <x:c r="E30" s="37" t="s"/>
+      <x:c r="F30" s="38" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="30" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C29" s="31" t="s"/>
-      <x:c r="D29" s="31" t="s"/>
-      <x:c r="E29" s="31" t="s"/>
-      <x:c r="F29" s="32" t="n">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C31" s="37" t="s"/>
+      <x:c r="D31" s="37" t="s"/>
+      <x:c r="E31" s="37" t="s"/>
+      <x:c r="F31" s="38" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="30" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C30" s="31" t="s"/>
-      <x:c r="D30" s="31" t="s"/>
-      <x:c r="E30" s="31" t="s"/>
-      <x:c r="F30" s="32" t="n">
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="36" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C32" s="37" t="s"/>
+      <x:c r="D32" s="37" t="s"/>
+      <x:c r="E32" s="37" t="s"/>
+      <x:c r="F32" s="38" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="33" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C31" s="34" t="s"/>
-      <x:c r="D31" s="34" t="s"/>
-      <x:c r="E31" s="34" t="s"/>
-      <x:c r="F31" s="35" t="n">
+    <x:row r="33" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B33" s="39" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C33" s="40" t="s"/>
+      <x:c r="D33" s="40" t="s"/>
+      <x:c r="E33" s="40" t="s"/>
+      <x:c r="F33" s="41" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2775,17 +2830,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B24:F24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
+  <x:mergeCells count="11">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B26:F26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -105,6 +105,15 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -114,15 +123,6 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -187,6 +187,18 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1192-904</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEVEL 3, 306A, BRGY. TEJERO, General Trias, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-05-0452-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1084-395</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
@@ -1110,7 +1122,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1180,7 +1192,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>
@@ -1355,19 +1367,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="H11" s="25">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I11" s="26">
-        <x:v>46144</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J11" s="24" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K11" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="28">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M11" s="23" t="s">
         <x:v>8</x:v>
@@ -1393,19 +1405,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H12" s="25">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I12" s="26">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J12" s="24" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K12" s="27" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="28">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M12" s="23" t="s">
         <x:v>8</x:v>
@@ -1641,131 +1653,155 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="23" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C19" s="23" t="s">
+      <x:c r="D19" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D19" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E19" s="23" t="s">
+      <x:c r="F19" s="23" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F19" s="23" t="s">
+      <x:c r="G19" s="23" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G19" s="23" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="H19" s="25">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I19" s="25">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I19" s="26">
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J19" s="24" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K19" s="27" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="28">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M19" s="23" t="s">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B20" s="23" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D20" s="24" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C20" s="23" t="s">
+      <x:c r="F20" s="23" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D20" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E20" s="23" t="s">
+      <x:c r="G20" s="23" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F20" s="23" t="s">
+      <x:c r="H20" s="25">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I20" s="25">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J20" s="24" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K20" s="27" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L20" s="28">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M20" s="23" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="G20" s="23" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H20" s="25">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I20" s="26">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J20" s="24" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K20" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="28">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M20" s="23" t="s">
-        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B21" s="23" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="D21" s="24" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E21" s="23" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F21" s="23" t="s">
+      <x:c r="G21" s="23" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G21" s="23" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H21" s="25">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I21" s="26">
-        <x:v>46094</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J21" s="24" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K21" s="27" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="28">
-        <x:v>46093.3109375</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M21" s="23" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B22" s="29" t="s"/>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="29" t="s"/>
-      <x:c r="G22" s="29" t="s"/>
-      <x:c r="H22" s="29" t="s"/>
-      <x:c r="I22" s="29" t="s"/>
-      <x:c r="J22" s="29" t="s"/>
-      <x:c r="K22" s="29" t="s"/>
-      <x:c r="L22" s="29" t="s"/>
-      <x:c r="M22" s="29" t="s"/>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="23" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D22" s="24" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F22" s="23" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G22" s="23" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H22" s="25">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I22" s="26">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J22" s="24" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K22" s="27" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L22" s="28">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M22" s="23" t="s">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15" customHeight="1">
       <x:c r="B23" s="29" t="s"/>
@@ -1781,64 +1817,67 @@
       <x:c r="L23" s="29" t="s"/>
       <x:c r="M23" s="29" t="s"/>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B24" s="29" t="s"/>
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="29" t="s"/>
+      <x:c r="G24" s="29" t="s"/>
+      <x:c r="H24" s="29" t="s"/>
+      <x:c r="I24" s="29" t="s"/>
+      <x:c r="J24" s="29" t="s"/>
+      <x:c r="K24" s="29" t="s"/>
+      <x:c r="L24" s="29" t="s"/>
+      <x:c r="M24" s="29" t="s"/>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="30" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C26" s="31" t="s"/>
-      <x:c r="D26" s="31" t="s"/>
-      <x:c r="E26" s="32" t="s"/>
-      <x:c r="F26" s="32" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="33" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C27" s="34" t="s"/>
-      <x:c r="D27" s="34" t="s"/>
-      <x:c r="E27" s="34" t="s"/>
-      <x:c r="F27" s="35" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="36" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C28" s="37" t="s"/>
-      <x:c r="D28" s="37" t="s"/>
-      <x:c r="E28" s="37" t="s"/>
-      <x:c r="F28" s="38" t="n">
-        <x:v>3</x:v>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C27" s="31" t="s"/>
+      <x:c r="D27" s="31" t="s"/>
+      <x:c r="E27" s="32" t="s"/>
+      <x:c r="F27" s="32" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="33" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C28" s="34" t="s"/>
+      <x:c r="D28" s="34" t="s"/>
+      <x:c r="E28" s="34" t="s"/>
+      <x:c r="F28" s="35" t="s">
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="36" t="s">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C29" s="37" t="s"/>
       <x:c r="D29" s="37" t="s"/>
       <x:c r="E29" s="37" t="s"/>
       <x:c r="F29" s="38" t="n">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="36" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C30" s="37" t="s"/>
       <x:c r="D30" s="37" t="s"/>
       <x:c r="E30" s="37" t="s"/>
       <x:c r="F30" s="38" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="36" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C31" s="37" t="s"/>
       <x:c r="D31" s="37" t="s"/>
@@ -1849,7 +1888,7 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="36" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C32" s="37" t="s"/>
       <x:c r="D32" s="37" t="s"/>
@@ -1858,18 +1897,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="39" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C33" s="40" t="s"/>
-      <x:c r="D33" s="40" t="s"/>
-      <x:c r="E33" s="40" t="s"/>
-      <x:c r="F33" s="41" t="n">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="36" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C33" s="37" t="s"/>
+      <x:c r="D33" s="37" t="s"/>
+      <x:c r="E33" s="37" t="s"/>
+      <x:c r="F33" s="38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="39" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C34" s="40" t="s"/>
+      <x:c r="D34" s="40" t="s"/>
+      <x:c r="E34" s="40" t="s"/>
+      <x:c r="F34" s="41" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2834,14 +2883,14 @@
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
     <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B26:F26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,12 +22,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>DENIEL GENNE PUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -268,7 +304,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -313,21 +349,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -337,6 +358,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -587,7 +615,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -598,77 +626,68 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -699,60 +718,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -763,67 +730,79 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1124,18 +1103,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1153,769 +1120,781 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s">
+      <x:c r="D7" s="10" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>8</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46090.2109953704</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>46090.2110069444</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1511204</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>46093.3080092593</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
+      <x:c r="E22" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I9" s="22">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J9" s="19" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K9" s="21" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I10" s="26">
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K10" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="28">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I11" s="26">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K11" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="28">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I12" s="26">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J12" s="24" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K12" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="28">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I13" s="26">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J13" s="24" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K13" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="28">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I14" s="26">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J14" s="24" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K14" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="28">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D15" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F15" s="23" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H15" s="25">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I15" s="26">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J15" s="24" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K15" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="28">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M15" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D16" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E16" s="23" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F16" s="23" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G16" s="23" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H16" s="25">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I16" s="26">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J16" s="24" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K16" s="27" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L16" s="28">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M16" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D17" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E17" s="23" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F17" s="23" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G17" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H17" s="25">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I17" s="26">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J17" s="24" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K17" s="27" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L17" s="28">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M17" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E18" s="23" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F18" s="23" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G18" s="23" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H18" s="25">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I18" s="26">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J18" s="24" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K18" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="28">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M18" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E19" s="23" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F19" s="23" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G19" s="23" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H19" s="25">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I19" s="26">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J19" s="24" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K19" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="28">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M19" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D20" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E20" s="23" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F20" s="23" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G20" s="23" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H20" s="25">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I20" s="25">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J20" s="24" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K20" s="27" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L20" s="28">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M20" s="23" t="s">
-        <x:v>64</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D21" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E21" s="23" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F21" s="23" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G21" s="23" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H21" s="25">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I21" s="26">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J21" s="24" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K21" s="27" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="28">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M21" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C22" s="23" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D22" s="24" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E22" s="23" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F22" s="23" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G22" s="23" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H22" s="25">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I22" s="26">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J22" s="24" t="n">
+      <x:c r="J24" s="15" t="n">
         <x:v>1511219</x:v>
       </x:c>
-      <x:c r="K22" s="27" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L22" s="28">
+      <x:c r="L24" s="18">
         <x:v>46093.3109375</x:v>
       </x:c>
-      <x:c r="M22" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B23" s="29" t="s"/>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="29" t="s"/>
-      <x:c r="G23" s="29" t="s"/>
-      <x:c r="H23" s="29" t="s"/>
-      <x:c r="I23" s="29" t="s"/>
-      <x:c r="J23" s="29" t="s"/>
-      <x:c r="K23" s="29" t="s"/>
-      <x:c r="L23" s="29" t="s"/>
-      <x:c r="M23" s="29" t="s"/>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B24" s="29" t="s"/>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="29" t="s"/>
-      <x:c r="G24" s="29" t="s"/>
-      <x:c r="H24" s="29" t="s"/>
-      <x:c r="I24" s="29" t="s"/>
-      <x:c r="J24" s="29" t="s"/>
-      <x:c r="K24" s="29" t="s"/>
-      <x:c r="L24" s="29" t="s"/>
-      <x:c r="M24" s="29" t="s"/>
+      <x:c r="M24" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="30" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C27" s="31" t="s"/>
-      <x:c r="D27" s="31" t="s"/>
-      <x:c r="E27" s="32" t="s"/>
-      <x:c r="F27" s="32" t="s"/>
+      <x:c r="B27" s="20" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C27" s="21" t="s"/>
+      <x:c r="D27" s="21" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="22" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="33" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C28" s="34" t="s"/>
-      <x:c r="D28" s="34" t="s"/>
-      <x:c r="E28" s="34" t="s"/>
-      <x:c r="F28" s="35" t="s">
+      <x:c r="B28" s="23" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C28" s="24" t="s"/>
+      <x:c r="D28" s="24" t="s"/>
+      <x:c r="E28" s="24" t="s"/>
+      <x:c r="F28" s="25" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
         <x:v>77</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="36" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C29" s="37" t="s"/>
-      <x:c r="D29" s="37" t="s"/>
-      <x:c r="E29" s="37" t="s"/>
-      <x:c r="F29" s="38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="36" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C30" s="37" t="s"/>
-      <x:c r="D30" s="37" t="s"/>
-      <x:c r="E30" s="37" t="s"/>
-      <x:c r="F30" s="38" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="36" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C31" s="37" t="s"/>
-      <x:c r="D31" s="37" t="s"/>
-      <x:c r="E31" s="37" t="s"/>
-      <x:c r="F31" s="38" t="n">
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="36" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C32" s="37" t="s"/>
-      <x:c r="D32" s="37" t="s"/>
-      <x:c r="E32" s="37" t="s"/>
-      <x:c r="F32" s="38" t="n">
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="36" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C33" s="37" t="s"/>
-      <x:c r="D33" s="37" t="s"/>
-      <x:c r="E33" s="37" t="s"/>
-      <x:c r="F33" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="39" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C34" s="40" t="s"/>
-      <x:c r="D34" s="40" t="s"/>
-      <x:c r="E34" s="40" t="s"/>
-      <x:c r="F34" s="41" t="n">
+      <x:c r="B34" s="29" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,12 +22,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>DENIEL GENNE PUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -304,7 +307,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -344,6 +347,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -615,14 +642,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -635,59 +671,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -718,91 +754,103 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1031,58 +1079,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1125,776 +1173,776 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I9" s="12">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="12">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="L10" s="21">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I12" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I13" s="22">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I14" s="22">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I15" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I16" s="22">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I17" s="22">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I19" s="22">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I20" s="22">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I21" s="22">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="L22" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="E23" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I23" s="22">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="L23" s="21">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I24" s="22">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
+      <x:c r="J24" s="18" t="n">
         <x:v>1511219</x:v>
       </x:c>
-      <x:c r="K24" s="17" t="n">
+      <x:c r="K24" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L24" s="18">
+      <x:c r="L24" s="21">
         <x:v>46093.3109375</x:v>
       </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M24" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="20" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="C27" s="21" t="s"/>
-      <x:c r="D27" s="21" t="s"/>
-      <x:c r="E27" s="22" t="s"/>
-      <x:c r="F27" s="22" t="s"/>
+      <x:c r="B27" s="23" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C27" s="24" t="s"/>
+      <x:c r="D27" s="24" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="25" t="s"/>
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C28" s="24" t="s"/>
-      <x:c r="D28" s="24" t="s"/>
-      <x:c r="E28" s="24" t="s"/>
-      <x:c r="F28" s="25" t="s">
+      <x:c r="B28" s="26" t="s">
         <x:v>89</x:v>
       </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="s">
+        <x:v>90</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="B29" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s"/>
+      <x:c r="D29" s="30" t="s"/>
+      <x:c r="E29" s="30" t="s"/>
+      <x:c r="F29" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="B30" s="29" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s"/>
+      <x:c r="D30" s="30" t="s"/>
+      <x:c r="E30" s="30" t="s"/>
+      <x:c r="F30" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="B31" s="29" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s"/>
+      <x:c r="D31" s="30" t="s"/>
+      <x:c r="E31" s="30" t="s"/>
+      <x:c r="F31" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="B32" s="29" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="B33" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s"/>
+      <x:c r="D33" s="30" t="s"/>
+      <x:c r="E33" s="30" t="s"/>
+      <x:c r="F33" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="29" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C34" s="30" t="s"/>
-      <x:c r="D34" s="30" t="s"/>
-      <x:c r="E34" s="30" t="s"/>
-      <x:c r="F34" s="31" t="n">
+      <x:c r="B34" s="32" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C34" s="33" t="s"/>
+      <x:c r="D34" s="33" t="s"/>
+      <x:c r="E34" s="33" t="s"/>
+      <x:c r="F34" s="34" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -2861,7 +2909,7 @@
   <x:mergeCells count="11">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,6 +67,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -304,10 +340,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -352,15 +390,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -376,15 +406,8 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -647,21 +670,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -671,59 +694,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -754,103 +777,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1079,78 +1090,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28">
-      <x:c r="A5" s="4" t="s"/>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1171,7 +1194,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1211,743 +1234,793 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46090.2558217593</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46090.2558333333</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1511203</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46097.2890740741</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="20" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C29" s="21" t="s"/>
+      <x:c r="D29" s="21" t="s"/>
+      <x:c r="E29" s="22" t="s"/>
+      <x:c r="F29" s="22" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B30" s="23" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C30" s="24" t="s"/>
+      <x:c r="D30" s="24" t="s"/>
+      <x:c r="E30" s="24" t="s"/>
+      <x:c r="F30" s="25" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B36" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s"/>
+      <x:c r="D36" s="30" t="s"/>
+      <x:c r="E36" s="30" t="s"/>
+      <x:c r="F36" s="31" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I11" s="22">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I12" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I13" s="22">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I14" s="22">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I15" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I16" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I17" s="22">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I18" s="22">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I19" s="22">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I20" s="22">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I21" s="22">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I23" s="22">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I24" s="22">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C27" s="24" t="s"/>
-      <x:c r="D27" s="24" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="25" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="26" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C29" s="30" t="s"/>
-      <x:c r="D29" s="30" t="s"/>
-      <x:c r="E29" s="30" t="s"/>
-      <x:c r="F29" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="29" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C30" s="30" t="s"/>
-      <x:c r="D30" s="30" t="s"/>
-      <x:c r="E30" s="30" t="s"/>
-      <x:c r="F30" s="31" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="29" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C31" s="30" t="s"/>
-      <x:c r="D31" s="30" t="s"/>
-      <x:c r="E31" s="30" t="s"/>
-      <x:c r="F31" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="29" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C32" s="30" t="s"/>
-      <x:c r="D32" s="30" t="s"/>
-      <x:c r="E32" s="30" t="s"/>
-      <x:c r="F32" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="29" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C33" s="30" t="s"/>
-      <x:c r="D33" s="30" t="s"/>
-      <x:c r="E33" s="30" t="s"/>
-      <x:c r="F33" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="32" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C34" s="33" t="s"/>
-      <x:c r="D34" s="33" t="s"/>
-      <x:c r="E34" s="33" t="s"/>
-      <x:c r="F34" s="34" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2906,18 +2979,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="12">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B27:F27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B29:F29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -67,42 +67,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -345,7 +309,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -389,14 +353,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -408,6 +364,21 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -665,7 +636,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -673,16 +644,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -694,13 +665,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -712,41 +677,50 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -777,28 +751,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -813,55 +779,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1194,7 +1176,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1234,793 +1216,743 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46090.2558217593</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46090.2558333333</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46097.2890740741</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="H9" s="15">
+        <x:v>46090.2418287037</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46090.2418518519</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1511203</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46093.3049884259</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+      <x:c r="D10" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="F10" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="G10" s="17" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="H10" s="19">
+        <x:v>46090.2109953704</x:v>
+      </x:c>
+      <x:c r="I10" s="19">
+        <x:v>46090.2110069444</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1511204</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="21">
+        <x:v>46093.3080092593</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="C11" s="17" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="D11" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="E11" s="17" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="F11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46083.2322337963</x:v>
+      </x:c>
+      <x:c r="I11" s="19">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1511233</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="21">
+        <x:v>46097.149525463</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>46069.3514814815</x:v>
+      </x:c>
+      <x:c r="I12" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1511194</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="21">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>46084.2189236111</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1511223</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="21">
+        <x:v>46093.3723842593</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>46084.2250115741</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1511224</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="21">
+        <x:v>46093.3804398148</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>46069.3573032407</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1511193</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="21">
+        <x:v>46097.2426388889</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46069.3341087963</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1511195</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="21">
+        <x:v>46097.2447337963</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46084.1512962963</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1511211</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="21">
+        <x:v>46097.2494560185</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46084.3311921296</x:v>
+      </x:c>
+      <x:c r="I18" s="19">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1511222</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="21">
+        <x:v>46093.366875</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46073.1135069444</x:v>
+      </x:c>
+      <x:c r="I19" s="19">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1511213</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L19" s="21">
+        <x:v>46097.2511342593</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46092.1012731481</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1511231</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="21">
+        <x:v>46097.1408217593</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46069.121724537</x:v>
+      </x:c>
+      <x:c r="I21" s="19">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1511240</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="21">
+        <x:v>46097.3375</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I22" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46097.2890740741</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="L22" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="22" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="s"/>
+      <x:c r="D27" s="23" t="s"/>
+      <x:c r="E27" s="24" t="s"/>
+      <x:c r="F27" s="24" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="25" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C29" s="29" t="s"/>
+      <x:c r="D29" s="29" t="s"/>
+      <x:c r="E29" s="29" t="s"/>
+      <x:c r="F29" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="28" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E16" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E17" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="C30" s="29" t="s"/>
+      <x:c r="D30" s="29" t="s"/>
+      <x:c r="E30" s="29" t="s"/>
+      <x:c r="F30" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="28" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H20" s="17">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C22" s="15" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D22" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E22" s="15" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="C31" s="29" t="s"/>
+      <x:c r="D31" s="29" t="s"/>
+      <x:c r="E31" s="29" t="s"/>
+      <x:c r="F31" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="28" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H22" s="17">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J22" s="16" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M22" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C23" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D23" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E23" s="15" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="28" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H23" s="17">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J23" s="16" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M23" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="15" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C24" s="15" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D24" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G24" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H24" s="17">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J24" s="16" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M24" s="15" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="15" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C25" s="15" t="s">
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="31" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="G25" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="H25" s="17">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J25" s="16" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M25" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="15" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C26" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D26" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G26" s="15" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H26" s="17">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I26" s="17">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J26" s="16" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K26" s="18" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L26" s="19">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M26" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="20" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C29" s="21" t="s"/>
-      <x:c r="D29" s="21" t="s"/>
-      <x:c r="E29" s="22" t="s"/>
-      <x:c r="F29" s="22" t="s"/>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="23" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C30" s="24" t="s"/>
-      <x:c r="D30" s="24" t="s"/>
-      <x:c r="E30" s="24" t="s"/>
-      <x:c r="F30" s="25" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="29" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C36" s="30" t="s"/>
-      <x:c r="D36" s="30" t="s"/>
-      <x:c r="E36" s="30" t="s"/>
-      <x:c r="F36" s="31" t="n">
+      <x:c r="C34" s="32" t="s"/>
+      <x:c r="D34" s="32" t="s"/>
+      <x:c r="E34" s="32" t="s"/>
+      <x:c r="F34" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2984,14 +2916,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B29:F29"/>
+    <x:mergeCell ref="B27:F27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -169,6 +169,18 @@
   </x:si>
   <x:si>
     <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLH GENTECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-17-11-0683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1109-317</x:t>
   </x:si>
   <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
@@ -1541,19 +1553,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H16" s="19">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>46094</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
         <x:v>21</x:v>
@@ -1579,19 +1591,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H17" s="19">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I17" s="19">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="21">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
         <x:v>21</x:v>
@@ -1617,19 +1629,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H18" s="19">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>46070</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
         <x:v>21</x:v>
@@ -1640,34 +1652,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C19" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D19" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E19" s="17" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F19" s="17" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G19" s="17" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>45751</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
-        <x:v>7530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
         <x:v>21</x:v>
@@ -1678,7 +1690,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>31</x:v>
@@ -1693,19 +1705,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H20" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>46100</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L20" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
         <x:v>21</x:v>
@@ -1731,19 +1743,19 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
         <x:v>21</x:v>
@@ -1751,176 +1763,203 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C22" s="17" t="s">
+      <x:c r="D22" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
+      <x:c r="F22" s="17" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F22" s="17" t="s">
+      <x:c r="G22" s="17" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="H22" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>77</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="s">
+      <x:c r="F23" s="17" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
+      <x:c r="G23" s="17" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F23" s="17" t="s">
+      <x:c r="H23" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I23" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="D24" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E24" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="F24" s="17" t="s">
+      <x:c r="G24" s="17" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="H24" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46094</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="24" t="s"/>
-      <x:c r="F27" s="24" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
-        <x:v>3</x:v>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="22" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="24" t="s"/>
+      <x:c r="F28" s="24" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="25" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="s">
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="28" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C30" s="29" t="s"/>
       <x:c r="D30" s="29" t="s"/>
       <x:c r="E30" s="29" t="s"/>
       <x:c r="F30" s="30" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="28" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="29" t="s"/>
       <x:c r="D31" s="29" t="s"/>
       <x:c r="E31" s="29" t="s"/>
       <x:c r="F31" s="30" t="n">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="28" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C32" s="29" t="s"/>
       <x:c r="D32" s="29" t="s"/>
@@ -1931,7 +1970,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="28" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C33" s="29" t="s"/>
       <x:c r="D33" s="29" t="s"/>
@@ -1940,18 +1979,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="31" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C34" s="32" t="s"/>
-      <x:c r="D34" s="32" t="s"/>
-      <x:c r="E34" s="32" t="s"/>
-      <x:c r="F34" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="28" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="31" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C35" s="32" t="s"/>
+      <x:c r="D35" s="32" t="s"/>
+      <x:c r="E35" s="32" t="s"/>
+      <x:c r="F35" s="33" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2916,14 +2965,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B27:F27"/>
-    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B28:F28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -144,6 +144,24 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -153,24 +171,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
@@ -183,6 +183,18 @@
     <x:t>43A-2-2026-1109-317</x:t>
   </x:si>
   <x:si>
+    <x:t>MOBILECRAZE TELECOM INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NO. 6 PUREGOLD BLDG. SAN PABLO COLAGO AVE, SAN ROQUE, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1113-757</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -210,6 +222,15 @@
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-471R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1108-762</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -217,15 +238,6 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1168-173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 24-471R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1108-762</x:t>
   </x:si>
   <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
@@ -1439,19 +1451,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46133</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
         <x:v>21</x:v>
@@ -1515,19 +1527,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H15" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
         <x:v>21</x:v>
@@ -1591,19 +1603,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H17" s="19">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I17" s="19">
-        <x:v>46094</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="21">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
         <x:v>21</x:v>
@@ -1629,19 +1641,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H18" s="19">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>46102</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
         <x:v>21</x:v>
@@ -1667,19 +1679,19 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>46070</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
         <x:v>21</x:v>
@@ -1690,19 +1702,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E20" s="17" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F20" s="17" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G20" s="17" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H20" s="19">
         <x:v>46073.1135069444</x:v>
@@ -1728,7 +1740,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>31</x:v>
@@ -1743,19 +1755,19 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
         <x:v>21</x:v>
@@ -1781,19 +1793,19 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
         <x:v>21</x:v>
@@ -1801,176 +1813,203 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C23" s="17" t="s">
+      <x:c r="D23" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
+      <x:c r="F23" s="17" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F23" s="17" t="s">
+      <x:c r="G23" s="17" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="H23" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
-        <x:v>81</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="C24" s="17" t="s">
+      <x:c r="F24" s="17" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
+      <x:c r="G24" s="17" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="F24" s="17" t="s">
+      <x:c r="H24" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E25" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F25" s="17" t="s">
+      <x:c r="G25" s="17" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="H25" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46094</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I26" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L26" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="24" t="s"/>
-      <x:c r="F28" s="24" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
-        <x:v>3</x:v>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="22" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="s"/>
+      <x:c r="D29" s="23" t="s"/>
+      <x:c r="E29" s="24" t="s"/>
+      <x:c r="F29" s="24" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B30" s="25" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="s">
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="28" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C31" s="29" t="s"/>
       <x:c r="D31" s="29" t="s"/>
       <x:c r="E31" s="29" t="s"/>
       <x:c r="F31" s="30" t="n">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="28" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C32" s="29" t="s"/>
       <x:c r="D32" s="29" t="s"/>
       <x:c r="E32" s="29" t="s"/>
       <x:c r="F32" s="30" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="28" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C33" s="29" t="s"/>
       <x:c r="D33" s="29" t="s"/>
@@ -1981,7 +2020,7 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="28" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C34" s="29" t="s"/>
       <x:c r="D34" s="29" t="s"/>
@@ -1990,18 +2029,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="31" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C35" s="32" t="s"/>
-      <x:c r="D35" s="32" t="s"/>
-      <x:c r="E35" s="32" t="s"/>
-      <x:c r="F35" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="28" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C35" s="29" t="s"/>
+      <x:c r="D35" s="29" t="s"/>
+      <x:c r="E35" s="29" t="s"/>
+      <x:c r="F35" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B36" s="31" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C36" s="32" t="s"/>
+      <x:c r="D36" s="32" t="s"/>
+      <x:c r="E36" s="32" t="s"/>
+      <x:c r="F36" s="33" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2965,14 +3014,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B28:F28"/>
-    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B29:F29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -144,6 +144,15 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -162,15 +171,6 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
@@ -241,6 +241,18 @@
   </x:si>
   <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1201-204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
   </x:si>
   <x:si>
     <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
@@ -1451,19 +1463,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46100</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
         <x:v>21</x:v>
@@ -1489,19 +1501,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H14" s="19">
-        <x:v>46084.2250115741</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46144</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>1511224</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="21">
-        <x:v>46093.3804398148</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
         <x:v>21</x:v>
@@ -1527,19 +1539,19 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H15" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46084.2250115741</x:v>
       </x:c>
       <x:c r="I15" s="19">
-        <x:v>46133</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511224</x:v>
       </x:c>
       <x:c r="K15" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46093.3804398148</x:v>
       </x:c>
       <x:c r="M15" s="17" t="s">
         <x:v>21</x:v>
@@ -1793,22 +1805,22 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46097.4214930556</x:v>
       </x:c>
       <x:c r="I22" s="19">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511270</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46100.2966666667</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>21</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -1816,7 +1828,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
         <x:v>31</x:v>
@@ -1831,19 +1843,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
         <x:v>21</x:v>
@@ -1851,176 +1863,203 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C24" s="17" t="s">
+      <x:c r="D24" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
+      <x:c r="F24" s="17" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F24" s="17" t="s">
+      <x:c r="G24" s="17" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="H24" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
-        <x:v>85</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C25" s="17" t="s">
+      <x:c r="F25" s="17" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
+      <x:c r="G25" s="17" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F25" s="17" t="s">
+      <x:c r="H25" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L25" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F26" s="17" t="s">
+      <x:c r="G26" s="17" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="H26" s="19">
-        <x:v>46092.9637847222</x:v>
+        <x:v>46084.1579513889</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46094</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511219</x:v>
+        <x:v>1511226</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46093.3109375</x:v>
+        <x:v>46093.4169212963</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="17" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
+        <x:v>46092.9637847222</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1511219</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46093.3109375</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="22" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C29" s="23" t="s"/>
-      <x:c r="D29" s="23" t="s"/>
-      <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="24" t="s"/>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
-        <x:v>3</x:v>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="22" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C30" s="23" t="s"/>
+      <x:c r="D30" s="23" t="s"/>
+      <x:c r="E30" s="24" t="s"/>
+      <x:c r="F30" s="24" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="25" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="s">
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="28" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C32" s="29" t="s"/>
       <x:c r="D32" s="29" t="s"/>
       <x:c r="E32" s="29" t="s"/>
       <x:c r="F32" s="30" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="28" t="s">
-        <x:v>80</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C33" s="29" t="s"/>
       <x:c r="D33" s="29" t="s"/>
       <x:c r="E33" s="29" t="s"/>
       <x:c r="F33" s="30" t="n">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="28" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C34" s="29" t="s"/>
       <x:c r="D34" s="29" t="s"/>
@@ -2031,7 +2070,7 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C35" s="29" t="s"/>
       <x:c r="D35" s="29" t="s"/>
@@ -2040,18 +2079,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="31" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C36" s="32" t="s"/>
-      <x:c r="D36" s="32" t="s"/>
-      <x:c r="E36" s="32" t="s"/>
-      <x:c r="F36" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="28" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C36" s="29" t="s"/>
+      <x:c r="D36" s="29" t="s"/>
+      <x:c r="E36" s="29" t="s"/>
+      <x:c r="F36" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="31" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C37" s="32" t="s"/>
+      <x:c r="D37" s="32" t="s"/>
+      <x:c r="E37" s="32" t="s"/>
+      <x:c r="F37" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3014,14 +3063,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B29:F29"/>
-    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B30:F30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -144,6 +144,36 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1111-408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -153,24 +183,6 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
@@ -195,6 +207,18 @@
     <x:t>43A-2-2026-1113-757</x:t>
   </x:si>
   <x:si>
+    <x:t>PHONEVILLE MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sm City Taytay Manila East Road Sm City Taytay Manila East Road, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1202-217</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -243,6 +267,15 @@
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0775 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1192-904</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
   </x:si>
   <x:si>
@@ -252,18 +285,6 @@
     <x:t>43A-3-2026-1201-204</x:t>
   </x:si>
   <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0775 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1192-904</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -307,6 +328,15 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1162-745</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-02-2011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1163-392</x:t>
   </x:si>
   <x:si>
     <x:t>Service Center Permit (RENEWAL)</x:t>
@@ -1463,19 +1493,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="19">
-        <x:v>46084.2189236111</x:v>
+        <x:v>46069.3573032407</x:v>
       </x:c>
       <x:c r="I13" s="19">
-        <x:v>46133</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>1511223</x:v>
+        <x:v>1511193</x:v>
       </x:c>
       <x:c r="K13" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="21">
-        <x:v>46093.3723842593</x:v>
+        <x:v>46097.2426388889</x:v>
       </x:c>
       <x:c r="M13" s="17" t="s">
         <x:v>21</x:v>
@@ -1501,22 +1531,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H14" s="19">
-        <x:v>46069.3573032407</x:v>
+        <x:v>46073.1441087963</x:v>
       </x:c>
       <x:c r="I14" s="19">
-        <x:v>46100</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>1511193</x:v>
+        <x:v>1511278</x:v>
       </x:c>
       <x:c r="K14" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="21">
-        <x:v>46097.2426388889</x:v>
+        <x:v>46100.4005439815</x:v>
       </x:c>
       <x:c r="M14" s="17" t="s">
-        <x:v>21</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
@@ -1530,13 +1560,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="E15" s="17" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F15" s="17" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G15" s="17" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H15" s="19">
         <x:v>46084.2250115741</x:v>
@@ -1562,7 +1592,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C16" s="17" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D16" s="18" t="s">
         <x:v>31</x:v>
@@ -1577,19 +1607,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H16" s="19">
-        <x:v>46073.125162037</x:v>
+        <x:v>46084.2189236111</x:v>
       </x:c>
       <x:c r="I16" s="19">
-        <x:v>45619</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>1511246</x:v>
+        <x:v>1511223</x:v>
       </x:c>
       <x:c r="K16" s="20" t="n">
-        <x:v>11280</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="21">
-        <x:v>46099.1200231481</x:v>
+        <x:v>46093.3723842593</x:v>
       </x:c>
       <x:c r="M16" s="17" t="s">
         <x:v>21</x:v>
@@ -1615,19 +1645,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H17" s="19">
-        <x:v>46073.1541087963</x:v>
+        <x:v>46073.125162037</x:v>
       </x:c>
       <x:c r="I17" s="19">
-        <x:v>46030</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>1511248</x:v>
+        <x:v>1511246</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L17" s="21">
-        <x:v>46099.1583912037</x:v>
+        <x:v>46099.1200231481</x:v>
       </x:c>
       <x:c r="M17" s="17" t="s">
         <x:v>21</x:v>
@@ -1653,19 +1683,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H18" s="19">
-        <x:v>46069.3341087963</x:v>
+        <x:v>46073.1541087963</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>46094</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1511195</x:v>
+        <x:v>1511248</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46097.2447337963</x:v>
+        <x:v>46099.1583912037</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
         <x:v>21</x:v>
@@ -1691,22 +1721,22 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46084.1512962963</x:v>
+        <x:v>46097.4788425926</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>46102</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1511211</x:v>
+        <x:v>1511271</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46097.2494560185</x:v>
+        <x:v>46100.29875</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
-        <x:v>21</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
@@ -1729,19 +1759,19 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="H20" s="19">
-        <x:v>46073.1135069444</x:v>
+        <x:v>46069.3341087963</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>45751</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>1511213</x:v>
+        <x:v>1511195</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="21">
-        <x:v>46097.2511342593</x:v>
+        <x:v>46097.2447337963</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
         <x:v>21</x:v>
@@ -1752,34 +1782,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E21" s="17" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F21" s="17" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G21" s="17" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46084.3311921296</x:v>
+        <x:v>46084.1512962963</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46070</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1511222</x:v>
+        <x:v>1511211</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46093.366875</x:v>
+        <x:v>46097.2494560185</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
         <x:v>21</x:v>
@@ -1790,37 +1820,37 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="17" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D22" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E22" s="17" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F22" s="17" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G22" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46097.4214930556</x:v>
+        <x:v>46073.1135069444</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>46100</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1511270</x:v>
+        <x:v>1511213</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46100.2966666667</x:v>
+        <x:v>46097.2511342593</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
-        <x:v>76</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
@@ -1828,7 +1858,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="17" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D23" s="18" t="s">
         <x:v>31</x:v>
@@ -1843,19 +1873,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46092.1012731481</x:v>
+        <x:v>46084.3311921296</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46100</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1511231</x:v>
+        <x:v>1511222</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46097.1408217593</x:v>
+        <x:v>46093.366875</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
         <x:v>21</x:v>
@@ -1881,19 +1911,19 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46069.121724537</x:v>
+        <x:v>46092.1012731481</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46157</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1511240</x:v>
+        <x:v>1511231</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46097.3375</x:v>
+        <x:v>46097.1408217593</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
         <x:v>21</x:v>
@@ -1901,75 +1931,75 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C25" s="17" t="s">
+      <x:c r="F25" s="17" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
+      <x:c r="G25" s="17" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F25" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="H25" s="19">
-        <x:v>46084.3419444444</x:v>
+        <x:v>46097.4214930556</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46084.3419560185</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1507967</x:v>
+        <x:v>1511270</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46090.3480902778</x:v>
+        <x:v>46100.2966666667</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="17" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C26" s="17" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F26" s="17" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G26" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46084.1579513889</x:v>
+        <x:v>46069.121724537</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46145</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1511226</x:v>
+        <x:v>1511240</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46093.4169212963</x:v>
+        <x:v>46097.3375</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
         <x:v>21</x:v>
@@ -1977,133 +2007,244 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C27" s="17" t="s">
+      <x:c r="H27" s="19">
+        <x:v>46084.3419444444</x:v>
+      </x:c>
+      <x:c r="I27" s="19">
+        <x:v>46084.3419560185</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="n">
+        <x:v>1507967</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L27" s="21">
+        <x:v>46090.3480902778</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D27" s="18" t="s">
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="17" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E27" s="17" t="s">
+      <x:c r="E28" s="17" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
+        <x:v>46084.1579513889</x:v>
+      </x:c>
+      <x:c r="I28" s="19">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J28" s="18" t="n">
+        <x:v>1511226</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="21">
+        <x:v>46093.4169212963</x:v>
+      </x:c>
+      <x:c r="M28" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="17" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
+      <x:c r="C29" s="17" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H29" s="19">
+        <x:v>46084.1627430556</x:v>
+      </x:c>
+      <x:c r="I29" s="19">
+        <x:v>46060</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="n">
+        <x:v>1511277</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L29" s="21">
+        <x:v>46100.3929282407</x:v>
+      </x:c>
+      <x:c r="M29" s="17" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="17" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H30" s="19">
         <x:v>46092.9637847222</x:v>
       </x:c>
-      <x:c r="I27" s="19">
+      <x:c r="I30" s="19">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J27" s="18" t="n">
+      <x:c r="J30" s="18" t="n">
         <x:v>1511219</x:v>
       </x:c>
-      <x:c r="K27" s="20" t="n">
+      <x:c r="K30" s="20" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L27" s="21">
+      <x:c r="L30" s="21">
         <x:v>46093.3109375</x:v>
       </x:c>
-      <x:c r="M27" s="17" t="s">
+      <x:c r="M30" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C30" s="23" t="s"/>
-      <x:c r="D30" s="23" t="s"/>
-      <x:c r="E30" s="24" t="s"/>
-      <x:c r="F30" s="24" t="s"/>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="28" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="28" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C34" s="29" t="s"/>
-      <x:c r="D34" s="29" t="s"/>
-      <x:c r="E34" s="29" t="s"/>
-      <x:c r="F34" s="30" t="n">
-        <x:v>1</x:v>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="22" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C33" s="23" t="s"/>
+      <x:c r="D33" s="23" t="s"/>
+      <x:c r="E33" s="24" t="s"/>
+      <x:c r="F33" s="24" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="25" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="s">
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="28" t="s">
-        <x:v>90</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C35" s="29" t="s"/>
       <x:c r="D35" s="29" t="s"/>
       <x:c r="E35" s="29" t="s"/>
       <x:c r="F35" s="30" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="28" t="s">
-        <x:v>95</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C36" s="29" t="s"/>
       <x:c r="D36" s="29" t="s"/>
       <x:c r="E36" s="29" t="s"/>
       <x:c r="F36" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="28" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C37" s="29" t="s"/>
+      <x:c r="D37" s="29" t="s"/>
+      <x:c r="E37" s="29" t="s"/>
+      <x:c r="F37" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="31" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C37" s="32" t="s"/>
-      <x:c r="D37" s="32" t="s"/>
-      <x:c r="E37" s="32" t="s"/>
-      <x:c r="F37" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="28" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C38" s="29" t="s"/>
+      <x:c r="D38" s="29" t="s"/>
+      <x:c r="E38" s="29" t="s"/>
+      <x:c r="F38" s="30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="28" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C39" s="29" t="s"/>
+      <x:c r="D39" s="29" t="s"/>
+      <x:c r="E39" s="29" t="s"/>
+      <x:c r="F39" s="30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B40" s="31" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C40" s="32" t="s"/>
+      <x:c r="D40" s="32" t="s"/>
+      <x:c r="E40" s="32" t="s"/>
+      <x:c r="F40" s="33" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3063,14 +3204,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B30:F30"/>
-    <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B33:F33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -87,6 +87,9 @@
     <x:t>43A-3-2026-1179-857</x:t>
   </x:si>
   <x:si>
+    <x:t>1511203</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -99,6 +102,9 @@
     <x:t>43A-3-2026-1178-478</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve"> 1511203</x:t>
+  </x:si>
+  <x:si>
     <x:t>X-DOT CONNECTION INC</x:t>
   </x:si>
   <x:si>
@@ -111,6 +117,9 @@
     <x:t>43A-3-2026-1177-099</x:t>
   </x:si>
   <x:si>
+    <x:t>1511204</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -129,6 +138,9 @@
     <x:t>43A-3-2026-1150-325</x:t>
   </x:si>
   <x:si>
+    <x:t>1511233</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -141,6 +153,9 @@
     <x:t>43A-2-2026-1095-163</x:t>
   </x:si>
   <x:si>
+    <x:t>1511194</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -153,6 +168,9 @@
     <x:t>43A-2-2026-1096-022</x:t>
   </x:si>
   <x:si>
+    <x:t>1511193</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
   </x:si>
   <x:si>
@@ -162,6 +180,9 @@
     <x:t>43A-2-2026-1111-408</x:t>
   </x:si>
   <x:si>
+    <x:t>1511278</x:t>
+  </x:si>
+  <x:si>
     <x:t>Caesar Allen Centeno</x:t>
   </x:si>
   <x:si>
@@ -174,6 +195,9 @@
     <x:t>43A-3-2026-1165-147</x:t>
   </x:si>
   <x:si>
+    <x:t>1511224</x:t>
+  </x:si>
+  <x:si>
     <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
   </x:si>
   <x:si>
@@ -183,6 +207,9 @@
     <x:t>43A-3-2026-1164-444</x:t>
   </x:si>
   <x:si>
+    <x:t>1511223</x:t>
+  </x:si>
+  <x:si>
     <x:t>HLH GENTECH INC.</x:t>
   </x:si>
   <x:si>
@@ -195,6 +222,9 @@
     <x:t>43A-2-2026-1109-317</x:t>
   </x:si>
   <x:si>
+    <x:t>1511246</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILECRAZE TELECOM INC.</x:t>
   </x:si>
   <x:si>
@@ -207,6 +237,9 @@
     <x:t>43A-2-2026-1113-757</x:t>
   </x:si>
   <x:si>
+    <x:t>1511248</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHONEVILLE MOBILE INC.</x:t>
   </x:si>
   <x:si>
@@ -219,6 +252,9 @@
     <x:t>43A-3-2026-1202-217</x:t>
   </x:si>
   <x:si>
+    <x:t>1511271</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -231,6 +267,9 @@
     <x:t>43A-2-2026-1094-777</x:t>
   </x:si>
   <x:si>
+    <x:t>1511195</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC</x:t>
   </x:si>
   <x:si>
@@ -243,6 +282,9 @@
     <x:t>43A-3-2026-1161-717</x:t>
   </x:si>
   <x:si>
+    <x:t>1511211</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
@@ -255,6 +297,9 @@
     <x:t>43A-2-2026-1108-762</x:t>
   </x:si>
   <x:si>
+    <x:t>1511213</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -264,6 +309,9 @@
     <x:t>43A-3-2026-1168-173</x:t>
   </x:si>
   <x:si>
+    <x:t>1511222</x:t>
+  </x:si>
+  <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
   </x:si>
   <x:si>
@@ -276,6 +324,9 @@
     <x:t>43A-3-2026-1192-904</x:t>
   </x:si>
   <x:si>
+    <x:t>1511231</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
   </x:si>
   <x:si>
@@ -285,6 +336,9 @@
     <x:t>43A-3-2026-1201-204</x:t>
   </x:si>
   <x:si>
+    <x:t>1511270</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -297,6 +351,9 @@
     <x:t>43A-2-2026-1084-395</x:t>
   </x:si>
   <x:si>
+    <x:t>1511240</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -312,6 +369,9 @@
     <x:t>43A-3-2026-1169-102</x:t>
   </x:si>
   <x:si>
+    <x:t>1507967</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ricardo Natividad</x:t>
   </x:si>
   <x:si>
@@ -330,6 +390,9 @@
     <x:t>43A-3-2026-1162-745</x:t>
   </x:si>
   <x:si>
+    <x:t>1511226</x:t>
+  </x:si>
+  <x:si>
     <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -339,6 +402,9 @@
     <x:t>43A-3-2026-1163-392</x:t>
   </x:si>
   <x:si>
+    <x:t>1511277</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -352,6 +418,9 @@
   </x:si>
   <x:si>
     <x:t>43A-3-2026-1194-347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511219</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -375,7 +444,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -444,13 +513,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -702,7 +764,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -743,50 +805,41 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -834,6 +887,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -845,71 +902,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1290,7 +1331,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
@@ -1302,23 +1343,23 @@
       <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46090.2558217593</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46090.2558333333</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="H8" s="16">
+        <x:v>46090.2558238542</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46090.2558400116</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46097.2890740741</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46097.2890797917</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1328,920 +1369,920 @@
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46090.2418365857</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46090.2418534606</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>46093.3049920255</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46090.2418287037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46090.2418518519</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1511203</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46090.210999456</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46090.211015162</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46093.3049884259</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="s">
+      <x:c r="L10" s="18">
+        <x:v>46093.3080127546</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46083.2322339931</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46097.1495293519</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46069.3514850347</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46069.3573124306</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46097.2426396643</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46073.1441202083</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46100.4005466667</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46084.2250188542</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>46093.3804507639</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46084.2189288542</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46093.3723926852</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46073.1251625463</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>45619</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>11280</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46099.1200232986</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46073.1541139005</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46099.1584012616</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46097.4788515162</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46100.2987549074</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46069.3341180556</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46097.244735544</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46084.1513040509</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46097.2494578472</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46073.1135088426</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46097.2511403241</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46084.3311976389</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46093.3668852546</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46092.1012814815</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46097.1408234491</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46097.4214954398</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46100.2966699421</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46069.1217257292</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46097.3375062153</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H10" s="19">
-        <x:v>46090.2109953704</x:v>
-      </x:c>
-      <x:c r="I10" s="19">
-        <x:v>46090.2110069444</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>1511204</x:v>
-      </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="E27" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46084.3419451968</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46084.3419617014</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="21">
-        <x:v>46093.3080092593</x:v>
-      </x:c>
-      <x:c r="M10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E11" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F11" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="s">
+      <x:c r="L27" s="18">
+        <x:v>46090.3480933681</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H11" s="19">
-        <x:v>46083.2322337963</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>1511233</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="E28" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46084.1579541898</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="21">
-        <x:v>46097.149525463</x:v>
-      </x:c>
-      <x:c r="M11" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E12" s="17" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="19">
-        <x:v>46069.3514814815</x:v>
-      </x:c>
-      <x:c r="I12" s="19">
+      <x:c r="L28" s="18">
+        <x:v>46093.4169326042</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46084.1627466204</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46060</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46100.392939537</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46092.9637875116</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1511194</x:v>
-      </x:c>
-      <x:c r="K12" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="21">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M12" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E13" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H13" s="19">
-        <x:v>46069.3573032407</x:v>
-      </x:c>
-      <x:c r="I13" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>1511193</x:v>
-      </x:c>
-      <x:c r="K13" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="21">
-        <x:v>46097.2426388889</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H14" s="19">
-        <x:v>46073.1441087963</x:v>
-      </x:c>
-      <x:c r="I14" s="19">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>1511278</x:v>
-      </x:c>
-      <x:c r="K14" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="21">
-        <x:v>46100.4005439815</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E15" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H15" s="19">
-        <x:v>46084.2250115741</x:v>
-      </x:c>
-      <x:c r="I15" s="19">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>1511224</x:v>
-      </x:c>
-      <x:c r="K15" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="21">
-        <x:v>46093.3804398148</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F16" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H16" s="19">
-        <x:v>46084.2189236111</x:v>
-      </x:c>
-      <x:c r="I16" s="19">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>1511223</x:v>
-      </x:c>
-      <x:c r="K16" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L16" s="21">
-        <x:v>46093.3723842593</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E17" s="17" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F17" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H17" s="19">
-        <x:v>46073.125162037</x:v>
-      </x:c>
-      <x:c r="I17" s="19">
-        <x:v>45619</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>1511246</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:v>11280</x:v>
-      </x:c>
-      <x:c r="L17" s="21">
-        <x:v>46099.1200231481</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H18" s="19">
-        <x:v>46073.1541087963</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>1511248</x:v>
-      </x:c>
-      <x:c r="K18" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="21">
-        <x:v>46099.1583912037</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C19" s="17" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E19" s="17" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F19" s="17" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H19" s="19">
-        <x:v>46097.4788425926</x:v>
-      </x:c>
-      <x:c r="I19" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>1511271</x:v>
-      </x:c>
-      <x:c r="K19" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="21">
-        <x:v>46100.29875</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C20" s="17" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H20" s="19">
-        <x:v>46069.3341087963</x:v>
-      </x:c>
-      <x:c r="I20" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>1511195</x:v>
-      </x:c>
-      <x:c r="K20" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="21">
-        <x:v>46097.2447337963</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E21" s="17" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F21" s="17" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H21" s="19">
-        <x:v>46084.1512962963</x:v>
-      </x:c>
-      <x:c r="I21" s="19">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>1511211</x:v>
-      </x:c>
-      <x:c r="K21" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="21">
-        <x:v>46097.2494560185</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C22" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E22" s="17" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F22" s="17" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H22" s="19">
-        <x:v>46073.1135069444</x:v>
-      </x:c>
-      <x:c r="I22" s="19">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>1511213</x:v>
-      </x:c>
-      <x:c r="K22" s="20" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L22" s="21">
-        <x:v>46097.2511342593</x:v>
-      </x:c>
-      <x:c r="M22" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C23" s="17" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E23" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F23" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H23" s="19">
-        <x:v>46084.3311921296</x:v>
-      </x:c>
-      <x:c r="I23" s="19">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>1511222</x:v>
-      </x:c>
-      <x:c r="K23" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L23" s="21">
-        <x:v>46093.366875</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E24" s="17" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F24" s="17" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H24" s="19">
-        <x:v>46092.1012731481</x:v>
-      </x:c>
-      <x:c r="I24" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>1511231</x:v>
-      </x:c>
-      <x:c r="K24" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="21">
-        <x:v>46097.1408217593</x:v>
-      </x:c>
-      <x:c r="M24" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C25" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E25" s="17" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F25" s="17" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H25" s="19">
-        <x:v>46097.4214930556</x:v>
-      </x:c>
-      <x:c r="I25" s="19">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="n">
-        <x:v>1511270</x:v>
-      </x:c>
-      <x:c r="K25" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="21">
-        <x:v>46100.2966666667</x:v>
-      </x:c>
-      <x:c r="M25" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="17" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C26" s="17" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D26" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E26" s="17" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F26" s="17" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H26" s="19">
-        <x:v>46069.121724537</x:v>
-      </x:c>
-      <x:c r="I26" s="19">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="n">
-        <x:v>1511240</x:v>
-      </x:c>
-      <x:c r="K26" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L26" s="21">
-        <x:v>46097.3375</x:v>
-      </x:c>
-      <x:c r="M26" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C27" s="17" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D27" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E27" s="17" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F27" s="17" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H27" s="19">
-        <x:v>46084.3419444444</x:v>
-      </x:c>
-      <x:c r="I27" s="19">
-        <x:v>46084.3419560185</x:v>
-      </x:c>
-      <x:c r="J27" s="18" t="n">
-        <x:v>1507967</x:v>
-      </x:c>
-      <x:c r="K27" s="20" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L27" s="21">
-        <x:v>46090.3480902778</x:v>
-      </x:c>
-      <x:c r="M27" s="17" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C28" s="17" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D28" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E28" s="17" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F28" s="17" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H28" s="19">
-        <x:v>46084.1579513889</x:v>
-      </x:c>
-      <x:c r="I28" s="19">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J28" s="18" t="n">
-        <x:v>1511226</x:v>
-      </x:c>
-      <x:c r="K28" s="20" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="21">
-        <x:v>46093.4169212963</x:v>
-      </x:c>
-      <x:c r="M28" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C29" s="17" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E29" s="17" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F29" s="17" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G29" s="17" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H29" s="19">
-        <x:v>46084.1627430556</x:v>
-      </x:c>
-      <x:c r="I29" s="19">
-        <x:v>46060</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="n">
-        <x:v>1511277</x:v>
-      </x:c>
-      <x:c r="K29" s="20" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L29" s="21">
-        <x:v>46100.3929282407</x:v>
-      </x:c>
-      <x:c r="M29" s="17" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="17" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C30" s="17" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D30" s="18" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E30" s="17" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F30" s="17" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G30" s="17" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H30" s="19">
-        <x:v>46092.9637847222</x:v>
-      </x:c>
-      <x:c r="I30" s="19">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J30" s="18" t="n">
-        <x:v>1511219</x:v>
-      </x:c>
-      <x:c r="K30" s="20" t="n">
+      <x:c r="J30" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L30" s="21">
-        <x:v>46093.3109375</x:v>
-      </x:c>
-      <x:c r="M30" s="17" t="s">
-        <x:v>21</x:v>
+      <x:c r="L30" s="18">
+        <x:v>46093.3109466551</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="22" t="s">
+      <x:c r="B33" s="19" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="s"/>
+      <x:c r="D33" s="20" t="s"/>
+      <x:c r="E33" s="21" t="s"/>
+      <x:c r="F33" s="21" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="22" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C34" s="23" t="s"/>
+      <x:c r="D34" s="23" t="s"/>
+      <x:c r="E34" s="23" t="s"/>
+      <x:c r="F34" s="24" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="25" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="25" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="C33" s="23" t="s"/>
-      <x:c r="D33" s="23" t="s"/>
-      <x:c r="E33" s="24" t="s"/>
-      <x:c r="F33" s="24" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="25" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C34" s="26" t="s"/>
-      <x:c r="D34" s="26" t="s"/>
-      <x:c r="E34" s="26" t="s"/>
-      <x:c r="F34" s="27" t="s">
-        <x:v>112</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C35" s="29" t="s"/>
-      <x:c r="D35" s="29" t="s"/>
-      <x:c r="E35" s="29" t="s"/>
-      <x:c r="F35" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="28" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C36" s="29" t="s"/>
-      <x:c r="D36" s="29" t="s"/>
-      <x:c r="E36" s="29" t="s"/>
-      <x:c r="F36" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="28" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C37" s="29" t="s"/>
-      <x:c r="D37" s="29" t="s"/>
-      <x:c r="E37" s="29" t="s"/>
-      <x:c r="F37" s="30" t="n">
+      <x:c r="C37" s="26" t="s"/>
+      <x:c r="D37" s="26" t="s"/>
+      <x:c r="E37" s="26" t="s"/>
+      <x:c r="F37" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="28" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C38" s="29" t="s"/>
-      <x:c r="D38" s="29" t="s"/>
-      <x:c r="E38" s="29" t="s"/>
-      <x:c r="F38" s="30" t="n">
+      <x:c r="B38" s="25" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C38" s="26" t="s"/>
+      <x:c r="D38" s="26" t="s"/>
+      <x:c r="E38" s="26" t="s"/>
+      <x:c r="F38" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C39" s="29" t="s"/>
-      <x:c r="D39" s="29" t="s"/>
-      <x:c r="E39" s="29" t="s"/>
-      <x:c r="F39" s="30" t="n">
+      <x:c r="B39" s="25" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C39" s="26" t="s"/>
+      <x:c r="D39" s="26" t="s"/>
+      <x:c r="E39" s="26" t="s"/>
+      <x:c r="F39" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B40" s="31" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C40" s="32" t="s"/>
-      <x:c r="D40" s="32" t="s"/>
-      <x:c r="E40" s="32" t="s"/>
-      <x:c r="F40" s="33" t="n">
+      <x:c r="B40" s="28" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C40" s="29" t="s"/>
+      <x:c r="D40" s="29" t="s"/>
+      <x:c r="E40" s="29" t="s"/>
+      <x:c r="F40" s="30" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,9 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
-  <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
+  <x:si>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>DENIEL GENNE PUYO</x:t>
@@ -72,12 +72,66 @@
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
+    <x:t>DGNATION INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 101B GROUND FLOOR VISTAMALL DASMARIÑAS AGUINALDO HIGHWAY, SAN AGUSTIN II, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07540-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1226-938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511314</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOWER GROUND LEVEL VISTA MALL SOMO DAANG HARI VISTA CITY CORNER, MOLINO IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07539-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1225-016</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 1511315</x:t>
+  </x:si>
+  <x:si>
+    <x:t>256 2/F SM CENTER ANGONO MANILA EAST ROAD, SAN ISIDRO, Angono, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07536-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1223-317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit 335 SM City Lucena Maharlika Highway corner Dalahican Road, Ibabang Dupay, Lucena City (Capital), Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07468-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1208-449</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511313</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL ANGLE MARKETING INC</x:t>
   </x:si>
   <x:si>
-    <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
     <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -90,7 +144,16 @@
     <x:t>1511203</x:t>
   </x:si>
   <x:si>
-    <x:t>Cesar Allen Centeno</x:t>
+    <x:t>UG MASSWAY SHOPPING CENTER F.T Catapusan, Plaza Almeda, Tanay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07520-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1221-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511337</x:t>
   </x:si>
   <x:si>
     <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
@@ -123,12 +186,99 @@
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
+    <x:t>ADI-ASIANIC DISTRIBUTORS INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#2072 2/F SM CITY SANTA ROSA, TAGAPO, City Of Santa Rosa, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0415</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1187-091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STALL 224 2/F SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1188-853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ-018 3/F SM CITY LUCENA, IBABANG DUPAY, Lucena City (Capital), Quezon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0413</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1184-446</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STALL E-232 2/F SM CITY DASMARIÑAS, SAMPALOC I, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1183-545</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STALL 216 2/F SM CITY LIPA, MARAOUY, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1182-290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>281 2ND FLOOR SM CITY CALAMBA, REAL, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1180-596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 420 4/F SM CITY BACOOR, HABAY II, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0412</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1186-322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ-207 2/F SM CITY MASINAG, MAYAMOT, City Of Antipolo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1181-124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STALL 024 2/F SM CITY BATANGAS, PALLOCAN WEST, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1185-901</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
   </x:si>
   <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -141,9 +291,36 @@
     <x:t>1511233</x:t>
   </x:si>
   <x:si>
+    <x:t>CELLBLITZ MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLA MALL PAGSANJAN GFK-005, PAGSANJAN, City Of Biñan, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-22-010R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1190-402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511321</x:t>
+  </x:si>
+  <x:si>
     <x:t>CELLBLITZ MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>G/F ULTIMART BLDG., BRGY. III-A, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-22-003R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1098-751</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511300</x:t>
+  </x:si>
+  <x:si>
     <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -159,6 +336,30 @@
     <x:t>CELLTY MOBILE INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>ROBINSONS PLACE LIPA LEVEL 2, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-21-04-2282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1191-381</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511320</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1111-408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511278</x:t>
+  </x:si>
+  <x:si>
     <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
   </x:si>
   <x:si>
@@ -171,19 +372,16 @@
     <x:t>1511193</x:t>
   </x:si>
   <x:si>
-    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-24-451R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1111-408</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511278</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
+    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511223</x:t>
   </x:si>
   <x:si>
     <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
@@ -198,16 +396,19 @@
     <x:t>1511224</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511223</x:t>
+    <x:t>DIGITAL WALKER CORP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT R09 BLK J. THE OUTLETS, SAN LUCAS, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-466b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1200-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511311</x:t>
   </x:si>
   <x:si>
     <x:t>HLH GENTECH INC.</x:t>
@@ -225,6 +426,18 @@
     <x:t>1511246</x:t>
   </x:si>
   <x:si>
+    <x:t>CZ2114 SM City Lipa, MARAUOY, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1092-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511299</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILECRAZE TELECOM INC.</x:t>
   </x:si>
   <x:si>
@@ -255,6 +468,21 @@
     <x:t>1511271</x:t>
   </x:si>
   <x:si>
+    <x:t>PRISMATECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UG 227 ROBINSONS PLACE ANTIPOLO SUMULONG HIGHWAY, DELA PAZ, City Of Antipolo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">     DD-MP-02-25-0456R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1228-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511301</x:t>
+  </x:si>
+  <x:si>
     <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
   </x:si>
   <x:si>
@@ -270,6 +498,48 @@
     <x:t>1511195</x:t>
   </x:si>
   <x:si>
+    <x:t>S1.TECHNOLOGIES INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ12 LGF CYBERZONE SM CITY TRECE MARTIRES, S.A PROPER, San Agustin, Trece Martires City (Capital), Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-470R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1212-990</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILICON VALLEY COMPUTER GROUP PHILS. INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ 02 CYBERZONE SM CITY TRECE MARTIRES, BRGY. SAN AGUSTIN, Trece Martires City (Capital), Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-16-04-0570 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1214-289</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LS 010 G/F XENTRO MALL, CALACA HIGHWAY, BRGY. MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-16-04-0569 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1213-189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511323</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYNCNETIC INC</x:t>
   </x:si>
   <x:si>
@@ -288,6 +558,30 @@
     <x:t>SYNCNETIC INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT NO. 248 3RD FLR SM CITY DASMARIÑAS, SAMPALOC I, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 02-25- 045R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1091-601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511298</x:t>
+  </x:si>
+  <x:si>
     <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
   </x:si>
   <x:si>
@@ -300,18 +594,6 @@
     <x:t>1511213</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-02-25-0452R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1168-173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511222</x:t>
-  </x:si>
-  <x:si>
     <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
   </x:si>
   <x:si>
@@ -357,6 +639,30 @@
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
+    <x:t>ROBINSONS GALLERIA SOUTH LEVEL 4 401, NUEVA, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06685-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1167-519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>313 3RD FLR. ROBINSONS PLACE GENERAL TRIAS ANTERO SORIANO HI-WAY, TEJERO, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06683-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1166-516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511305</x:t>
+  </x:si>
+  <x:si>
     <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -393,6 +699,21 @@
     <x:t>1511226</x:t>
   </x:si>
   <x:si>
+    <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>257-G SM City Molino Molino Rd, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-3-25-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1148-415</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511150</x:t>
+  </x:si>
+  <x:si>
     <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
   </x:si>
   <x:si>
@@ -408,7 +729,37 @@
     <x:t>Service Center Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
-    <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
+    <x:t>CPH COMPUTER PARTS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Level 3 LS-K10 Robinson South Galleria KM 31 National Highway, Nueva, City Of San Pedro, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1149-406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511151</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIZMOTECH CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/f sm city batangas pastor village, pallocan west, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DDSC22091049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1227-607</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511918</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adora Mercado</x:t>
   </x:si>
   <x:si>
     <x:t>257-G SM City Molino Molino Road, Molino IV, Bacoor City, Cavite</x:t>
@@ -1283,7 +1634,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1323,7 +1674,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -1344,10 +1695,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46090.2558238542</x:v>
+        <x:v>46105.2006856829</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46090.2558400116</x:v>
+        <x:v>46105.2007036921</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>21</x:v>
@@ -1356,13 +1707,13 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46097.2890797917</x:v>
+        <x:v>46106.1315601157</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -1382,10 +1733,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46090.2418365857</x:v>
+        <x:v>46105.1989528125</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46090.2418534606</x:v>
+        <x:v>46105.1989710069</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
@@ -1394,927 +1745,2000 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46093.3049920255</x:v>
+        <x:v>46106.1359238194</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>46105.191745625</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46105.1917622685</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46090.210999456</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46090.211015162</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
+        <x:v>46106.1259714815</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46100.3466235648</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46100.34664375</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>46106.1287182292</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46090.2558238542</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46090.2558400116</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>46097.2890797917</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46104.3254651157</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46104.325483287</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46107.2521065509</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46090.2418365857</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46090.2418534606</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>46093.3049920255</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46090.210999456</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46090.211015162</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
         <x:v>46093.3080127546</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46083.2322339931</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46097.1495293519</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46069.3514850347</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46069.3573124306</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46097.2426396643</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46073.1441202083</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46100.4005466667</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
+      <x:c r="M15" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46084.2250188542</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46093.3804507639</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46090.379734213</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46084.2189288542</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46093.3723926852</x:v>
+        <x:v>46105.224634919</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="H17" s="16">
+        <x:v>46090.3851441782</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46105.22531625</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46073.1251625463</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>45619</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
+      <x:c r="H18" s="16">
+        <x:v>46090.365904456</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46105.2229815046</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>11280</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46099.1200232986</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46073.1541139005</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46099.1584012616</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="H19" s="16">
-        <x:v>46097.4788515162</x:v>
+        <x:v>46090.3537036343</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46100</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>76</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46100.2987549074</x:v>
+        <x:v>46105.2225829398</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46069.3341180556</x:v>
+        <x:v>46090.3356997569</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46094</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>81</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46097.244735544</x:v>
+        <x:v>46105.2220323264</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>84</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46084.1513040509</x:v>
+        <x:v>46090.3208883218</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46102</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>86</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46097.2494578472</x:v>
+        <x:v>46105.2211048843</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46073.1135088426</x:v>
+        <x:v>46090.3747280671</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>45751</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>91</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46097.2511403241</x:v>
+        <x:v>46105.2237759722</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46084.3311976389</x:v>
+        <x:v>46090.3276135532</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46070</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46093.3668852546</x:v>
+        <x:v>46105.2216826968</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>98</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46092.1012814815</x:v>
+        <x:v>46090.3705350231</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46100</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>100</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46097.1408234491</x:v>
+        <x:v>46105.2233433449</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>103</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46097.4214954398</x:v>
+        <x:v>46083.2322339931</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46100</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>104</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46100.2966699421</x:v>
+        <x:v>46097.1495293519</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>105</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>107</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46069.1217257292</x:v>
+        <x:v>46091.3241459028</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46157</x:v>
+        <x:v>46090</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46097.3375062153</x:v>
+        <x:v>46106.2491112732</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>112</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>113</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46084.3419451968</x:v>
+        <x:v>46069.3768614236</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46084.3419617014</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>115</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46090.3480933681</x:v>
+        <x:v>46105.312268125</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="14" t="s">
-        <x:v>117</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
-        <x:v>119</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>120</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46084.1579541898</x:v>
+        <x:v>46069.3514850347</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46145</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
-        <x:v>122</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="18">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46091.3318239931</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>45768</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46106.2406020602</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46073.1441202083</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46100.4005466667</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46069.3573124306</x:v>
+      </x:c>
+      <x:c r="I31" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="18">
+        <x:v>46097.2426396643</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46084.2189288542</x:v>
+      </x:c>
+      <x:c r="I32" s="16">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="18">
+        <x:v>46093.3723926852</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46084.2250188542</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="18">
+        <x:v>46093.3804507639</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
+        <x:v>46097.0601290857</x:v>
+      </x:c>
+      <x:c r="I34" s="16">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="J34" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="18">
+        <x:v>46106.1139344792</x:v>
+      </x:c>
+      <x:c r="M34" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
+        <x:v>46073.1251625463</x:v>
+      </x:c>
+      <x:c r="I35" s="16">
+        <x:v>45619</x:v>
+      </x:c>
+      <x:c r="J35" s="15" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="n">
+        <x:v>11280</x:v>
+      </x:c>
+      <x:c r="L35" s="18">
+        <x:v>46099.1200232986</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
+        <x:v>46069.2988094792</x:v>
+      </x:c>
+      <x:c r="I36" s="16">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J36" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L36" s="18">
+        <x:v>46105.2995247917</x:v>
+      </x:c>
+      <x:c r="M36" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
+        <x:v>46073.1541139005</x:v>
+      </x:c>
+      <x:c r="I37" s="16">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J37" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L37" s="18">
+        <x:v>46099.1584012616</x:v>
+      </x:c>
+      <x:c r="M37" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
+        <x:v>46097.4788515162</x:v>
+      </x:c>
+      <x:c r="I38" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J38" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="18">
+        <x:v>46100.2987549074</x:v>
+      </x:c>
+      <x:c r="M38" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
+        <x:v>46105.2848483681</x:v>
+      </x:c>
+      <x:c r="I39" s="16">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J39" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L39" s="18">
+        <x:v>46105.3281210069</x:v>
+      </x:c>
+      <x:c r="M39" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B40" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H40" s="16">
+        <x:v>46069.3341180556</x:v>
+      </x:c>
+      <x:c r="I40" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J40" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L40" s="18">
+        <x:v>46097.244735544</x:v>
+      </x:c>
+      <x:c r="M40" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H41" s="16">
+        <x:v>46104.077202419</x:v>
+      </x:c>
+      <x:c r="I41" s="16">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="J41" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="18">
+        <x:v>46106.2743414352</x:v>
+      </x:c>
+      <x:c r="M41" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46104.0901424306</x:v>
+      </x:c>
+      <x:c r="I42" s="16">
+        <x:v>46117</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="18">
+        <x:v>46106.2675132176</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D43" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H43" s="16">
+        <x:v>46104.0855029514</x:v>
+      </x:c>
+      <x:c r="I43" s="16">
+        <x:v>46117</x:v>
+      </x:c>
+      <x:c r="J43" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="18">
+        <x:v>46106.2705830787</x:v>
+      </x:c>
+      <x:c r="M43" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B44" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D44" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="H44" s="16">
+        <x:v>46084.1513040509</x:v>
+      </x:c>
+      <x:c r="I44" s="16">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J44" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="K44" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="18">
+        <x:v>46097.2494578472</x:v>
+      </x:c>
+      <x:c r="M44" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D45" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H45" s="16">
+        <x:v>46084.3311976389</x:v>
+      </x:c>
+      <x:c r="I45" s="16">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J45" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="K45" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L45" s="18">
+        <x:v>46093.3668852546</x:v>
+      </x:c>
+      <x:c r="M45" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D46" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H46" s="16">
+        <x:v>46069.2869081713</x:v>
+      </x:c>
+      <x:c r="I46" s="16">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J46" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="K46" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L46" s="18">
+        <x:v>46105.2599488542</x:v>
+      </x:c>
+      <x:c r="M46" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B47" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D47" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H47" s="16">
+        <x:v>46073.1135088426</x:v>
+      </x:c>
+      <x:c r="I47" s="16">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J47" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="K47" s="17" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L47" s="18">
+        <x:v>46097.2511403241</x:v>
+      </x:c>
+      <x:c r="M47" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B48" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D48" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G48" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H48" s="16">
+        <x:v>46092.1012814815</x:v>
+      </x:c>
+      <x:c r="I48" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J48" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="K48" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L48" s="18">
+        <x:v>46097.1408234491</x:v>
+      </x:c>
+      <x:c r="M48" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B49" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D49" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G49" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H49" s="16">
+        <x:v>46097.4214954398</x:v>
+      </x:c>
+      <x:c r="I49" s="16">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J49" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="K49" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L49" s="18">
+        <x:v>46100.2966699421</x:v>
+      </x:c>
+      <x:c r="M49" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D50" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H50" s="16">
+        <x:v>46069.1217257292</x:v>
+      </x:c>
+      <x:c r="I50" s="16">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J50" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="K50" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L50" s="18">
+        <x:v>46097.3375062153</x:v>
+      </x:c>
+      <x:c r="M50" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D51" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G51" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H51" s="16">
+        <x:v>46084.2548997222</x:v>
+      </x:c>
+      <x:c r="I51" s="16">
+        <x:v>46084.2549156713</x:v>
+      </x:c>
+      <x:c r="J51" s="15" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="K51" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L51" s="18">
+        <x:v>46105.4010316319</x:v>
+      </x:c>
+      <x:c r="M51" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B52" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D52" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G52" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H52" s="16">
+        <x:v>46084.2374126389</x:v>
+      </x:c>
+      <x:c r="I52" s="16">
+        <x:v>46084.2374295139</x:v>
+      </x:c>
+      <x:c r="J52" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K52" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L52" s="18">
+        <x:v>46105.4096900347</x:v>
+      </x:c>
+      <x:c r="M52" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D53" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G53" s="14" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H53" s="16">
+        <x:v>46084.3419451968</x:v>
+      </x:c>
+      <x:c r="I53" s="16">
+        <x:v>46084.3419617014</x:v>
+      </x:c>
+      <x:c r="J53" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="K53" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L53" s="18">
+        <x:v>46090.3480933681</x:v>
+      </x:c>
+      <x:c r="M53" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B54" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D54" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H54" s="16">
+        <x:v>46084.1579541898</x:v>
+      </x:c>
+      <x:c r="I54" s="16">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J54" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="K54" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L54" s="18">
         <x:v>46093.4169326042</x:v>
       </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
+      <x:c r="M54" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B55" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D55" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G55" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H55" s="16">
+        <x:v>46083.2228741435</x:v>
+      </x:c>
+      <x:c r="I55" s="16">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J55" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="K55" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L55" s="18">
+        <x:v>46111.2343215393</x:v>
+      </x:c>
+      <x:c r="M55" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B56" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D56" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G56" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H56" s="16">
         <x:v>46084.1627466204</x:v>
       </x:c>
-      <x:c r="I29" s="16">
+      <x:c r="I56" s="16">
         <x:v>46060</x:v>
       </x:c>
-      <x:c r="J29" s="15" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
+      <x:c r="J56" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="K56" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L29" s="18">
+      <x:c r="L56" s="18">
         <x:v>46100.392939537</x:v>
       </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
+      <x:c r="M56" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B57" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D57" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G57" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H57" s="16">
+        <x:v>46083.2276334028</x:v>
+      </x:c>
+      <x:c r="I57" s="16">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J57" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K57" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L57" s="18">
+        <x:v>46111.2358333681</x:v>
+      </x:c>
+      <x:c r="M57" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B58" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D58" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G58" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H58" s="16">
+        <x:v>46105.2817877199</x:v>
+      </x:c>
+      <x:c r="I58" s="16">
+        <x:v>46634</x:v>
+      </x:c>
+      <x:c r="J58" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="K58" s="17" t="n">
+        <x:v>8190</x:v>
+      </x:c>
+      <x:c r="L58" s="18">
+        <x:v>46105.3080007639</x:v>
+      </x:c>
+      <x:c r="M58" s="14" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B59" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D59" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="H59" s="16">
         <x:v>46092.9637875116</x:v>
       </x:c>
-      <x:c r="I30" s="16">
+      <x:c r="I59" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J30" s="15" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
+      <x:c r="J59" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="K59" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L30" s="18">
+      <x:c r="L59" s="18">
         <x:v>46093.3109466551</x:v>
       </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="19" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C33" s="20" t="s"/>
-      <x:c r="D33" s="20" t="s"/>
-      <x:c r="E33" s="21" t="s"/>
-      <x:c r="F33" s="21" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="22" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C34" s="23" t="s"/>
-      <x:c r="D34" s="23" t="s"/>
-      <x:c r="E34" s="23" t="s"/>
-      <x:c r="F34" s="24" t="s">
-        <x:v>135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C35" s="26" t="s"/>
-      <x:c r="D35" s="26" t="s"/>
-      <x:c r="E35" s="26" t="s"/>
-      <x:c r="F35" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="25" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C36" s="26" t="s"/>
-      <x:c r="D36" s="26" t="s"/>
-      <x:c r="E36" s="26" t="s"/>
-      <x:c r="F36" s="27" t="n">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="25" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C37" s="26" t="s"/>
-      <x:c r="D37" s="26" t="s"/>
-      <x:c r="E37" s="26" t="s"/>
-      <x:c r="F37" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="25" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C38" s="26" t="s"/>
-      <x:c r="D38" s="26" t="s"/>
-      <x:c r="E38" s="26" t="s"/>
-      <x:c r="F38" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="25" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="C39" s="26" t="s"/>
-      <x:c r="D39" s="26" t="s"/>
-      <x:c r="E39" s="26" t="s"/>
-      <x:c r="F39" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B40" s="28" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C40" s="29" t="s"/>
-      <x:c r="D40" s="29" t="s"/>
-      <x:c r="E40" s="29" t="s"/>
-      <x:c r="F40" s="30" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M59" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B62" s="19" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C62" s="20" t="s"/>
+      <x:c r="D62" s="20" t="s"/>
+      <x:c r="E62" s="21" t="s"/>
+      <x:c r="F62" s="21" t="s"/>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B63" s="22" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C63" s="23" t="s"/>
+      <x:c r="D63" s="23" t="s"/>
+      <x:c r="E63" s="23" t="s"/>
+      <x:c r="F63" s="24" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B64" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C64" s="26" t="s"/>
+      <x:c r="D64" s="26" t="s"/>
+      <x:c r="E64" s="26" t="s"/>
+      <x:c r="F64" s="27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B65" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C65" s="26" t="s"/>
+      <x:c r="D65" s="26" t="s"/>
+      <x:c r="E65" s="26" t="s"/>
+      <x:c r="F65" s="27" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="25" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C66" s="26" t="s"/>
+      <x:c r="D66" s="26" t="s"/>
+      <x:c r="E66" s="26" t="s"/>
+      <x:c r="F66" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="25" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C67" s="26" t="s"/>
+      <x:c r="D67" s="26" t="s"/>
+      <x:c r="E67" s="26" t="s"/>
+      <x:c r="F67" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B68" s="25" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C68" s="26" t="s"/>
+      <x:c r="D68" s="26" t="s"/>
+      <x:c r="E68" s="26" t="s"/>
+      <x:c r="F68" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B69" s="28" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="C69" s="29" t="s"/>
+      <x:c r="D69" s="29" t="s"/>
+      <x:c r="E69" s="29" t="s"/>
+      <x:c r="F69" s="30" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
     <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3245,14 +4669,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B33:F33"/>
-    <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
-    <x:mergeCell ref="B38:E38"/>
-    <x:mergeCell ref="B39:E39"/>
-    <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B62:F62"/>
+    <x:mergeCell ref="B63:E63"/>
+    <x:mergeCell ref="B64:E64"/>
+    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B66:E66"/>
+    <x:mergeCell ref="B67:E67"/>
+    <x:mergeCell ref="B68:E68"/>
+    <x:mergeCell ref="B69:E69"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -22,15 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>DENIEL GENNE PUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IV-A | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -1115,7 +1112,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1132,6 +1129,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1190,7 +1190,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1226,6 +1226,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1600,20 +1604,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1636,2106 +1640,2106 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>46105.2006856829</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46105.2007036921</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46105.2006856829</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46105.2007036921</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="18">
+      <x:c r="L8" s="19">
         <x:v>46106.1315601157</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46105.1989528125</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46105.1989710069</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46106.1359238194</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46105.1989528125</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46105.1989710069</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="E10" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="F10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46105.191745625</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46105.1917622685</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46106.1359238194</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="L10" s="19">
+        <x:v>46106.1259714815</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46105.191745625</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46105.1917622685</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="E11" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="F11" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46100.3466235648</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46100.34664375</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46106.1259714815</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="L11" s="19">
+        <x:v>46106.1287182292</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46100.3466235648</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46100.34664375</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
+      <x:c r="E12" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46090.2558238542</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46090.2558400116</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46097.2890797917</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46104.3254651157</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46104.325483287</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46106.1287182292</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46090.2558238542</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46090.2558400116</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="L13" s="19">
+        <x:v>46107.2521065509</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46090.2418365857</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46090.2418534606</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46097.2890797917</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46104.3254651157</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46104.325483287</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="L14" s="19">
+        <x:v>46093.3049920255</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46090.210999456</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46090.211015162</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46107.2521065509</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46090.2418365857</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46090.2418534606</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="L15" s="19">
+        <x:v>46093.3080127546</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46090.379734213</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46105.224634919</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46090.3851441782</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46105.22531625</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46090.365904456</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46105.2229815046</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46090.3537036343</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46105.2225829398</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46090.3356997569</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46105.2220323264</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46090.3208883218</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46105.2211048843</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46090.3747280671</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46105.2237759722</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46090.3276135532</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46105.2216826968</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46090.3705350231</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46105.2233433449</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46083.2322339931</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46097.1495293519</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46091.3241459028</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>46090</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46106.2491112732</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46069.3768614236</x:v>
+      </x:c>
+      <x:c r="I27" s="17">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46105.312268125</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46069.3514850347</x:v>
+      </x:c>
+      <x:c r="I28" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46097.2437384259</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H29" s="17">
+        <x:v>46091.3318239931</x:v>
+      </x:c>
+      <x:c r="I29" s="17">
+        <x:v>45768</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L29" s="19">
+        <x:v>46106.2406020602</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H30" s="17">
+        <x:v>46073.1441202083</x:v>
+      </x:c>
+      <x:c r="I30" s="17">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L30" s="19">
+        <x:v>46100.4005466667</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H31" s="17">
+        <x:v>46069.3573124306</x:v>
+      </x:c>
+      <x:c r="I31" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J31" s="16" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L31" s="19">
+        <x:v>46097.2426396643</x:v>
+      </x:c>
+      <x:c r="M31" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H32" s="17">
+        <x:v>46084.2189288542</x:v>
+      </x:c>
+      <x:c r="I32" s="17">
+        <x:v>46133</x:v>
+      </x:c>
+      <x:c r="J32" s="16" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="K32" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L32" s="19">
+        <x:v>46093.3723926852</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H33" s="17">
+        <x:v>46084.2250188542</x:v>
+      </x:c>
+      <x:c r="I33" s="17">
+        <x:v>46144</x:v>
+      </x:c>
+      <x:c r="J33" s="16" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L33" s="19">
+        <x:v>46093.3804507639</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H34" s="17">
+        <x:v>46097.0601290857</x:v>
+      </x:c>
+      <x:c r="I34" s="17">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="J34" s="16" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="K34" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L34" s="19">
+        <x:v>46106.1139344792</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H35" s="17">
+        <x:v>46073.1251625463</x:v>
+      </x:c>
+      <x:c r="I35" s="17">
+        <x:v>45619</x:v>
+      </x:c>
+      <x:c r="J35" s="16" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="K35" s="18" t="n">
+        <x:v>11280</x:v>
+      </x:c>
+      <x:c r="L35" s="19">
+        <x:v>46099.1200232986</x:v>
+      </x:c>
+      <x:c r="M35" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H36" s="17">
+        <x:v>46069.2988094792</x:v>
+      </x:c>
+      <x:c r="I36" s="17">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J36" s="16" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K36" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L36" s="19">
+        <x:v>46105.2995247917</x:v>
+      </x:c>
+      <x:c r="M36" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H37" s="17">
+        <x:v>46073.1541139005</x:v>
+      </x:c>
+      <x:c r="I37" s="17">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J37" s="16" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K37" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L37" s="19">
+        <x:v>46099.1584012616</x:v>
+      </x:c>
+      <x:c r="M37" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H38" s="17">
+        <x:v>46097.4788515162</x:v>
+      </x:c>
+      <x:c r="I38" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J38" s="16" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="K38" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L38" s="19">
+        <x:v>46100.2987549074</x:v>
+      </x:c>
+      <x:c r="M38" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H39" s="17">
+        <x:v>46105.2848483681</x:v>
+      </x:c>
+      <x:c r="I39" s="17">
+        <x:v>46105</x:v>
+      </x:c>
+      <x:c r="J39" s="16" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="K39" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L39" s="19">
+        <x:v>46105.3281210069</x:v>
+      </x:c>
+      <x:c r="M39" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B40" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H40" s="17">
+        <x:v>46069.3341180556</x:v>
+      </x:c>
+      <x:c r="I40" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J40" s="16" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="K40" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L40" s="19">
+        <x:v>46097.244735544</x:v>
+      </x:c>
+      <x:c r="M40" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H41" s="17">
+        <x:v>46104.077202419</x:v>
+      </x:c>
+      <x:c r="I41" s="17">
+        <x:v>46106</x:v>
+      </x:c>
+      <x:c r="J41" s="16" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="K41" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L41" s="19">
+        <x:v>46106.2743414352</x:v>
+      </x:c>
+      <x:c r="M41" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B42" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G42" s="15" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H42" s="17">
+        <x:v>46104.0901424306</x:v>
+      </x:c>
+      <x:c r="I42" s="17">
+        <x:v>46117</x:v>
+      </x:c>
+      <x:c r="J42" s="16" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="K42" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L42" s="19">
+        <x:v>46106.2675132176</x:v>
+      </x:c>
+      <x:c r="M42" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E43" s="15" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F43" s="15" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G43" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H43" s="17">
+        <x:v>46104.0855029514</x:v>
+      </x:c>
+      <x:c r="I43" s="17">
+        <x:v>46117</x:v>
+      </x:c>
+      <x:c r="J43" s="16" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="K43" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L43" s="19">
+        <x:v>46106.2705830787</x:v>
+      </x:c>
+      <x:c r="M43" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B44" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E44" s="15" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F44" s="15" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G44" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H44" s="17">
+        <x:v>46084.1513040509</x:v>
+      </x:c>
+      <x:c r="I44" s="17">
+        <x:v>46102</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="K44" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L44" s="19">
+        <x:v>46097.2494578472</x:v>
+      </x:c>
+      <x:c r="M44" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C45" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E45" s="15" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F45" s="15" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G45" s="15" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H45" s="17">
+        <x:v>46084.3311976389</x:v>
+      </x:c>
+      <x:c r="I45" s="17">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J45" s="16" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="K45" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L45" s="19">
+        <x:v>46093.3668852546</x:v>
+      </x:c>
+      <x:c r="M45" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C46" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E46" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F46" s="15" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G46" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H46" s="17">
+        <x:v>46069.2869081713</x:v>
+      </x:c>
+      <x:c r="I46" s="17">
+        <x:v>46070</x:v>
+      </x:c>
+      <x:c r="J46" s="16" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="K46" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L46" s="19">
+        <x:v>46105.2599488542</x:v>
+      </x:c>
+      <x:c r="M46" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B47" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C47" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E47" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F47" s="15" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G47" s="15" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H47" s="17">
+        <x:v>46073.1135088426</x:v>
+      </x:c>
+      <x:c r="I47" s="17">
+        <x:v>45751</x:v>
+      </x:c>
+      <x:c r="J47" s="16" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="K47" s="18" t="n">
+        <x:v>7530</x:v>
+      </x:c>
+      <x:c r="L47" s="19">
+        <x:v>46097.2511403241</x:v>
+      </x:c>
+      <x:c r="M47" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B48" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C48" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E48" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F48" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G48" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H48" s="17">
+        <x:v>46092.1012814815</x:v>
+      </x:c>
+      <x:c r="I48" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J48" s="16" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="K48" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L48" s="19">
+        <x:v>46097.1408234491</x:v>
+      </x:c>
+      <x:c r="M48" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B49" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C49" s="15" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E49" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F49" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G49" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H49" s="17">
+        <x:v>46097.4214954398</x:v>
+      </x:c>
+      <x:c r="I49" s="17">
+        <x:v>46100</x:v>
+      </x:c>
+      <x:c r="J49" s="16" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="K49" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L49" s="19">
+        <x:v>46100.2966699421</x:v>
+      </x:c>
+      <x:c r="M49" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C50" s="15" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D50" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E50" s="15" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F50" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G50" s="15" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H50" s="17">
+        <x:v>46069.1217257292</x:v>
+      </x:c>
+      <x:c r="I50" s="17">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="J50" s="16" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="K50" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L50" s="19">
+        <x:v>46097.3375062153</x:v>
+      </x:c>
+      <x:c r="M50" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C51" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D51" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E51" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F51" s="15" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G51" s="15" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H51" s="17">
+        <x:v>46084.2548997222</x:v>
+      </x:c>
+      <x:c r="I51" s="17">
+        <x:v>46084.2549156713</x:v>
+      </x:c>
+      <x:c r="J51" s="16" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="K51" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46093.3049920255</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46090.210999456</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46090.211015162</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="L51" s="19">
+        <x:v>46105.4010316319</x:v>
+      </x:c>
+      <x:c r="M51" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B52" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C52" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D52" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E52" s="15" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F52" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G52" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H52" s="17">
+        <x:v>46084.2374126389</x:v>
+      </x:c>
+      <x:c r="I52" s="17">
+        <x:v>46084.2374295139</x:v>
+      </x:c>
+      <x:c r="J52" s="16" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="K52" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46093.3080127546</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="L52" s="19">
+        <x:v>46105.4096900347</x:v>
+      </x:c>
+      <x:c r="M52" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="15" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C53" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D53" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E53" s="15" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F53" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G53" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H53" s="17">
+        <x:v>46084.3419451968</x:v>
+      </x:c>
+      <x:c r="I53" s="17">
+        <x:v>46084.3419617014</x:v>
+      </x:c>
+      <x:c r="J53" s="16" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="K53" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L53" s="19">
+        <x:v>46090.3480933681</x:v>
+      </x:c>
+      <x:c r="M53" s="15" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B54" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C54" s="15" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D54" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46090.379734213</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="E54" s="15" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F54" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G54" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H54" s="17">
+        <x:v>46084.1579541898</x:v>
+      </x:c>
+      <x:c r="I54" s="17">
+        <x:v>46145</x:v>
+      </x:c>
+      <x:c r="J54" s="16" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="K54" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46105.224634919</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="L54" s="19">
+        <x:v>46093.4169326042</x:v>
+      </x:c>
+      <x:c r="M54" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B55" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C55" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D55" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46090.3851441782</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="E55" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F55" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G55" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H55" s="17">
+        <x:v>46083.2228741435</x:v>
+      </x:c>
+      <x:c r="I55" s="17">
+        <x:v>46083</x:v>
+      </x:c>
+      <x:c r="J55" s="16" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="K55" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46105.22531625</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="L55" s="19">
+        <x:v>46111.2343215393</x:v>
+      </x:c>
+      <x:c r="M55" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B56" s="15" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C56" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D56" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46090.365904456</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46105.2229815046</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
+      <x:c r="E56" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F56" s="15" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G56" s="15" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H56" s="17">
+        <x:v>46084.1627466204</x:v>
+      </x:c>
+      <x:c r="I56" s="17">
+        <x:v>46060</x:v>
+      </x:c>
+      <x:c r="J56" s="16" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="K56" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L56" s="19">
+        <x:v>46100.392939537</x:v>
+      </x:c>
+      <x:c r="M56" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B57" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C57" s="15" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D57" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46090.3537036343</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46105.2225829398</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
+      <x:c r="E57" s="15" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F57" s="15" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G57" s="15" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="H57" s="17">
+        <x:v>46083.2276334028</x:v>
+      </x:c>
+      <x:c r="I57" s="17">
+        <x:v>46094</x:v>
+      </x:c>
+      <x:c r="J57" s="16" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="K57" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L57" s="19">
+        <x:v>46111.2358333681</x:v>
+      </x:c>
+      <x:c r="M57" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B58" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C58" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D58" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46090.3356997569</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46105.2220323264</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
+      <x:c r="E58" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F58" s="15" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G58" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H58" s="17">
+        <x:v>46105.2817877199</x:v>
+      </x:c>
+      <x:c r="I58" s="17">
+        <x:v>46634</x:v>
+      </x:c>
+      <x:c r="J58" s="16" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="K58" s="18" t="n">
+        <x:v>8190</x:v>
+      </x:c>
+      <x:c r="L58" s="19">
+        <x:v>46105.3080007639</x:v>
+      </x:c>
+      <x:c r="M58" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B59" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C59" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D59" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46090.3208883218</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46105.2211048843</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46090.3747280671</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46105.2237759722</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46090.3276135532</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46105.2216826968</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46090.3705350231</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46105.2233433449</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46083.2322339931</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46097.1495293519</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46091.3241459028</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46090</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46106.2491112732</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46069.3768614236</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46105.312268125</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46069.3514850347</x:v>
-      </x:c>
-      <x:c r="I28" s="16">
+      <x:c r="E59" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F59" s="15" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G59" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H59" s="17">
+        <x:v>46092.9637875116</x:v>
+      </x:c>
+      <x:c r="I59" s="17">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J28" s="15" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46097.2437384259</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46091.3318239931</x:v>
-      </x:c>
-      <x:c r="I29" s="16">
-        <x:v>45768</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46106.2406020602</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46073.1441202083</x:v>
-      </x:c>
-      <x:c r="I30" s="16">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
-        <x:v>46100.4005466667</x:v>
-      </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
-        <x:v>46069.3573124306</x:v>
-      </x:c>
-      <x:c r="I31" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J31" s="15" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="K31" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L31" s="18">
-        <x:v>46097.2426396643</x:v>
-      </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
-        <x:v>46084.2189288542</x:v>
-      </x:c>
-      <x:c r="I32" s="16">
-        <x:v>46133</x:v>
-      </x:c>
-      <x:c r="J32" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="K32" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L32" s="18">
-        <x:v>46093.3723926852</x:v>
-      </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46084.2250188542</x:v>
-      </x:c>
-      <x:c r="I33" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="K33" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L33" s="18">
-        <x:v>46093.3804507639</x:v>
-      </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E34" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
-        <x:v>46097.0601290857</x:v>
-      </x:c>
-      <x:c r="I34" s="16">
-        <x:v>46109</x:v>
-      </x:c>
-      <x:c r="J34" s="15" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="K34" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L34" s="18">
-        <x:v>46106.1139344792</x:v>
-      </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E35" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
-        <x:v>46073.1251625463</x:v>
-      </x:c>
-      <x:c r="I35" s="16">
-        <x:v>45619</x:v>
-      </x:c>
-      <x:c r="J35" s="15" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="K35" s="17" t="n">
-        <x:v>11280</x:v>
-      </x:c>
-      <x:c r="L35" s="18">
-        <x:v>46099.1200232986</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
-        <x:v>46069.2988094792</x:v>
-      </x:c>
-      <x:c r="I36" s="16">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J36" s="15" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="K36" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L36" s="18">
-        <x:v>46105.2995247917</x:v>
-      </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
-        <x:v>46073.1541139005</x:v>
-      </x:c>
-      <x:c r="I37" s="16">
-        <x:v>46030</x:v>
-      </x:c>
-      <x:c r="J37" s="15" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="K37" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L37" s="18">
-        <x:v>46099.1584012616</x:v>
-      </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
-        <x:v>46097.4788515162</x:v>
-      </x:c>
-      <x:c r="I38" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J38" s="15" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="K38" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L38" s="18">
-        <x:v>46100.2987549074</x:v>
-      </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
-        <x:v>46105.2848483681</x:v>
-      </x:c>
-      <x:c r="I39" s="16">
-        <x:v>46105</x:v>
-      </x:c>
-      <x:c r="J39" s="15" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="K39" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L39" s="18">
-        <x:v>46105.3281210069</x:v>
-      </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D40" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E40" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F40" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G40" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H40" s="16">
-        <x:v>46069.3341180556</x:v>
-      </x:c>
-      <x:c r="I40" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J40" s="15" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="K40" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L40" s="18">
-        <x:v>46097.244735544</x:v>
-      </x:c>
-      <x:c r="M40" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C41" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D41" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E41" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G41" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H41" s="16">
-        <x:v>46104.077202419</x:v>
-      </x:c>
-      <x:c r="I41" s="16">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="J41" s="15" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="K41" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L41" s="18">
-        <x:v>46106.2743414352</x:v>
-      </x:c>
-      <x:c r="M41" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C42" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D42" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E42" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G42" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H42" s="16">
-        <x:v>46104.0901424306</x:v>
-      </x:c>
-      <x:c r="I42" s="16">
-        <x:v>46117</x:v>
-      </x:c>
-      <x:c r="J42" s="15" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="K42" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L42" s="18">
-        <x:v>46106.2675132176</x:v>
-      </x:c>
-      <x:c r="M42" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C43" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D43" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E43" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F43" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G43" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H43" s="16">
-        <x:v>46104.0855029514</x:v>
-      </x:c>
-      <x:c r="I43" s="16">
-        <x:v>46117</x:v>
-      </x:c>
-      <x:c r="J43" s="15" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="K43" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L43" s="18">
-        <x:v>46106.2705830787</x:v>
-      </x:c>
-      <x:c r="M43" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C44" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D44" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E44" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F44" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="G44" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H44" s="16">
-        <x:v>46084.1513040509</x:v>
-      </x:c>
-      <x:c r="I44" s="16">
-        <x:v>46102</x:v>
-      </x:c>
-      <x:c r="J44" s="15" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="K44" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L44" s="18">
-        <x:v>46097.2494578472</x:v>
-      </x:c>
-      <x:c r="M44" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C45" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D45" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E45" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="F45" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="G45" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H45" s="16">
-        <x:v>46084.3311976389</x:v>
-      </x:c>
-      <x:c r="I45" s="16">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J45" s="15" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="K45" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L45" s="18">
-        <x:v>46093.3668852546</x:v>
-      </x:c>
-      <x:c r="M45" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C46" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D46" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E46" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F46" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G46" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H46" s="16">
-        <x:v>46069.2869081713</x:v>
-      </x:c>
-      <x:c r="I46" s="16">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="J46" s="15" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="K46" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L46" s="18">
-        <x:v>46105.2599488542</x:v>
-      </x:c>
-      <x:c r="M46" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C47" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D47" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E47" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F47" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G47" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H47" s="16">
-        <x:v>46073.1135088426</x:v>
-      </x:c>
-      <x:c r="I47" s="16">
-        <x:v>45751</x:v>
-      </x:c>
-      <x:c r="J47" s="15" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="K47" s="17" t="n">
-        <x:v>7530</x:v>
-      </x:c>
-      <x:c r="L47" s="18">
-        <x:v>46097.2511403241</x:v>
-      </x:c>
-      <x:c r="M47" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C48" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D48" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E48" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F48" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G48" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H48" s="16">
-        <x:v>46092.1012814815</x:v>
-      </x:c>
-      <x:c r="I48" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J48" s="15" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="K48" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L48" s="18">
-        <x:v>46097.1408234491</x:v>
-      </x:c>
-      <x:c r="M48" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B49" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C49" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D49" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E49" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F49" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G49" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H49" s="16">
-        <x:v>46097.4214954398</x:v>
-      </x:c>
-      <x:c r="I49" s="16">
-        <x:v>46100</x:v>
-      </x:c>
-      <x:c r="J49" s="15" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="K49" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L49" s="18">
-        <x:v>46100.2966699421</x:v>
-      </x:c>
-      <x:c r="M49" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C50" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="D50" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E50" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F50" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G50" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H50" s="16">
-        <x:v>46069.1217257292</x:v>
-      </x:c>
-      <x:c r="I50" s="16">
-        <x:v>46157</x:v>
-      </x:c>
-      <x:c r="J50" s="15" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="K50" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L50" s="18">
-        <x:v>46097.3375062153</x:v>
-      </x:c>
-      <x:c r="M50" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="C51" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D51" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E51" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="F51" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="G51" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="H51" s="16">
-        <x:v>46084.2548997222</x:v>
-      </x:c>
-      <x:c r="I51" s="16">
-        <x:v>46084.2549156713</x:v>
-      </x:c>
-      <x:c r="J51" s="15" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="K51" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L51" s="18">
-        <x:v>46105.4010316319</x:v>
-      </x:c>
-      <x:c r="M51" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B52" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="C52" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D52" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E52" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F52" s="14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G52" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H52" s="16">
-        <x:v>46084.2374126389</x:v>
-      </x:c>
-      <x:c r="I52" s="16">
-        <x:v>46084.2374295139</x:v>
-      </x:c>
-      <x:c r="J52" s="15" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="K52" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L52" s="18">
-        <x:v>46105.4096900347</x:v>
-      </x:c>
-      <x:c r="M52" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="C53" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D53" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E53" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F53" s="14" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G53" s="14" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H53" s="16">
-        <x:v>46084.3419451968</x:v>
-      </x:c>
-      <x:c r="I53" s="16">
-        <x:v>46084.3419617014</x:v>
-      </x:c>
-      <x:c r="J53" s="15" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="K53" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L53" s="18">
-        <x:v>46090.3480933681</x:v>
-      </x:c>
-      <x:c r="M53" s="14" t="s">
-        <x:v>218</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="C54" s="14" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="D54" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E54" s="14" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F54" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G54" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H54" s="16">
-        <x:v>46084.1579541898</x:v>
-      </x:c>
-      <x:c r="I54" s="16">
-        <x:v>46145</x:v>
-      </x:c>
-      <x:c r="J54" s="15" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="K54" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L54" s="18">
-        <x:v>46093.4169326042</x:v>
-      </x:c>
-      <x:c r="M54" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B55" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="C55" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D55" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E55" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F55" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G55" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H55" s="16">
-        <x:v>46083.2228741435</x:v>
-      </x:c>
-      <x:c r="I55" s="16">
-        <x:v>46083</x:v>
-      </x:c>
-      <x:c r="J55" s="15" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="K55" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L55" s="18">
-        <x:v>46111.2343215393</x:v>
-      </x:c>
-      <x:c r="M55" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B56" s="14" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="C56" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D56" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E56" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F56" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G56" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H56" s="16">
-        <x:v>46084.1627466204</x:v>
-      </x:c>
-      <x:c r="I56" s="16">
-        <x:v>46060</x:v>
-      </x:c>
-      <x:c r="J56" s="15" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="K56" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L56" s="18">
-        <x:v>46100.392939537</x:v>
-      </x:c>
-      <x:c r="M56" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B57" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C57" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="D57" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E57" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="F57" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G57" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="H57" s="16">
-        <x:v>46083.2276334028</x:v>
-      </x:c>
-      <x:c r="I57" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J57" s="15" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="K57" s="17" t="n">
+      <x:c r="J59" s="16" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="K59" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L57" s="18">
-        <x:v>46111.2358333681</x:v>
-      </x:c>
-      <x:c r="M57" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B58" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C58" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="D58" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E58" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F58" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G58" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H58" s="16">
-        <x:v>46105.2817877199</x:v>
-      </x:c>
-      <x:c r="I58" s="16">
-        <x:v>46634</x:v>
-      </x:c>
-      <x:c r="J58" s="15" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="K58" s="17" t="n">
-        <x:v>8190</x:v>
-      </x:c>
-      <x:c r="L58" s="18">
-        <x:v>46105.3080007639</x:v>
-      </x:c>
-      <x:c r="M58" s="14" t="s">
-        <x:v>245</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B59" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C59" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D59" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E59" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="F59" s="14" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="G59" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="H59" s="16">
-        <x:v>46092.9637875116</x:v>
-      </x:c>
-      <x:c r="I59" s="16">
-        <x:v>46094</x:v>
-      </x:c>
-      <x:c r="J59" s="15" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="K59" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L59" s="18">
+      <x:c r="L59" s="19">
         <x:v>46093.3109466551</x:v>
       </x:c>
-      <x:c r="M59" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M59" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B62" s="19" t="s">
+      <x:c r="B62" s="20" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C62" s="21" t="s"/>
+      <x:c r="D62" s="21" t="s"/>
+      <x:c r="E62" s="22" t="s"/>
+      <x:c r="F62" s="22" t="s"/>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B63" s="23" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C62" s="20" t="s"/>
-      <x:c r="D62" s="20" t="s"/>
-      <x:c r="E62" s="21" t="s"/>
-      <x:c r="F62" s="21" t="s"/>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B63" s="22" t="s">
+      <x:c r="C63" s="24" t="s"/>
+      <x:c r="D63" s="24" t="s"/>
+      <x:c r="E63" s="24" t="s"/>
+      <x:c r="F63" s="25" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="C63" s="23" t="s"/>
-      <x:c r="D63" s="23" t="s"/>
-      <x:c r="E63" s="23" t="s"/>
-      <x:c r="F63" s="24" t="s">
+    </x:row>
+    <x:row r="64" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B64" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C64" s="27" t="s"/>
+      <x:c r="D64" s="27" t="s"/>
+      <x:c r="E64" s="27" t="s"/>
+      <x:c r="F64" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B65" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C65" s="27" t="s"/>
+      <x:c r="D65" s="27" t="s"/>
+      <x:c r="E65" s="27" t="s"/>
+      <x:c r="F65" s="28" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="26" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C66" s="27" t="s"/>
+      <x:c r="D66" s="27" t="s"/>
+      <x:c r="E66" s="27" t="s"/>
+      <x:c r="F66" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="26" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C67" s="27" t="s"/>
+      <x:c r="D67" s="27" t="s"/>
+      <x:c r="E67" s="27" t="s"/>
+      <x:c r="F67" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B68" s="26" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C68" s="27" t="s"/>
+      <x:c r="D68" s="27" t="s"/>
+      <x:c r="E68" s="27" t="s"/>
+      <x:c r="F68" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B69" s="29" t="s">
         <x:v>252</x:v>
       </x:c>
-    </x:row>
-    <x:row r="64" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B64" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C64" s="26" t="s"/>
-      <x:c r="D64" s="26" t="s"/>
-      <x:c r="E64" s="26" t="s"/>
-      <x:c r="F64" s="27" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B65" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C65" s="26" t="s"/>
-      <x:c r="D65" s="26" t="s"/>
-      <x:c r="E65" s="26" t="s"/>
-      <x:c r="F65" s="27" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="25" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="C66" s="26" t="s"/>
-      <x:c r="D66" s="26" t="s"/>
-      <x:c r="E66" s="26" t="s"/>
-      <x:c r="F66" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="25" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="C67" s="26" t="s"/>
-      <x:c r="D67" s="26" t="s"/>
-      <x:c r="E67" s="26" t="s"/>
-      <x:c r="F67" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B68" s="25" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C68" s="26" t="s"/>
-      <x:c r="D68" s="26" t="s"/>
-      <x:c r="E68" s="26" t="s"/>
-      <x:c r="F68" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B69" s="28" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="C69" s="29" t="s"/>
-      <x:c r="D69" s="29" t="s"/>
-      <x:c r="E69" s="29" t="s"/>
-      <x:c r="F69" s="30" t="n">
+      <x:c r="C69" s="30" t="s"/>
+      <x:c r="D69" s="30" t="s"/>
+      <x:c r="E69" s="30" t="s"/>
+      <x:c r="F69" s="31" t="n">
         <x:v>52</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -7,6 +7,7 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="March 2026" sheetId="7" r:id="rId7"/>
+    <x:sheet name="April 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -781,6 +782,30 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYBERZONE UGF SM CITY DASMARIÑAS EK 207A, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-23-002R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1110-411</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511393</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GFA29 CENTRAL MALL, SALITRAN II, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-009R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1088-572</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511394</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4695,4 +4720,1297 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46073.1304932986</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46034</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46119.2877239352</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46069.272014213</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46119.2995831134</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>251</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="29" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -784,6 +784,18 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>AYALA MALLS SERIN SILANG, JUNCTION EAST, Tagaytay City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-05-0455-23R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1248-431</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511443</x:t>
+  </x:si>
+  <x:si>
     <x:t>CYBERZONE UGF SM CITY DASMARIÑAS EK 207A, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
@@ -806,6 +818,33 @@
   </x:si>
   <x:si>
     <x:t>1511394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XOCUS BELL TECH MERCHANDISING INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 19 L2 2F BIGBEN COMPLEX AYALA HIGHWAY, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-25-02-1095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1276-984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530679</x:t>
+  </x:si>
+  <x:si>
+    <x:t>unit 5 2nd floor, Adenson Bldg. 3 national highway, Parian, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-25-03-1096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1275-362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530678</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4911,19 +4950,19 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46073.1304932986</x:v>
+        <x:v>46112.3105175116</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46034</x:v>
+        <x:v>46171</x:v>
       </x:c>
       <x:c r="J8" s="16" t="s">
         <x:v>256</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46119.2877239352</x:v>
+        <x:v>46128.1580781366</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
@@ -4934,7 +4973,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>176</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
         <x:v>54</x:v>
@@ -4949,10 +4988,10 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46069.272014213</x:v>
+        <x:v>46073.1304932986</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46067</x:v>
+        <x:v>46034</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
         <x:v>260</x:v>
@@ -4961,60 +5000,181 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46119.2877239352</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46069.272014213</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46119.2995831134</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46128.2227381019</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46072</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46128.3098665394</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46128.1990794213</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46128.3062135532</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="20" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>251</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="29" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5990,15 +6150,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -806,6 +806,18 @@
   </x:si>
   <x:si>
     <x:t>1511393</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 008 G/F WALTERMART BACOOR WALTERMART BACOOR BLVD., MAMBOG IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 06-25-0463R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1253-931</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511450</x:t>
   </x:si>
   <x:si>
     <x:t>GFA29 CENTRAL MALL, SALITRAN II, City Of Dasmariñas, Cavite</x:t>
@@ -5011,7 +5023,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>176</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>54</x:v>
@@ -5026,19 +5038,19 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46069.272014213</x:v>
+        <x:v>46112.337306331</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>46067</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="J10" s="16" t="s">
         <x:v>264</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46128.3625958333</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>21</x:v>
@@ -5046,40 +5058,40 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="15" t="s">
-        <x:v>233</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="H11" s="17">
+        <x:v>46069.272014213</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="H11" s="17">
-        <x:v>46128.2227381019</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46072</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="s">
-        <x:v>269</x:v>
-      </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>2550</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46119.2995831134</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
-        <x:v>244</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
@@ -5087,7 +5099,7 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>54</x:v>
@@ -5102,10 +5114,10 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46128.1990794213</x:v>
+        <x:v>46128.2227381019</x:v>
       </x:c>
       <x:c r="I12" s="17">
-        <x:v>46092</x:v>
+        <x:v>46072</x:v>
       </x:c>
       <x:c r="J12" s="16" t="s">
         <x:v>273</x:v>
@@ -5114,68 +5126,105 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46128.3062135532</x:v>
+        <x:v>46128.3098665394</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46128.1990794213</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46128.3062135532</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="20" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>251</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="26" t="s">
-        <x:v>233</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="27" t="s"/>
       <x:c r="D18" s="27" t="s"/>
       <x:c r="E18" s="27" t="s"/>
       <x:c r="F18" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="29" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6155,11 +6204,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -868,7 +868,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -908,14 +908,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1188,7 +1180,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1199,16 +1191,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1220,53 +1209,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1301,87 +1290,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1683,17 +1668,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1716,2106 +1701,2106 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46105.2006856829</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46105.2007036921</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46106.1315601157</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46105.1989528125</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46105.1989710069</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46106.1359238194</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46105.191745625</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46105.1917622685</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46106.1259714815</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46100.3466235648</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46100.34664375</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46106.1287182292</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46090.2558238542</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46090.2558400116</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46097.2890797917</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46104.3254651157</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46104.325483287</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46107.2521065509</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46090.2418365857</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46090.2418534606</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46093.3049920255</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46090.210999456</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46090.211015162</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46093.3080127546</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46090.379734213</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46105.224634919</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46090.3851441782</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46105.22531625</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46090.365904456</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46105.2229815046</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46090.3537036343</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46105.2225829398</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46090.3356997569</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46105.2220323264</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46090.3208883218</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46105.2211048843</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46090.3747280671</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46105.2237759722</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>46090.3276135532</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>46105.2216826968</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>46090.3705350231</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>46107</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>46105.2233433449</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="15" t="s">
+      <x:c r="B25" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="s">
+      <x:c r="C25" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="s">
+      <x:c r="D25" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="s">
+      <x:c r="E25" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="s">
+      <x:c r="F25" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G25" s="15" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="H25" s="17">
+      <x:c r="H25" s="16">
         <x:v>46083.2322339931</x:v>
       </x:c>
-      <x:c r="I25" s="17">
+      <x:c r="I25" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="s">
+      <x:c r="J25" s="15" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="K25" s="18" t="n">
+      <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="18">
         <x:v>46097.1495293519</x:v>
       </x:c>
-      <x:c r="M25" s="15" t="s">
+      <x:c r="M25" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="15" t="s">
+      <x:c r="B26" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="s">
+      <x:c r="C26" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="s">
+      <x:c r="D26" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="s">
+      <x:c r="E26" s="14" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="s">
+      <x:c r="F26" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G26" s="15" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="H26" s="17">
+      <x:c r="H26" s="16">
         <x:v>46091.3241459028</x:v>
       </x:c>
-      <x:c r="I26" s="17">
+      <x:c r="I26" s="16">
         <x:v>46090</x:v>
       </x:c>
-      <x:c r="J26" s="16" t="s">
+      <x:c r="J26" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="K26" s="18" t="n">
+      <x:c r="K26" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L26" s="19">
+      <x:c r="L26" s="18">
         <x:v>46106.2491112732</x:v>
       </x:c>
-      <x:c r="M26" s="15" t="s">
+      <x:c r="M26" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="15" t="s">
+      <x:c r="B27" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="s">
+      <x:c r="C27" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D27" s="16" t="s">
+      <x:c r="D27" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="s">
+      <x:c r="E27" s="14" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="s">
+      <x:c r="F27" s="14" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G27" s="15" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="H27" s="17">
+      <x:c r="H27" s="16">
         <x:v>46069.3768614236</x:v>
       </x:c>
-      <x:c r="I27" s="17">
+      <x:c r="I27" s="16">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J27" s="16" t="s">
+      <x:c r="J27" s="15" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="K27" s="18" t="n">
+      <x:c r="K27" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L27" s="19">
+      <x:c r="L27" s="18">
         <x:v>46105.312268125</x:v>
       </x:c>
-      <x:c r="M27" s="15" t="s">
+      <x:c r="M27" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="15" t="s">
+      <x:c r="B28" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="s">
+      <x:c r="C28" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D28" s="16" t="s">
+      <x:c r="D28" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="s">
+      <x:c r="E28" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="s">
+      <x:c r="F28" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G28" s="15" t="s">
+      <x:c r="G28" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H28" s="17">
+      <x:c r="H28" s="16">
         <x:v>46069.3514850347</x:v>
       </x:c>
-      <x:c r="I28" s="17">
+      <x:c r="I28" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J28" s="16" t="s">
+      <x:c r="J28" s="15" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="K28" s="18" t="n">
+      <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L28" s="19">
+      <x:c r="L28" s="18">
         <x:v>46097.2437384259</x:v>
       </x:c>
-      <x:c r="M28" s="15" t="s">
+      <x:c r="M28" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="15" t="s">
+      <x:c r="B29" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="s">
+      <x:c r="C29" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D29" s="16" t="s">
+      <x:c r="D29" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="s">
+      <x:c r="E29" s="14" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="s">
+      <x:c r="F29" s="14" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G29" s="15" t="s">
+      <x:c r="G29" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H29" s="17">
+      <x:c r="H29" s="16">
         <x:v>46091.3318239931</x:v>
       </x:c>
-      <x:c r="I29" s="17">
+      <x:c r="I29" s="16">
         <x:v>45768</x:v>
       </x:c>
-      <x:c r="J29" s="16" t="s">
+      <x:c r="J29" s="15" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="K29" s="18" t="n">
+      <x:c r="K29" s="17" t="n">
         <x:v>7530</x:v>
       </x:c>
-      <x:c r="L29" s="19">
+      <x:c r="L29" s="18">
         <x:v>46106.2406020602</x:v>
       </x:c>
-      <x:c r="M29" s="15" t="s">
+      <x:c r="M29" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="15" t="s">
+      <x:c r="B30" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="s">
+      <x:c r="C30" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D30" s="16" t="s">
+      <x:c r="D30" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="s">
+      <x:c r="E30" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="s">
+      <x:c r="F30" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G30" s="15" t="s">
+      <x:c r="G30" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H30" s="17">
+      <x:c r="H30" s="16">
         <x:v>46073.1441202083</x:v>
       </x:c>
-      <x:c r="I30" s="17">
+      <x:c r="I30" s="16">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J30" s="16" t="s">
+      <x:c r="J30" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="K30" s="18" t="n">
+      <x:c r="K30" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L30" s="19">
+      <x:c r="L30" s="18">
         <x:v>46100.4005466667</x:v>
       </x:c>
-      <x:c r="M30" s="15" t="s">
+      <x:c r="M30" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="15" t="s">
+      <x:c r="B31" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="s">
+      <x:c r="C31" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D31" s="16" t="s">
+      <x:c r="D31" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="s">
+      <x:c r="E31" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="s">
+      <x:c r="F31" s="14" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G31" s="15" t="s">
+      <x:c r="G31" s="14" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H31" s="17">
+      <x:c r="H31" s="16">
         <x:v>46069.3573124306</x:v>
       </x:c>
-      <x:c r="I31" s="17">
+      <x:c r="I31" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J31" s="16" t="s">
+      <x:c r="J31" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="K31" s="18" t="n">
+      <x:c r="K31" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L31" s="19">
+      <x:c r="L31" s="18">
         <x:v>46097.2426396643</x:v>
       </x:c>
-      <x:c r="M31" s="15" t="s">
+      <x:c r="M31" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="15" t="s">
+      <x:c r="B32" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="s">
+      <x:c r="C32" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D32" s="16" t="s">
+      <x:c r="D32" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="s">
+      <x:c r="E32" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="s">
+      <x:c r="F32" s="14" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G32" s="15" t="s">
+      <x:c r="G32" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H32" s="17">
+      <x:c r="H32" s="16">
         <x:v>46084.2189288542</x:v>
       </x:c>
-      <x:c r="I32" s="17">
+      <x:c r="I32" s="16">
         <x:v>46133</x:v>
       </x:c>
-      <x:c r="J32" s="16" t="s">
+      <x:c r="J32" s="15" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="K32" s="18" t="n">
+      <x:c r="K32" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L32" s="19">
+      <x:c r="L32" s="18">
         <x:v>46093.3723926852</x:v>
       </x:c>
-      <x:c r="M32" s="15" t="s">
+      <x:c r="M32" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="15" t="s">
+      <x:c r="B33" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="s">
+      <x:c r="C33" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D33" s="16" t="s">
+      <x:c r="D33" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="s">
+      <x:c r="E33" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="s">
+      <x:c r="F33" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G33" s="15" t="s">
+      <x:c r="G33" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="H33" s="17">
+      <x:c r="H33" s="16">
         <x:v>46084.2250188542</x:v>
       </x:c>
-      <x:c r="I33" s="17">
+      <x:c r="I33" s="16">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="J33" s="16" t="s">
+      <x:c r="J33" s="15" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="K33" s="18" t="n">
+      <x:c r="K33" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L33" s="19">
+      <x:c r="L33" s="18">
         <x:v>46093.3804507639</x:v>
       </x:c>
-      <x:c r="M33" s="15" t="s">
+      <x:c r="M33" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="15" t="s">
+      <x:c r="B34" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="s">
+      <x:c r="C34" s="14" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D34" s="16" t="s">
+      <x:c r="D34" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="s">
+      <x:c r="E34" s="14" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="s">
+      <x:c r="F34" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G34" s="15" t="s">
+      <x:c r="G34" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="H34" s="17">
+      <x:c r="H34" s="16">
         <x:v>46097.0601290857</x:v>
       </x:c>
-      <x:c r="I34" s="17">
+      <x:c r="I34" s="16">
         <x:v>46109</x:v>
       </x:c>
-      <x:c r="J34" s="16" t="s">
+      <x:c r="J34" s="15" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="K34" s="18" t="n">
+      <x:c r="K34" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L34" s="19">
+      <x:c r="L34" s="18">
         <x:v>46106.1139344792</x:v>
       </x:c>
-      <x:c r="M34" s="15" t="s">
+      <x:c r="M34" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="15" t="s">
+      <x:c r="B35" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="s">
+      <x:c r="C35" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D35" s="16" t="s">
+      <x:c r="D35" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="s">
+      <x:c r="E35" s="14" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="s">
+      <x:c r="F35" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="G35" s="15" t="s">
+      <x:c r="G35" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="H35" s="17">
+      <x:c r="H35" s="16">
         <x:v>46073.1251625463</x:v>
       </x:c>
-      <x:c r="I35" s="17">
+      <x:c r="I35" s="16">
         <x:v>45619</x:v>
       </x:c>
-      <x:c r="J35" s="16" t="s">
+      <x:c r="J35" s="15" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="K35" s="18" t="n">
+      <x:c r="K35" s="17" t="n">
         <x:v>11280</x:v>
       </x:c>
-      <x:c r="L35" s="19">
+      <x:c r="L35" s="18">
         <x:v>46099.1200232986</x:v>
       </x:c>
-      <x:c r="M35" s="15" t="s">
+      <x:c r="M35" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="15" t="s">
+      <x:c r="B36" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="s">
+      <x:c r="C36" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D36" s="16" t="s">
+      <x:c r="D36" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="s">
+      <x:c r="E36" s="14" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="s">
+      <x:c r="F36" s="14" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G36" s="15" t="s">
+      <x:c r="G36" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="H36" s="17">
+      <x:c r="H36" s="16">
         <x:v>46069.2988094792</x:v>
       </x:c>
-      <x:c r="I36" s="17">
+      <x:c r="I36" s="16">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J36" s="16" t="s">
+      <x:c r="J36" s="15" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="K36" s="18" t="n">
+      <x:c r="K36" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L36" s="19">
+      <x:c r="L36" s="18">
         <x:v>46105.2995247917</x:v>
       </x:c>
-      <x:c r="M36" s="15" t="s">
+      <x:c r="M36" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="15" t="s">
+      <x:c r="B37" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="s">
+      <x:c r="C37" s="14" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D37" s="16" t="s">
+      <x:c r="D37" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="s">
+      <x:c r="E37" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="s">
+      <x:c r="F37" s="14" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G37" s="15" t="s">
+      <x:c r="G37" s="14" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="H37" s="17">
+      <x:c r="H37" s="16">
         <x:v>46073.1541139005</x:v>
       </x:c>
-      <x:c r="I37" s="17">
+      <x:c r="I37" s="16">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J37" s="16" t="s">
+      <x:c r="J37" s="15" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="K37" s="18" t="n">
+      <x:c r="K37" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L37" s="19">
+      <x:c r="L37" s="18">
         <x:v>46099.1584012616</x:v>
       </x:c>
-      <x:c r="M37" s="15" t="s">
+      <x:c r="M37" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="15" t="s">
+      <x:c r="B38" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="s">
+      <x:c r="C38" s="14" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D38" s="16" t="s">
+      <x:c r="D38" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="s">
+      <x:c r="E38" s="14" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="s">
+      <x:c r="F38" s="14" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="G38" s="15" t="s">
+      <x:c r="G38" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="H38" s="17">
+      <x:c r="H38" s="16">
         <x:v>46097.4788515162</x:v>
       </x:c>
-      <x:c r="I38" s="17">
+      <x:c r="I38" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J38" s="16" t="s">
+      <x:c r="J38" s="15" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="K38" s="18" t="n">
+      <x:c r="K38" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L38" s="19">
+      <x:c r="L38" s="18">
         <x:v>46100.2987549074</x:v>
       </x:c>
-      <x:c r="M38" s="15" t="s">
+      <x:c r="M38" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="15" t="s">
+      <x:c r="B39" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="s">
+      <x:c r="C39" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="D39" s="16" t="s">
+      <x:c r="D39" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="s">
+      <x:c r="E39" s="14" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="s">
+      <x:c r="F39" s="14" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="G39" s="15" t="s">
+      <x:c r="G39" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="H39" s="17">
+      <x:c r="H39" s="16">
         <x:v>46105.2848483681</x:v>
       </x:c>
-      <x:c r="I39" s="17">
+      <x:c r="I39" s="16">
         <x:v>46105</x:v>
       </x:c>
-      <x:c r="J39" s="16" t="s">
+      <x:c r="J39" s="15" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="K39" s="18" t="n">
+      <x:c r="K39" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L39" s="19">
+      <x:c r="L39" s="18">
         <x:v>46105.3281210069</x:v>
       </x:c>
-      <x:c r="M39" s="15" t="s">
+      <x:c r="M39" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="15" t="s">
+      <x:c r="B40" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="s">
+      <x:c r="C40" s="14" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D40" s="16" t="s">
+      <x:c r="D40" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E40" s="15" t="s">
+      <x:c r="E40" s="14" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="s">
+      <x:c r="F40" s="14" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G40" s="15" t="s">
+      <x:c r="G40" s="14" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H40" s="17">
+      <x:c r="H40" s="16">
         <x:v>46069.3341180556</x:v>
       </x:c>
-      <x:c r="I40" s="17">
+      <x:c r="I40" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J40" s="16" t="s">
+      <x:c r="J40" s="15" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="K40" s="18" t="n">
+      <x:c r="K40" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L40" s="19">
+      <x:c r="L40" s="18">
         <x:v>46097.244735544</x:v>
       </x:c>
-      <x:c r="M40" s="15" t="s">
+      <x:c r="M40" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="15" t="s">
+      <x:c r="B41" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C41" s="15" t="s">
+      <x:c r="C41" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D41" s="16" t="s">
+      <x:c r="D41" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E41" s="15" t="s">
+      <x:c r="E41" s="14" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="s">
+      <x:c r="F41" s="14" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="G41" s="15" t="s">
+      <x:c r="G41" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="H41" s="17">
+      <x:c r="H41" s="16">
         <x:v>46104.077202419</x:v>
       </x:c>
-      <x:c r="I41" s="17">
+      <x:c r="I41" s="16">
         <x:v>46106</x:v>
       </x:c>
-      <x:c r="J41" s="16" t="s">
+      <x:c r="J41" s="15" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="K41" s="18" t="n">
+      <x:c r="K41" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L41" s="19">
+      <x:c r="L41" s="18">
         <x:v>46106.2743414352</x:v>
       </x:c>
-      <x:c r="M41" s="15" t="s">
+      <x:c r="M41" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="15" t="s">
+      <x:c r="B42" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C42" s="15" t="s">
+      <x:c r="C42" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="D42" s="16" t="s">
+      <x:c r="D42" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E42" s="15" t="s">
+      <x:c r="E42" s="14" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="s">
+      <x:c r="F42" s="14" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="G42" s="15" t="s">
+      <x:c r="G42" s="14" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="H42" s="17">
+      <x:c r="H42" s="16">
         <x:v>46104.0901424306</x:v>
       </x:c>
-      <x:c r="I42" s="17">
+      <x:c r="I42" s="16">
         <x:v>46117</x:v>
       </x:c>
-      <x:c r="J42" s="16" t="s">
+      <x:c r="J42" s="15" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="K42" s="18" t="n">
+      <x:c r="K42" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L42" s="19">
+      <x:c r="L42" s="18">
         <x:v>46106.2675132176</x:v>
       </x:c>
-      <x:c r="M42" s="15" t="s">
+      <x:c r="M42" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="15" t="s">
+      <x:c r="B43" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C43" s="15" t="s">
+      <x:c r="C43" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="D43" s="16" t="s">
+      <x:c r="D43" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E43" s="15" t="s">
+      <x:c r="E43" s="14" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="F43" s="15" t="s">
+      <x:c r="F43" s="14" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G43" s="15" t="s">
+      <x:c r="G43" s="14" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="H43" s="17">
+      <x:c r="H43" s="16">
         <x:v>46104.0855029514</x:v>
       </x:c>
-      <x:c r="I43" s="17">
+      <x:c r="I43" s="16">
         <x:v>46117</x:v>
       </x:c>
-      <x:c r="J43" s="16" t="s">
+      <x:c r="J43" s="15" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="K43" s="18" t="n">
+      <x:c r="K43" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L43" s="19">
+      <x:c r="L43" s="18">
         <x:v>46106.2705830787</x:v>
       </x:c>
-      <x:c r="M43" s="15" t="s">
+      <x:c r="M43" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="15" t="s">
+      <x:c r="B44" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C44" s="15" t="s">
+      <x:c r="C44" s="14" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D44" s="16" t="s">
+      <x:c r="D44" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E44" s="15" t="s">
+      <x:c r="E44" s="14" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F44" s="15" t="s">
+      <x:c r="F44" s="14" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G44" s="15" t="s">
+      <x:c r="G44" s="14" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H44" s="17">
+      <x:c r="H44" s="16">
         <x:v>46084.1513040509</x:v>
       </x:c>
-      <x:c r="I44" s="17">
+      <x:c r="I44" s="16">
         <x:v>46102</x:v>
       </x:c>
-      <x:c r="J44" s="16" t="s">
+      <x:c r="J44" s="15" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="K44" s="18" t="n">
+      <x:c r="K44" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L44" s="19">
+      <x:c r="L44" s="18">
         <x:v>46097.2494578472</x:v>
       </x:c>
-      <x:c r="M44" s="15" t="s">
+      <x:c r="M44" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="15" t="s">
+      <x:c r="B45" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C45" s="15" t="s">
+      <x:c r="C45" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D45" s="16" t="s">
+      <x:c r="D45" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E45" s="15" t="s">
+      <x:c r="E45" s="14" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F45" s="15" t="s">
+      <x:c r="F45" s="14" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G45" s="15" t="s">
+      <x:c r="G45" s="14" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="H45" s="17">
+      <x:c r="H45" s="16">
         <x:v>46084.3311976389</x:v>
       </x:c>
-      <x:c r="I45" s="17">
+      <x:c r="I45" s="16">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J45" s="16" t="s">
+      <x:c r="J45" s="15" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="K45" s="18" t="n">
+      <x:c r="K45" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L45" s="19">
+      <x:c r="L45" s="18">
         <x:v>46093.3668852546</x:v>
       </x:c>
-      <x:c r="M45" s="15" t="s">
+      <x:c r="M45" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="15" t="s">
+      <x:c r="B46" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C46" s="15" t="s">
+      <x:c r="C46" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D46" s="16" t="s">
+      <x:c r="D46" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E46" s="15" t="s">
+      <x:c r="E46" s="14" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="F46" s="15" t="s">
+      <x:c r="F46" s="14" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G46" s="15" t="s">
+      <x:c r="G46" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="H46" s="17">
+      <x:c r="H46" s="16">
         <x:v>46069.2869081713</x:v>
       </x:c>
-      <x:c r="I46" s="17">
+      <x:c r="I46" s="16">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J46" s="16" t="s">
+      <x:c r="J46" s="15" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="K46" s="18" t="n">
+      <x:c r="K46" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L46" s="19">
+      <x:c r="L46" s="18">
         <x:v>46105.2599488542</x:v>
       </x:c>
-      <x:c r="M46" s="15" t="s">
+      <x:c r="M46" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="15" t="s">
+      <x:c r="B47" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C47" s="15" t="s">
+      <x:c r="C47" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D47" s="16" t="s">
+      <x:c r="D47" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E47" s="15" t="s">
+      <x:c r="E47" s="14" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="F47" s="15" t="s">
+      <x:c r="F47" s="14" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="G47" s="15" t="s">
+      <x:c r="G47" s="14" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="H47" s="17">
+      <x:c r="H47" s="16">
         <x:v>46073.1135088426</x:v>
       </x:c>
-      <x:c r="I47" s="17">
+      <x:c r="I47" s="16">
         <x:v>45751</x:v>
       </x:c>
-      <x:c r="J47" s="16" t="s">
+      <x:c r="J47" s="15" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="K47" s="18" t="n">
+      <x:c r="K47" s="17" t="n">
         <x:v>7530</x:v>
       </x:c>
-      <x:c r="L47" s="19">
+      <x:c r="L47" s="18">
         <x:v>46097.2511403241</x:v>
       </x:c>
-      <x:c r="M47" s="15" t="s">
+      <x:c r="M47" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="15" t="s">
+      <x:c r="B48" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C48" s="15" t="s">
+      <x:c r="C48" s="14" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="D48" s="16" t="s">
+      <x:c r="D48" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E48" s="15" t="s">
+      <x:c r="E48" s="14" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="F48" s="15" t="s">
+      <x:c r="F48" s="14" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="G48" s="15" t="s">
+      <x:c r="G48" s="14" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="H48" s="17">
+      <x:c r="H48" s="16">
         <x:v>46092.1012814815</x:v>
       </x:c>
-      <x:c r="I48" s="17">
+      <x:c r="I48" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J48" s="16" t="s">
+      <x:c r="J48" s="15" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="K48" s="18" t="n">
+      <x:c r="K48" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L48" s="19">
+      <x:c r="L48" s="18">
         <x:v>46097.1408234491</x:v>
       </x:c>
-      <x:c r="M48" s="15" t="s">
+      <x:c r="M48" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B49" s="15" t="s">
+      <x:c r="B49" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C49" s="15" t="s">
+      <x:c r="C49" s="14" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="D49" s="16" t="s">
+      <x:c r="D49" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E49" s="15" t="s">
+      <x:c r="E49" s="14" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="F49" s="15" t="s">
+      <x:c r="F49" s="14" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G49" s="15" t="s">
+      <x:c r="G49" s="14" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H49" s="17">
+      <x:c r="H49" s="16">
         <x:v>46097.4214954398</x:v>
       </x:c>
-      <x:c r="I49" s="17">
+      <x:c r="I49" s="16">
         <x:v>46100</x:v>
       </x:c>
-      <x:c r="J49" s="16" t="s">
+      <x:c r="J49" s="15" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="K49" s="18" t="n">
+      <x:c r="K49" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L49" s="19">
+      <x:c r="L49" s="18">
         <x:v>46100.2966699421</x:v>
       </x:c>
-      <x:c r="M49" s="15" t="s">
+      <x:c r="M49" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="15" t="s">
+      <x:c r="B50" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C50" s="15" t="s">
+      <x:c r="C50" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D50" s="16" t="s">
+      <x:c r="D50" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E50" s="15" t="s">
+      <x:c r="E50" s="14" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="F50" s="15" t="s">
+      <x:c r="F50" s="14" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G50" s="15" t="s">
+      <x:c r="G50" s="14" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="H50" s="17">
+      <x:c r="H50" s="16">
         <x:v>46069.1217257292</x:v>
       </x:c>
-      <x:c r="I50" s="17">
+      <x:c r="I50" s="16">
         <x:v>46157</x:v>
       </x:c>
-      <x:c r="J50" s="16" t="s">
+      <x:c r="J50" s="15" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="K50" s="18" t="n">
+      <x:c r="K50" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L50" s="19">
+      <x:c r="L50" s="18">
         <x:v>46097.3375062153</x:v>
       </x:c>
-      <x:c r="M50" s="15" t="s">
+      <x:c r="M50" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="15" t="s">
+      <x:c r="B51" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C51" s="15" t="s">
+      <x:c r="C51" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D51" s="16" t="s">
+      <x:c r="D51" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E51" s="15" t="s">
+      <x:c r="E51" s="14" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="F51" s="15" t="s">
+      <x:c r="F51" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G51" s="15" t="s">
+      <x:c r="G51" s="14" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="H51" s="17">
+      <x:c r="H51" s="16">
         <x:v>46084.2548997222</x:v>
       </x:c>
-      <x:c r="I51" s="17">
+      <x:c r="I51" s="16">
         <x:v>46084.2549156713</x:v>
       </x:c>
-      <x:c r="J51" s="16" t="s">
+      <x:c r="J51" s="15" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="K51" s="18" t="n">
+      <x:c r="K51" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L51" s="19">
+      <x:c r="L51" s="18">
         <x:v>46105.4010316319</x:v>
       </x:c>
-      <x:c r="M51" s="15" t="s">
+      <x:c r="M51" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B52" s="15" t="s">
+      <x:c r="B52" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C52" s="15" t="s">
+      <x:c r="C52" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D52" s="16" t="s">
+      <x:c r="D52" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E52" s="15" t="s">
+      <x:c r="E52" s="14" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="F52" s="15" t="s">
+      <x:c r="F52" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G52" s="15" t="s">
+      <x:c r="G52" s="14" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H52" s="17">
+      <x:c r="H52" s="16">
         <x:v>46084.2374126389</x:v>
       </x:c>
-      <x:c r="I52" s="17">
+      <x:c r="I52" s="16">
         <x:v>46084.2374295139</x:v>
       </x:c>
-      <x:c r="J52" s="16" t="s">
+      <x:c r="J52" s="15" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="K52" s="18" t="n">
+      <x:c r="K52" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L52" s="19">
+      <x:c r="L52" s="18">
         <x:v>46105.4096900347</x:v>
       </x:c>
-      <x:c r="M52" s="15" t="s">
+      <x:c r="M52" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="15" t="s">
+      <x:c r="B53" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C53" s="15" t="s">
+      <x:c r="C53" s="14" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="D53" s="16" t="s">
+      <x:c r="D53" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E53" s="15" t="s">
+      <x:c r="E53" s="14" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="F53" s="15" t="s">
+      <x:c r="F53" s="14" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="G53" s="15" t="s">
+      <x:c r="G53" s="14" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="H53" s="17">
+      <x:c r="H53" s="16">
         <x:v>46084.3419451968</x:v>
       </x:c>
-      <x:c r="I53" s="17">
+      <x:c r="I53" s="16">
         <x:v>46084.3419617014</x:v>
       </x:c>
-      <x:c r="J53" s="16" t="s">
+      <x:c r="J53" s="15" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="K53" s="18" t="n">
+      <x:c r="K53" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L53" s="19">
+      <x:c r="L53" s="18">
         <x:v>46090.3480933681</x:v>
       </x:c>
-      <x:c r="M53" s="15" t="s">
+      <x:c r="M53" s="14" t="s">
         <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="15" t="s">
+      <x:c r="B54" s="14" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="C54" s="15" t="s">
+      <x:c r="C54" s="14" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="D54" s="16" t="s">
+      <x:c r="D54" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E54" s="15" t="s">
+      <x:c r="E54" s="14" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="F54" s="15" t="s">
+      <x:c r="F54" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="G54" s="15" t="s">
+      <x:c r="G54" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="H54" s="17">
+      <x:c r="H54" s="16">
         <x:v>46084.1579541898</x:v>
       </x:c>
-      <x:c r="I54" s="17">
+      <x:c r="I54" s="16">
         <x:v>46145</x:v>
       </x:c>
-      <x:c r="J54" s="16" t="s">
+      <x:c r="J54" s="15" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="K54" s="18" t="n">
+      <x:c r="K54" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L54" s="19">
+      <x:c r="L54" s="18">
         <x:v>46093.4169326042</x:v>
       </x:c>
-      <x:c r="M54" s="15" t="s">
+      <x:c r="M54" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B55" s="15" t="s">
+      <x:c r="B55" s="14" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="C55" s="15" t="s">
+      <x:c r="C55" s="14" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="D55" s="16" t="s">
+      <x:c r="D55" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E55" s="15" t="s">
+      <x:c r="E55" s="14" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="F55" s="15" t="s">
+      <x:c r="F55" s="14" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G55" s="15" t="s">
+      <x:c r="G55" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="H55" s="17">
+      <x:c r="H55" s="16">
         <x:v>46083.2228741435</x:v>
       </x:c>
-      <x:c r="I55" s="17">
+      <x:c r="I55" s="16">
         <x:v>46083</x:v>
       </x:c>
-      <x:c r="J55" s="16" t="s">
+      <x:c r="J55" s="15" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="K55" s="18" t="n">
+      <x:c r="K55" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L55" s="19">
+      <x:c r="L55" s="18">
         <x:v>46111.2343215393</x:v>
       </x:c>
-      <x:c r="M55" s="15" t="s">
+      <x:c r="M55" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B56" s="15" t="s">
+      <x:c r="B56" s="14" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="C56" s="15" t="s">
+      <x:c r="C56" s="14" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D56" s="16" t="s">
+      <x:c r="D56" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E56" s="15" t="s">
+      <x:c r="E56" s="14" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="F56" s="15" t="s">
+      <x:c r="F56" s="14" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G56" s="15" t="s">
+      <x:c r="G56" s="14" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="H56" s="17">
+      <x:c r="H56" s="16">
         <x:v>46084.1627466204</x:v>
       </x:c>
-      <x:c r="I56" s="17">
+      <x:c r="I56" s="16">
         <x:v>46060</x:v>
       </x:c>
-      <x:c r="J56" s="16" t="s">
+      <x:c r="J56" s="15" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="K56" s="18" t="n">
+      <x:c r="K56" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L56" s="19">
+      <x:c r="L56" s="18">
         <x:v>46100.392939537</x:v>
       </x:c>
-      <x:c r="M56" s="15" t="s">
+      <x:c r="M56" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B57" s="15" t="s">
+      <x:c r="B57" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C57" s="15" t="s">
+      <x:c r="C57" s="14" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="D57" s="16" t="s">
+      <x:c r="D57" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E57" s="15" t="s">
+      <x:c r="E57" s="14" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="F57" s="15" t="s">
+      <x:c r="F57" s="14" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="G57" s="15" t="s">
+      <x:c r="G57" s="14" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="H57" s="17">
+      <x:c r="H57" s="16">
         <x:v>46083.2276334028</x:v>
       </x:c>
-      <x:c r="I57" s="17">
+      <x:c r="I57" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J57" s="16" t="s">
+      <x:c r="J57" s="15" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="K57" s="18" t="n">
+      <x:c r="K57" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L57" s="19">
+      <x:c r="L57" s="18">
         <x:v>46111.2358333681</x:v>
       </x:c>
-      <x:c r="M57" s="15" t="s">
+      <x:c r="M57" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B58" s="15" t="s">
+      <x:c r="B58" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C58" s="15" t="s">
+      <x:c r="C58" s="14" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="D58" s="16" t="s">
+      <x:c r="D58" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E58" s="15" t="s">
+      <x:c r="E58" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="F58" s="15" t="s">
+      <x:c r="F58" s="14" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G58" s="15" t="s">
+      <x:c r="G58" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="H58" s="17">
+      <x:c r="H58" s="16">
         <x:v>46105.2817877199</x:v>
       </x:c>
-      <x:c r="I58" s="17">
+      <x:c r="I58" s="16">
         <x:v>46634</x:v>
       </x:c>
-      <x:c r="J58" s="16" t="s">
+      <x:c r="J58" s="15" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="K58" s="18" t="n">
+      <x:c r="K58" s="17" t="n">
         <x:v>8190</x:v>
       </x:c>
-      <x:c r="L58" s="19">
+      <x:c r="L58" s="18">
         <x:v>46105.3080007639</x:v>
       </x:c>
-      <x:c r="M58" s="15" t="s">
+      <x:c r="M58" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B59" s="15" t="s">
+      <x:c r="B59" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C59" s="15" t="s">
+      <x:c r="C59" s="14" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="D59" s="16" t="s">
+      <x:c r="D59" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E59" s="15" t="s">
+      <x:c r="E59" s="14" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="F59" s="15" t="s">
+      <x:c r="F59" s="14" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G59" s="15" t="s">
+      <x:c r="G59" s="14" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="H59" s="17">
+      <x:c r="H59" s="16">
         <x:v>46092.9637875116</x:v>
       </x:c>
-      <x:c r="I59" s="17">
+      <x:c r="I59" s="16">
         <x:v>46094</x:v>
       </x:c>
-      <x:c r="J59" s="16" t="s">
+      <x:c r="J59" s="15" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="K59" s="18" t="n">
+      <x:c r="K59" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L59" s="19">
+      <x:c r="L59" s="18">
         <x:v>46093.3109466551</x:v>
       </x:c>
-      <x:c r="M59" s="15" t="s">
+      <x:c r="M59" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B62" s="20" t="s">
+      <x:c r="B62" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C62" s="21" t="s"/>
-      <x:c r="D62" s="21" t="s"/>
-      <x:c r="E62" s="22" t="s"/>
-      <x:c r="F62" s="22" t="s"/>
+      <x:c r="C62" s="20" t="s"/>
+      <x:c r="D62" s="20" t="s"/>
+      <x:c r="E62" s="21" t="s"/>
+      <x:c r="F62" s="21" t="s"/>
     </x:row>
     <x:row r="63" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B63" s="23" t="s">
+      <x:c r="B63" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C63" s="24" t="s"/>
-      <x:c r="D63" s="24" t="s"/>
-      <x:c r="E63" s="24" t="s"/>
-      <x:c r="F63" s="25" t="s">
+      <x:c r="C63" s="23" t="s"/>
+      <x:c r="D63" s="23" t="s"/>
+      <x:c r="E63" s="23" t="s"/>
+      <x:c r="F63" s="24" t="s">
         <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B64" s="26" t="s">
+      <x:c r="B64" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C64" s="27" t="s"/>
-      <x:c r="D64" s="27" t="s"/>
-      <x:c r="E64" s="27" t="s"/>
-      <x:c r="F64" s="28" t="n">
+      <x:c r="C64" s="26" t="s"/>
+      <x:c r="D64" s="26" t="s"/>
+      <x:c r="E64" s="26" t="s"/>
+      <x:c r="F64" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B65" s="26" t="s">
+      <x:c r="B65" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C65" s="27" t="s"/>
-      <x:c r="D65" s="27" t="s"/>
-      <x:c r="E65" s="27" t="s"/>
-      <x:c r="F65" s="28" t="n">
+      <x:c r="C65" s="26" t="s"/>
+      <x:c r="D65" s="26" t="s"/>
+      <x:c r="E65" s="26" t="s"/>
+      <x:c r="F65" s="27" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="26" t="s">
+      <x:c r="B66" s="25" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C66" s="27" t="s"/>
-      <x:c r="D66" s="27" t="s"/>
-      <x:c r="E66" s="27" t="s"/>
-      <x:c r="F66" s="28" t="n">
+      <x:c r="C66" s="26" t="s"/>
+      <x:c r="D66" s="26" t="s"/>
+      <x:c r="E66" s="26" t="s"/>
+      <x:c r="F66" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="26" t="s">
+      <x:c r="B67" s="25" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="C67" s="27" t="s"/>
-      <x:c r="D67" s="27" t="s"/>
-      <x:c r="E67" s="27" t="s"/>
-      <x:c r="F67" s="28" t="n">
+      <x:c r="C67" s="26" t="s"/>
+      <x:c r="D67" s="26" t="s"/>
+      <x:c r="E67" s="26" t="s"/>
+      <x:c r="F67" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B68" s="26" t="s">
+      <x:c r="B68" s="25" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C68" s="27" t="s"/>
-      <x:c r="D68" s="27" t="s"/>
-      <x:c r="E68" s="27" t="s"/>
-      <x:c r="F68" s="28" t="n">
+      <x:c r="C68" s="26" t="s"/>
+      <x:c r="D68" s="26" t="s"/>
+      <x:c r="E68" s="26" t="s"/>
+      <x:c r="F68" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B69" s="29" t="s">
+      <x:c r="B69" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C69" s="30" t="s"/>
-      <x:c r="D69" s="30" t="s"/>
-      <x:c r="E69" s="30" t="s"/>
-      <x:c r="F69" s="31" t="n">
+      <x:c r="C69" s="29" t="s"/>
+      <x:c r="D69" s="29" t="s"/>
+      <x:c r="E69" s="29" t="s"/>
+      <x:c r="F69" s="30" t="n">
         <x:v>52</x:v>
       </x:c>
     </x:row>
@@ -4870,17 +4855,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4903,325 +4888,325 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46112.3105175116</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46171</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46128.1580781366</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46073.1304932986</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46034</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46119.2877239352</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46112.337306331</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46177</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46128.3625958333</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46069.272014213</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46067</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46119.2995831134</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46128.2227381019</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46072</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46128.3098665394</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46128.1990794213</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46128.3062135532</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
         <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
+      <x:c r="B20" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
+      <x:c r="C20" s="29" t="s"/>
+      <x:c r="D20" s="29" t="s"/>
+      <x:c r="E20" s="29" t="s"/>
+      <x:c r="F20" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -784,6 +784,21 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>CLIXTEC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTROMALL MONTALBAN LS-107, MANGGAHAN, Rodriguez (Montalban), Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07943-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1244-042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511469</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYALA MALLS SERIN SILANG, JUNCTION EAST, Tagaytay City, Cavite</x:t>
   </x:si>
   <x:si>
@@ -830,6 +845,18 @@
   </x:si>
   <x:si>
     <x:t>1511394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOTUS CENTRAL MALL 2/F NUEVO AVENUE, TANZANG LUMA I, Imus City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-15-06-C1887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1250-534</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511468</x:t>
   </x:si>
   <x:si>
     <x:t>XOCUS BELL TECH MERCHANDISING INC</x:t>
@@ -4929,37 +4956,37 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46112.3105175116</x:v>
+        <x:v>46112.2780077662</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46171</x:v>
+        <x:v>46112.2780258912</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46128.1580781366</x:v>
+        <x:v>46132.3858322685</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
@@ -4976,28 +5003,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46073.1304932986</x:v>
+        <x:v>46112.3105175116</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46034</x:v>
+        <x:v>46171</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46119.2877239352</x:v>
+        <x:v>46128.1580781366</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -5008,34 +5035,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46112.337306331</x:v>
+        <x:v>46073.1304932986</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46177</x:v>
+        <x:v>46034</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46128.3625958333</x:v>
+        <x:v>46119.2877239352</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -5046,34 +5073,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46069.272014213</x:v>
+        <x:v>46112.337306331</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46067</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46128.3625958333</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -5081,10 +5108,10 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>269</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>54</x:v>
@@ -5099,30 +5126,30 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46128.2227381019</x:v>
+        <x:v>46069.272014213</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46072</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>273</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46119.2995831134</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>269</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>54</x:v>
@@ -5137,83 +5164,177 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46128.1990794213</x:v>
+        <x:v>46112.3204506829</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46092</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>277</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>46132.3781534259</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46128.2227381019</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46072</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L14" s="18">
+        <x:v>46128.3098665394</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46128.1990794213</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
         <x:v>46128.3062135532</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
         <x:v>251</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="25" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="25" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="25" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="28" t="s">
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s"/>
-      <x:c r="D20" s="29" t="s"/>
-      <x:c r="E20" s="29" t="s"/>
-      <x:c r="F20" s="30" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6184,16 +6305,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -797,6 +797,18 @@
   </x:si>
   <x:si>
     <x:t>1511469</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SM CITY STO. TOMAS, SAN BATOLOME, Santo Tomas, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07945-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1246-428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511472</x:t>
   </x:si>
   <x:si>
     <x:t>AYALA MALLS SERIN SILANG, JUNCTION EAST, Tagaytay City, Cavite</x:t>
@@ -4994,13 +5006,13 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
         <x:v>258</x:v>
@@ -5012,19 +5024,19 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46112.3105175116</x:v>
+        <x:v>46112.2975525116</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46171</x:v>
+        <x:v>46112.2975902315</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>261</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46128.1580781366</x:v>
+        <x:v>46133.115857338</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -5050,19 +5062,19 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46073.1304932986</x:v>
+        <x:v>46112.3105175116</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46034</x:v>
+        <x:v>46171</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>265</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46119.2877239352</x:v>
+        <x:v>46128.1580781366</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -5073,7 +5085,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>54</x:v>
@@ -5088,19 +5100,19 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46112.337306331</x:v>
+        <x:v>46073.1304932986</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46177</x:v>
+        <x:v>46034</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>269</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46128.3625958333</x:v>
+        <x:v>46119.2877239352</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -5111,7 +5123,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>54</x:v>
@@ -5126,19 +5138,19 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46069.272014213</x:v>
+        <x:v>46112.337306331</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46067</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>273</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46128.3625958333</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -5146,10 +5158,10 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>54</x:v>
@@ -5164,19 +5176,19 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46112.3204506829</x:v>
+        <x:v>46069.272014213</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46182</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>277</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46132.3781534259</x:v>
+        <x:v>46119.2995831134</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -5184,40 +5196,40 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46112.3204506829</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46128.2227381019</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46072</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>282</x:v>
-      </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46132.3781534259</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
@@ -5225,7 +5237,7 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>54</x:v>
@@ -5240,10 +5252,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46128.1990794213</x:v>
+        <x:v>46128.2227381019</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46092</x:v>
+        <x:v>46072</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>286</x:v>
@@ -5252,90 +5264,127 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.3062135532</x:v>
+        <x:v>46128.3098665394</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46128.1990794213</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46128.3062135532</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="19" t="s">
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C18" s="20" t="s"/>
-      <x:c r="D18" s="20" t="s"/>
-      <x:c r="E18" s="21" t="s"/>
-      <x:c r="F18" s="21" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="22" t="s">
+      <x:c r="C19" s="20" t="s"/>
+      <x:c r="D19" s="20" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="21" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="s">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="s">
         <x:v>251</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="26" t="s"/>
       <x:c r="D21" s="26" t="s"/>
       <x:c r="E21" s="26" t="s"/>
       <x:c r="F21" s="27" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="25" t="s">
-        <x:v>218</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="26" t="s"/>
       <x:c r="D22" s="26" t="s"/>
       <x:c r="E22" s="26" t="s"/>
       <x:c r="F22" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
       <x:c r="E23" s="26" t="s"/>
       <x:c r="F23" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="25" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="28" t="s">
+    <x:row r="25" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B25" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="30" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6310,13 +6359,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="295">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -845,6 +845,18 @@
   </x:si>
   <x:si>
     <x:t>1511450</x:t>
+  </x:si>
+  <x:si>
+    <x:t>225 2/F CYBERZONE SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-17-05-0645 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1273-206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511477</x:t>
   </x:si>
   <x:si>
     <x:t>GFA29 CENTRAL MALL, SALITRAN II, City Of Dasmariñas, Cavite</x:t>
@@ -5161,7 +5173,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>54</x:v>
@@ -5176,19 +5188,19 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46069.272014213</x:v>
+        <x:v>46127.1415970486</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46067</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>277</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46133.2825861574</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -5196,10 +5208,10 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>54</x:v>
@@ -5214,19 +5226,19 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46112.3204506829</x:v>
+        <x:v>46069.272014213</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46182</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>281</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46132.3781534259</x:v>
+        <x:v>46119.2995831134</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -5234,40 +5246,40 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46112.3204506829</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46128.2227381019</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46072</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>286</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46132.3781534259</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
@@ -5275,7 +5287,7 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>54</x:v>
@@ -5290,10 +5302,10 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46128.1990794213</x:v>
+        <x:v>46128.2227381019</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46092</x:v>
+        <x:v>46072</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>290</x:v>
@@ -5302,90 +5314,127 @@
         <x:v>2550</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.3062135532</x:v>
+        <x:v>46128.3098665394</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46128.1990794213</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46128.3062135532</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="19" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C19" s="20" t="s"/>
-      <x:c r="D19" s="20" t="s"/>
-      <x:c r="E19" s="21" t="s"/>
-      <x:c r="F19" s="21" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="22" t="s">
+      <x:c r="C20" s="20" t="s"/>
+      <x:c r="D20" s="20" t="s"/>
+      <x:c r="E20" s="21" t="s"/>
+      <x:c r="F20" s="21" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="s">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="s">
         <x:v>251</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="26" t="s"/>
       <x:c r="D22" s="26" t="s"/>
       <x:c r="E22" s="26" t="s"/>
       <x:c r="F22" s="27" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>218</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
       <x:c r="E23" s="26" t="s"/>
       <x:c r="F23" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
       <x:c r="E24" s="26" t="s"/>
       <x:c r="F24" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="25" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="28" t="s">
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="30" t="n">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6359,13 +6408,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="295">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -869,6 +869,21 @@
   </x:si>
   <x:si>
     <x:t>1511394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RKD GADGET SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>128 J RIZAL ST, POBLACION II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-08866-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1293-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530147</x:t>
   </x:si>
   <x:si>
     <x:t>LOTUS CENTRAL MALL 2/F NUEVO AVENUE, TANZANG LUMA I, Imus City, Cavite</x:t>
@@ -5246,48 +5261,48 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46112.3204506829</x:v>
+        <x:v>46135.740464213</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46182</x:v>
+        <x:v>46135.7404903472</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46132.3781534259</x:v>
+        <x:v>46139.3656545718</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>286</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>54</x:v>
@@ -5302,22 +5317,22 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46128.2227381019</x:v>
+        <x:v>46112.3204506829</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46072</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>290</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46132.3781534259</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
@@ -5325,118 +5340,165 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46128.1990794213</x:v>
+        <x:v>46128.2227381019</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46092</x:v>
+        <x:v>46072</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.3062135532</x:v>
+        <x:v>46128.3098665394</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46128.1990794213</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46128.3062135532</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="19" t="s">
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C20" s="20" t="s"/>
-      <x:c r="D20" s="20" t="s"/>
-      <x:c r="E20" s="21" t="s"/>
-      <x:c r="F20" s="21" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="22" t="s">
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="s">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
         <x:v>251</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
       <x:c r="E23" s="26" t="s"/>
       <x:c r="F23" s="27" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>218</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
       <x:c r="E24" s="26" t="s"/>
       <x:c r="F24" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="25" t="s">
-        <x:v>233</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C25" s="26" t="s"/>
       <x:c r="D25" s="26" t="s"/>
       <x:c r="E25" s="26" t="s"/>
       <x:c r="F25" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="25" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="25" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="28" t="s">
+    <x:row r="28" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B28" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="30" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C28" s="29" t="s"/>
+      <x:c r="D28" s="29" t="s"/>
+      <x:c r="E28" s="29" t="s"/>
+      <x:c r="F28" s="30" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6403,18 +6465,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B21:F21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="324">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -847,6 +847,51 @@
     <x:t>1511450</x:t>
   </x:si>
   <x:si>
+    <x:t>INTO GADGETS TOO INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E224 SM City Dasmariñas,, Brgy. Sampaloc 1,, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-NCR-3110-19 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1284-676</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2nd Flr. Cyberzone SM City Calamba, Real, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-468b-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1295-329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CZ-24 SM City Trece,, Brgy. Agustin,, Trece Martires City (Capital), Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-05-0796 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1287-504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531178</x:t>
+  </x:si>
+  <x:si>
     <x:t>225 2/F CYBERZONE SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -869,6 +914,33 @@
   </x:si>
   <x:si>
     <x:t>1511394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNO KID CELLPHONE CENTER INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C214 SM City Trece Martires,, Brgy. San Agustin, Trece Martires City (Capital), Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-472a-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1286-938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CP220 SM City Dasmariñas, Brgy. Sampaloc 14114, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-471a-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1285-656</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531179</x:t>
   </x:si>
   <x:si>
     <x:t>RKD GADGET SHOP</x:t>
@@ -5188,34 +5260,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46127.1415970486</x:v>
+        <x:v>46134.4259644444</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46135</x:v>
+        <x:v>46179</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46133.2825861574</x:v>
+        <x:v>46141.2705907986</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -5226,34 +5298,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46069.272014213</x:v>
+        <x:v>46139.1392404861</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46067</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46141.238019537</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -5261,75 +5333,75 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46135.740464213</x:v>
+        <x:v>46134.4505067245</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46135.7404903472</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46139.3656545718</x:v>
+        <x:v>46141.2556749421</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>217</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46112.3204506829</x:v>
+        <x:v>46127.1415970486</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46182</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>290</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46132.3781534259</x:v>
+        <x:v>46133.2825861574</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
@@ -5337,173 +5409,358 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>291</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46128.2227381019</x:v>
+        <x:v>46069.272014213</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46072</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46119.2995831134</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>291</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>296</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46134.4424908912</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46164</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46141.2427502662</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
+      <x:c r="D19" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46134.4345563194</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46164</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46141.2618936806</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46135.740464213</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46135.7404903472</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46139.3656545718</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46112.3204506829</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46132.3781534259</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46128.2227381019</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46072</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46128.3098665394</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
         <x:v>46128.1990794213</x:v>
       </x:c>
-      <x:c r="I18" s="16">
+      <x:c r="I23" s="16">
         <x:v>46092</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="J23" s="15" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L23" s="18">
         <x:v>46128.3062135532</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="19" t="s">
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C21" s="20" t="s"/>
-      <x:c r="D21" s="20" t="s"/>
-      <x:c r="E21" s="21" t="s"/>
-      <x:c r="F21" s="21" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="22" t="s">
+      <x:c r="C26" s="20" t="s"/>
+      <x:c r="D26" s="20" t="s"/>
+      <x:c r="E26" s="21" t="s"/>
+      <x:c r="F26" s="21" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B27" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C22" s="23" t="s"/>
-      <x:c r="D22" s="23" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="24" t="s">
+      <x:c r="C27" s="23" t="s"/>
+      <x:c r="D27" s="23" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="24" t="s">
         <x:v>251</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="25" t="s">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="25" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="25" t="s">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="25" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="25" t="s">
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="25" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C27" s="26" t="s"/>
-      <x:c r="D27" s="26" t="s"/>
-      <x:c r="E27" s="26" t="s"/>
-      <x:c r="F27" s="27" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B28" s="28" t="s">
+    <x:row r="33" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B33" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C28" s="29" t="s"/>
-      <x:c r="D28" s="29" t="s"/>
-      <x:c r="E28" s="29" t="s"/>
-      <x:c r="F28" s="30" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6470,14 +6727,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B21:F21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B26:F26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="324">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -892,6 +892,21 @@
     <x:t>1531178</x:t>
   </x:si>
   <x:si>
+    <x:t>SANDZTEL MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lot #292 B2 SM City Calamba National Highway, Real, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-469b-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1294-919</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531181</x:t>
+  </x:si>
+  <x:si>
     <x:t>225 2/F CYBERZONE SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
   </x:si>
   <x:si>
@@ -919,6 +934,18 @@
     <x:t>TECHNO KID CELLPHONE CENTER INC.</x:t>
   </x:si>
   <x:si>
+    <x:t>CP220 SM City Dasmariñas, Brgy. Sampaloc 14114, City Of Dasmariñas, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-471a-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1285-656</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531179</x:t>
+  </x:si>
+  <x:si>
     <x:t>C214 SM City Trece Martires,, Brgy. San Agustin, Trece Martires City (Capital), Cavite</x:t>
   </x:si>
   <x:si>
@@ -929,18 +956,6 @@
   </x:si>
   <x:si>
     <x:t>1531176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CP220 SM City Dasmariñas, Brgy. Sampaloc 14114, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-471a-22R (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1285-656</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1531179</x:t>
   </x:si>
   <x:si>
     <x:t>RKD GADGET SHOP</x:t>
@@ -5374,34 +5389,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46127.1415970486</x:v>
+        <x:v>46139.1324899537</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46135</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46133.2825861574</x:v>
+        <x:v>46141.3857011921</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
@@ -5412,34 +5427,34 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46069.272014213</x:v>
+        <x:v>46127.1415970486</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46067</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46133.2825861574</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
@@ -5450,7 +5465,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>54</x:v>
@@ -5465,19 +5480,19 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46134.4424908912</x:v>
+        <x:v>46069.272014213</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46164</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
         <x:v>301</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46141.2427502662</x:v>
+        <x:v>46119.2995831134</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
@@ -5488,19 +5503,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>297</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="H19" s="16">
         <x:v>46134.4345563194</x:v>
@@ -5509,7 +5524,7 @@
         <x:v>46164</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
@@ -5523,13 +5538,13 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>306</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
         <x:v>307</x:v>
@@ -5541,68 +5556,68 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46135.740464213</x:v>
+        <x:v>46134.4424908912</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46135.7404903472</x:v>
+        <x:v>46164</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>310</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46139.3656545718</x:v>
+        <x:v>46141.2427502662</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>217</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46112.3204506829</x:v>
+        <x:v>46135.740464213</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46182</x:v>
+        <x:v>46135.7404903472</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46132.3781534259</x:v>
+        <x:v>46139.3656545718</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>315</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>54</x:v>
@@ -5617,22 +5632,22 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46128.2227381019</x:v>
+        <x:v>46112.3204506829</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46072</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
         <x:v>319</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46132.3781534259</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
@@ -5640,97 +5655,124 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>315</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46128.1990794213</x:v>
+        <x:v>46128.2227381019</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46092</x:v>
+        <x:v>46072</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46128.3062135532</x:v>
+        <x:v>46128.3098665394</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46128.1990794213</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46092</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46128.3062135532</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="19" t="s">
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="19" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="C26" s="20" t="s"/>
-      <x:c r="D26" s="20" t="s"/>
-      <x:c r="E26" s="21" t="s"/>
-      <x:c r="F26" s="21" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="22" t="s">
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="21" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="22" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="24" t="s">
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="s">
         <x:v>251</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="26" t="s"/>
       <x:c r="D29" s="26" t="s"/>
       <x:c r="E29" s="26" t="s"/>
       <x:c r="F29" s="27" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>203</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
       <x:c r="E30" s="26" t="s"/>
       <x:c r="F30" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="25" t="s">
-        <x:v>218</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C31" s="26" t="s"/>
       <x:c r="D31" s="26" t="s"/>
@@ -5741,27 +5783,37 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="25" t="s">
-        <x:v>233</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C32" s="26" t="s"/>
       <x:c r="D32" s="26" t="s"/>
       <x:c r="E32" s="26" t="s"/>
       <x:c r="F32" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="25" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="28" t="s">
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="28" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6727,14 +6779,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B26:F26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
+++ b/reports/service-tracking-report-DENIEL-GENNE-PUYO-evaluator-cache-serviceTracking-DENIEL-GENNE-PUYO-IV-A-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -67,18 +67,489 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Retailer/Reseller Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XENTRO MALL LEMERY NATIONAL ROAD, MALINIS, Lemery, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06698-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1169-102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1507967</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ricardo Natividad</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL ANGLE MARKETING INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UG MASSWAY SHOPPING CENTER F.T Catapusan, Plaza Almeda, Tanay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06915-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1178-478</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 1511203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caesar Allen Centeno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>X-DOT CONNECTION INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06900-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1177-099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Service Center Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>257-G SM City Molino Molino Road, Molino IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1194-347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 008 G/F WALTERMART BACOOR WALTERMART BACOOR BLVD., MAMBOG IV, Bacoor City, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0452R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1168-173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1164-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-024R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1165-147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-16-05-1938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1162-745</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2nd Flr. Cyberzone SM City Calamba, Real, City Of Calamba, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-03-0775 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1192-904</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511231</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1150-325</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511233</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 467-24R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1096-022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511193</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBLITZ MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 23- 019R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1095-163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-018R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1094-777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYNCNETIC INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-468R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1161-717</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 24-471R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1108-762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-06919-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1179-857</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-05-0452-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1084-395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511240</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLH GENTECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-17-11-0683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1109-317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511246</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBILECRAZE TELECOM INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-01-25-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1113-757</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511248</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1201-204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511270</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHONEVILLE MOBILE INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sm City Taytay Manila East Road Sm City Taytay Manila East Road, Dolores, Taytay, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-03-0774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1202-217</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511271</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-17-02-2011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1163-392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511277</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-451R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1111-408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADI-ASIANIC DISTRIBUTORS INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STALL 224 2/F SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1180-596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1181-124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1182-290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1183-545</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0413</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1184-446</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1185-901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0412</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1186-322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0415</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1187-091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-14-04-0410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1188-853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 02-25- 045R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1091-601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511298</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-02-25-0453R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1092-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIZMOTECH CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/f sm city batangas pastor village, pallocan west, Batangas City (Capital), Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DDSC22091049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1227-607</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511918</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Adora Mercado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-22-003R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1098-751</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRISMATECH INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UG 227 ROBINSONS PLACE ANTIPOLO SUMULONG HIGHWAY, DELA PAZ, City Of Antipolo, Rizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">     DD-MP-02-25-0456R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1228-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06685-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1167-519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-06683-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1166-516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIGITAL WALKER CORP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT R09 BLK J. THE OUTLETS, SAN LUCAS, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-466b-22R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1200-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511311</x:t>
+  </x:si>
+  <x:si>
     <x:t>DGNATION INC.</x:t>
   </x:si>
   <x:si>
-    <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
     <x:t>UNIT 101B GROUND FLOOR VISTAMALL DASMARIÑAS AGUINALDO HIGHWAY, SAN AGUSTIN II, City Of Dasmariñas, Cavite</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROIV-A-07536-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1223-317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIV-A-07468-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1208-449</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511313</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROIV-A-07540-26</x:t>
   </x:si>
   <x:si>
@@ -88,12 +559,6 @@
     <x:t>1511314</x:t>
   </x:si>
   <x:si>
-    <x:t>Caesar Allen Centeno</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOWER GROUND LEVEL VISTA MALL SOMO DAANG HARI VISTA CITY CORNER, MOLINO IV, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
     <x:t>MPDP-ROIV-A-07539-26</x:t>
   </x:si>
   <x:si>
@@ -103,46 +568,61 @@
     <x:t xml:space="preserve"> 1511315</x:t>
   </x:si>
   <x:si>
-    <x:t>256 2/F SM CENTER ANGONO MANILA EAST ROAD, SAN ISIDRO, Angono, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-07536-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1223-317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511312</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unit 335 SM City Lucena Maharlika Highway corner Dalahican Road, Ibabang Dupay, Lucena City (Capital), Quezon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-07468-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1208-449</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL ANGLE MARKETING INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 11 2ND FLR SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06919-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1179-857</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UG MASSWAY SHOPPING CENTER F.T Catapusan, Plaza Almeda, Tanay, Rizal</x:t>
+    <x:t>DD-RR-21-04-2282</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1191-381</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511320</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLBLITZ MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-22-010R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1190-402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILICON VALLEY COMPUTER GROUP PHILS. INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>225 2/F CYBERZONE SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-16-04-0570 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1214-289</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511322</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-16-04-0569 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1213-189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S1.TECHNOLOGIES INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-24-470R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1212-990</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511324</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROIV-A-07520-26</x:t>
@@ -154,555 +634,6 @@
     <x:t>1511337</x:t>
   </x:si>
   <x:si>
-    <x:t>CZ 02 SM CITY SAN MATEO Ampid 1, General Luna, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06915-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1178-478</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 1511203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>X-DOT CONNECTION INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEVEL 3 UNIT 103, BATONG MALAKE, Los Baños, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROIV-A-06900-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1177-099</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dealer Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADI-ASIANIC DISTRIBUTORS INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#2072 2/F SM CITY SANTA ROSA, TAGAPO, City Of Santa Rosa, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0415</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1187-091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STALL 224 2/F SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1188-853</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ-018 3/F SM CITY LUCENA, IBABANG DUPAY, Lucena City (Capital), Quezon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0413</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1184-446</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STALL E-232 2/F SM CITY DASMARIÑAS, SAMPALOC I, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0406</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1183-545</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STALL 216 2/F SM CITY LIPA, MARAOUY, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0414</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1182-290</x:t>
-  </x:si>
-  <x:si>
-    <x:t>281 2ND FLOOR SM CITY CALAMBA, REAL, City Of Calamba, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1180-596</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIT 420 4/F SM CITY BACOOR, HABAY II, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0412</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1186-322</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ-207 2/F SM CITY MASINAG, MAYAMOT, City Of Antipolo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0407</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1181-124</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STALL 024 2/F SM CITY BATANGAS, PALLOCAN WEST, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-14-04-0408</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1185-901</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSD INTERNATIONAL MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cyberzone K-018 SM City San Pablo,, Brgy. San Rafael,, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-25-03-2429ML (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1150-325</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511233</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELLBLITZ MOBILE INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLA MALL PAGSANJAN GFK-005, PAGSANJAN, City Of Biñan, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-22-010R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1190-402</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELLBLITZ MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G/F ULTIMART BLDG., BRGY. III-A, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-22-003R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1098-751</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM CITY BATANGAS, PALLOCAN KANLURAN, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 23- 019R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1095-163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELLTY MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROBINSONS PLACE LIPA LEVEL 2, MATAAS NA LUPA, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-21-04-2282</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1191-381</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511320</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN PASCUAL, SAN ANTONIO, San Pascual, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-24-451R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1111-408</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511278</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTERMART SAN ANTONIO, SAN PASCUAL, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467-24R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1096-022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511193</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO BINANGONAN 2ND FLR. GAISANO CAPITAL MANILA EAST ROAD ST., CALUMPANG, Binangonan, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 467b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1164-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2ND FLR. WALTERMART DASMARIÑAS ZONE IV, ZONE IV, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-024R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1165-147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIGITAL WALKER CORP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIT R09 BLK J. THE OUTLETS, SAN LUCAS, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-466b-22R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1200-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511311</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLH GENTECH INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROBINSONS PLACE LIPA, MATAAS NA LUPA, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-17-11-0683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1109-317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511246</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ2114 SM City Lipa, MARAUOY, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-02-25-0453R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1092-444</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511299</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBILECRAZE TELECOM INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NO. 6 PUREGOLD BLDG. SAN PABLO COLAGO AVE, SAN ROQUE, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-01-25-451R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1113-757</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511248</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHONEVILLE MOBILE INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sm City Taytay Manila East Road Sm City Taytay Manila East Road, Dolores, Taytay, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19-03-0774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1202-217</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511271</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRISMATECH INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UG 227 ROBINSONS PLACE ANTIPOLO SUMULONG HIGHWAY, DELA PAZ, City Of Antipolo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">     DD-MP-02-25-0456R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1228-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RULLS CELLPHONES AND ACCESSORIES INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEVEL 3 03714 ROBINSONS PLACE DASMARIÑAS, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-018R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1094-777</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S1.TECHNOLOGIES INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ12 LGF CYBERZONE SM CITY TRECE MARTIRES, S.A PROPER, San Agustin, Trece Martires City (Capital), Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-24-470R (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1212-990</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511324</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILICON VALLEY COMPUTER GROUP PHILS. INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ 02 CYBERZONE SM CITY TRECE MARTIRES, BRGY. SAN AGUSTIN, Trece Martires City (Capital), Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-16-04-0570 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1214-289</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511322</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LS 010 G/F XENTRO MALL, CALACA HIGHWAY, BRGY. MALINIS, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-16-04-0569 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1213-189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYNCNETIC INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLA MALL PAGSANJAN NATIONAL ROAD, PAGSANJAN, City Of Biñan, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-24-468R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1161-717</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYNCNETIC INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SM CITY DASMARIÑAS UNIT 248 3RD FLR., SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-02-25-0452R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1168-173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511222</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIT NO. 248 3RD FLR SM CITY DASMARIÑAS, SAMPALOC I, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 02-25- 045R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1091-601</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511298</x:t>
-  </x:si>
-  <x:si>
-    <x:t>223 SM CENTER LEMERY, DISTRICT IV, Lemery, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 24-471R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1108-762</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TECHNOKID CELLPHONE CENTER INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unit 243 CZ SM City Molino, Brgy. Habay,, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-03-0775 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1192-904</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511231</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unit 15 Unit 15 CZ SM City Taytay, Dolores, Taytay, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19-03-0776</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1201-204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511270</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEQWARE PHONES AND ACCESSORIES INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LEVEL 3, 306A, BRGY. TEJERO, General Trias, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-05-0452-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1084-395</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511240</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retailer/Reseller Permit (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROBINSONS GALLERIA SOUTH LEVEL 4 401, NUEVA, City Of San Pedro, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-06685-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1167-519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>313 3RD FLR. ROBINSONS PLACE GENERAL TRIAS ANTERO SORIANO HI-WAY, TEJERO, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-06683-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1166-516</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511305</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRKD GADGETS AND ACCESSORIES STORE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1ST FLOOR UNICITY MALL KM. 30 NATIONAL HIGHWAY, NUEVA, City Of San Pedro, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-06698-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1169-102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1507967</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ricardo Natividad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUDIONET- AXIS TELECOMM INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#95 CZ 28 3RD, FLOOR SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-16-05-1938</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1162-745</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511226</x:t>
-  </x:si>
-  <x:si>
-    <x:t>I’ZELL MOBILE PHONES AND ACCESSORIES SHOP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>257-G SM City Molino Molino Rd, Molino IV, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-RR-3-25-451R</x:t>
   </x:si>
   <x:si>
@@ -712,27 +643,9 @@
     <x:t>1511150</x:t>
   </x:si>
   <x:si>
-    <x:t>#95 CZ13 SM CITY SAN MATEO GENERAL LUNA ST., AMPID I, San Mateo, Rizal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-17-02-2011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1163-392</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511277</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Service Center Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
     <x:t>CPH COMPUTER PARTS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
-    <x:t>Level 3 LS-K10 Robinson South Galleria KM 31 National Highway, Nueva, City Of San Pedro, Laguna</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-SC-24-452R</x:t>
   </x:si>
   <x:si>
@@ -742,36 +655,6 @@
     <x:t>1511151</x:t>
   </x:si>
   <x:si>
-    <x:t>GIZMOTECH CORPORATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2/f sm city batangas pastor village, pallocan west, Batangas City (Capital), Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DDSC22091049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1227-607</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511918</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Adora Mercado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>257-G SM City Molino Molino Road, Molino IV, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-24-451R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1194-347</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511219</x:t>
-  </x:si>
-  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -784,12 +667,78 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>DD-RR-23-002R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1110-411</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511393</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-23-009R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-2-2026-1088-572</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-05-0455-23R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1248-431</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XOCUS BELL TECH MERCHANDISING INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIT 19 L2 2F BIGBEN COMPLEX AYALA HIGHWAY, MATAAS NA LUPA, Lipa City, Batangas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-25-03-1096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1275-362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530678</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-SC-25-02-1095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1276-984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530679</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP- 06-25-0463R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1253-931</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511450</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-RR-15-06-C1887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-3-2026-1250-534</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511468</x:t>
+  </x:si>
+  <x:si>
     <x:t>CLIXTEC INC.</x:t>
   </x:si>
   <x:si>
-    <x:t>XENTROMALL MONTALBAN LS-107, MANGGAHAN, Rodriguez (Montalban), Rizal</x:t>
-  </x:si>
-  <x:si>
     <x:t>MPDP-ROIV-A-07943-26</x:t>
   </x:si>
   <x:si>
@@ -799,9 +748,6 @@
     <x:t>1511469</x:t>
   </x:si>
   <x:si>
-    <x:t>SM CITY STO. TOMAS, SAN BATOLOME, Santo Tomas, Batangas</x:t>
-  </x:si>
-  <x:si>
     <x:t>MPDP-ROIV-A-07945-26</x:t>
   </x:si>
   <x:si>
@@ -811,48 +757,78 @@
     <x:t>1511472</x:t>
   </x:si>
   <x:si>
-    <x:t>AYALA MALLS SERIN SILANG, JUNCTION EAST, Tagaytay City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-05-0455-23R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1248-431</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511443</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CYBERZONE UGF SM CITY DASMARIÑAS EK 207A, SAMPALOC 1, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-23-002R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1110-411</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511393</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIT 008 G/F WALTERMART BACOOR WALTERMART BACOOR BLVD., MAMBOG IV, Bacoor City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP- 06-25-0463R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1253-931</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511450</x:t>
+    <x:t>DD-MP-17-05-0645 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1273-206</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1511477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RKD GADGET SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>128 J RIZAL ST, POBLACION II, Silang, Cavite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIV-A-08866-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1293-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1530147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-468b-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1295-329</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNO KID CELLPHONE CENTER INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-472a-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1286-938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE DOTCOM CELL, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-19-05-0796 (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1287-504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DD-MP-471a-22R (REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43A-4-2026-1285-656</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1531179</x:t>
   </x:si>
   <x:si>
     <x:t>INTO GADGETS TOO INC.</x:t>
   </x:si>
   <x:si>
-    <x:t>E224 SM City Dasmariñas,, Brgy. Sampaloc 1,, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
     <x:t>MPDP-NCR-3110-19 (REN)</x:t>
   </x:si>
   <x:si>
@@ -862,42 +838,9 @@
     <x:t>1531180</x:t>
   </x:si>
   <x:si>
-    <x:t>ONE DOTCOM CELL INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2nd Flr. Cyberzone SM City Calamba, Real, City Of Calamba, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-468b-22R (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1295-329</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1531175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONE DOTCOM CELL, INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CZ-24 SM City Trece,, Brgy. Agustin,, Trece Martires City (Capital), Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-19-05-0796 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1287-504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1531178</x:t>
-  </x:si>
-  <x:si>
     <x:t>SANDZTEL MOBILE INC.</x:t>
   </x:si>
   <x:si>
-    <x:t>Lot #292 B2 SM City Calamba National Highway, Real, City Of Calamba, Laguna</x:t>
-  </x:si>
-  <x:si>
     <x:t>DD-MP-469b-22R (REN)</x:t>
   </x:si>
   <x:si>
@@ -905,111 +848,6 @@
   </x:si>
   <x:si>
     <x:t>1531181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>225 2/F CYBERZONE SM CITY SAN PABLO, SAN RAFAEL, San Pablo City, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-17-05-0645 (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1273-206</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511477</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GFA29 CENTRAL MALL, SALITRAN II, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-23-009R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-2-2026-1088-572</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511394</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TECHNO KID CELLPHONE CENTER INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CP220 SM City Dasmariñas, Brgy. Sampaloc 14114, City Of Dasmariñas, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-471a-22R (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1285-656</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1531179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C214 SM City Trece Martires,, Brgy. San Agustin, Trece Martires City (Capital), Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-MP-472a-22R (REN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1286-938</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1531176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RKD GADGET SHOP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>128 J RIZAL ST, POBLACION II, Silang, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRRP-ROIV-A-08866-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1293-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1530147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOTUS CENTRAL MALL 2/F NUEVO AVENUE, TANZANG LUMA I, Imus City, Cavite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-RR-15-06-C1887</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-3-2026-1250-534</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1511468</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XOCUS BELL TECH MERCHANDISING INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIT 19 L2 2F BIGBEN COMPLEX AYALA HIGHWAY, MATAAS NA LUPA, Lipa City, Batangas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-25-02-1095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1276-984</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1530679</x:t>
-  </x:si>
-  <x:si>
-    <x:t>unit 5 2nd floor, Adenson Bldg. 3 national highway, Parian, City Of Calamba, Laguna</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DD-SC-25-03-1096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43A-4-2026-1275-362</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1530678</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1913,10 +1751,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46105.2006856829</x:v>
+        <x:v>46084.3419451968</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46105.2007036921</x:v>
+        <x:v>46084.3419617014</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
@@ -1925,7 +1763,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46106.1315601157</x:v>
+        <x:v>46090.3480933681</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
@@ -1933,820 +1771,820 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46105.1989528125</x:v>
+        <x:v>46090.2418365857</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46105.1989710069</x:v>
+        <x:v>46090.2418534606</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46106.1359238194</x:v>
+        <x:v>46093.3049920255</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46105.191745625</x:v>
+        <x:v>46090.210999456</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46105.1917622685</x:v>
+        <x:v>46090.211015162</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46106.1259714815</x:v>
+        <x:v>46093.3080127546</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46100.3466235648</x:v>
+        <x:v>46092.9637875116</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46100.34664375</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46106.1287182292</x:v>
+        <x:v>46093.3109466551</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46090.2558238542</x:v>
+        <x:v>46084.3311976389</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46090.2558400116</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46097.2890797917</x:v>
+        <x:v>46093.3668852546</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46104.3254651157</x:v>
+        <x:v>46084.2189288542</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46104.325483287</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46107.2521065509</x:v>
+        <x:v>46093.3723926852</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46090.2418365857</x:v>
+        <x:v>46084.2250188542</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46090.2418534606</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46093.3049920255</x:v>
+        <x:v>46093.3804507639</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46090.210999456</x:v>
+        <x:v>46084.1579541898</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46090.211015162</x:v>
+        <x:v>46145</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46093.3080127546</x:v>
+        <x:v>46093.4169326042</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46090.379734213</x:v>
+        <x:v>46092.1012814815</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46107</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46105.224634919</x:v>
+        <x:v>46097.1408234491</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46090.3851441782</x:v>
+        <x:v>46083.2322339931</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46107</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46105.22531625</x:v>
+        <x:v>46097.1495293519</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46090.365904456</x:v>
+        <x:v>46069.3573124306</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46107</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46105.2229815046</x:v>
+        <x:v>46097.2426396643</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46090.3537036343</x:v>
+        <x:v>46069.3514850347</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46107</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46105.2225829398</x:v>
+        <x:v>46097.2437384259</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46090.3356997569</x:v>
+        <x:v>46069.3341180556</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46107</x:v>
+        <x:v>46094</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46105.2220323264</x:v>
+        <x:v>46097.244735544</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46090.3208883218</x:v>
+        <x:v>46084.1513040509</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46107</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46105.2211048843</x:v>
+        <x:v>46097.2494578472</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46090.3747280671</x:v>
+        <x:v>46073.1135088426</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46107</x:v>
+        <x:v>45751</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46105.2237759722</x:v>
+        <x:v>46097.2511403241</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46090.3276135532</x:v>
+        <x:v>46090.2558238542</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46107</x:v>
+        <x:v>46090.2558400116</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46105.2216826968</x:v>
+        <x:v>46097.2890797917</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46090.3705350231</x:v>
+        <x:v>46069.1217257292</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46107</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46105.2233433449</x:v>
+        <x:v>46097.3375062153</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>84</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46083.2322339931</x:v>
+        <x:v>46073.1251625463</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46112</x:v>
+        <x:v>45619</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>11280</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46097.1495293519</x:v>
+        <x:v>46099.1200232986</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46091.3241459028</x:v>
+        <x:v>46073.1541139005</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46090</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46106.2491112732</x:v>
+        <x:v>46099.1584012616</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46069.3768614236</x:v>
+        <x:v>46097.4214954398</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46070</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46105.312268125</x:v>
+        <x:v>46100.2966699421</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
-        <x:v>98</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46069.3514850347</x:v>
+        <x:v>46097.4788515162</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46094</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
-        <x:v>101</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46097.2437384259</x:v>
+        <x:v>46100.2987549074</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D29" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E29" s="14" t="s">
-        <x:v>103</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G29" s="14" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46091.3318239931</x:v>
+        <x:v>46084.1627466204</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>45768</x:v>
+        <x:v>46060</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
-        <x:v>7530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46106.2406020602</x:v>
+        <x:v>46100.392939537</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D30" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E30" s="14" t="s">
-        <x:v>107</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G30" s="14" t="s">
-        <x:v>109</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H30" s="16">
         <x:v>46073.1441202083</x:v>
@@ -2755,7 +2593,7 @@
         <x:v>46030</x:v>
       </x:c>
       <x:c r="J30" s="15" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K30" s="17" t="n">
         <x:v>3780</x:v>
@@ -2764,1116 +2602,1116 @@
         <x:v>46100.4005466667</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C31" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D31" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E31" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F31" s="14" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G31" s="14" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H31" s="16">
-        <x:v>46069.3573124306</x:v>
+        <x:v>46090.3208883218</x:v>
       </x:c>
       <x:c r="I31" s="16">
-        <x:v>46100</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J31" s="15" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K31" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L31" s="18">
-        <x:v>46097.2426396643</x:v>
+        <x:v>46105.2211048843</x:v>
       </x:c>
       <x:c r="M31" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D32" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E32" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F32" s="14" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G32" s="14" t="s">
-        <x:v>117</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H32" s="16">
-        <x:v>46084.2189288542</x:v>
+        <x:v>46090.3276135532</x:v>
       </x:c>
       <x:c r="I32" s="16">
-        <x:v>46133</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J32" s="15" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K32" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L32" s="18">
-        <x:v>46093.3723926852</x:v>
+        <x:v>46105.2216826968</x:v>
       </x:c>
       <x:c r="M32" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C33" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D33" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E33" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46090.3356997569</x:v>
+      </x:c>
+      <x:c r="I33" s="16">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
-        <x:v>46084.2250188542</x:v>
-      </x:c>
-      <x:c r="I33" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J33" s="15" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="K33" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L33" s="18">
-        <x:v>46093.3804507639</x:v>
+        <x:v>46105.2220323264</x:v>
       </x:c>
       <x:c r="M33" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="14" t="s">
-        <x:v>123</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D34" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E34" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="F34" s="14" t="s">
+      <x:c r="G34" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="H34" s="16">
-        <x:v>46097.0601290857</x:v>
+        <x:v>46090.3537036343</x:v>
       </x:c>
       <x:c r="I34" s="16">
-        <x:v>46109</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J34" s="15" t="s">
-        <x:v>127</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K34" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L34" s="18">
-        <x:v>46106.1139344792</x:v>
+        <x:v>46105.2225829398</x:v>
       </x:c>
       <x:c r="M34" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C35" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D35" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E35" s="14" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F35" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G35" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H35" s="16">
-        <x:v>46073.1251625463</x:v>
+        <x:v>46090.365904456</x:v>
       </x:c>
       <x:c r="I35" s="16">
-        <x:v>45619</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J35" s="15" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K35" s="17" t="n">
-        <x:v>11280</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L35" s="18">
-        <x:v>46099.1200232986</x:v>
+        <x:v>46105.2229815046</x:v>
       </x:c>
       <x:c r="M35" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="G36" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H36" s="16">
-        <x:v>46069.2988094792</x:v>
+        <x:v>46090.3705350231</x:v>
       </x:c>
       <x:c r="I36" s="16">
-        <x:v>46070</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J36" s="15" t="s">
-        <x:v>136</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K36" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L36" s="18">
-        <x:v>46105.2995247917</x:v>
+        <x:v>46105.2233433449</x:v>
       </x:c>
       <x:c r="M36" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D37" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E37" s="14" t="s">
-        <x:v>138</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F37" s="14" t="s">
-        <x:v>139</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G37" s="14" t="s">
-        <x:v>140</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H37" s="16">
-        <x:v>46073.1541139005</x:v>
+        <x:v>46090.3747280671</x:v>
       </x:c>
       <x:c r="I37" s="16">
-        <x:v>46030</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J37" s="15" t="s">
-        <x:v>141</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K37" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L37" s="18">
-        <x:v>46099.1584012616</x:v>
+        <x:v>46105.2237759722</x:v>
       </x:c>
       <x:c r="M37" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D38" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E38" s="14" t="s">
-        <x:v>143</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F38" s="14" t="s">
-        <x:v>144</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G38" s="14" t="s">
-        <x:v>145</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H38" s="16">
-        <x:v>46097.4788515162</x:v>
+        <x:v>46090.379734213</x:v>
       </x:c>
       <x:c r="I38" s="16">
-        <x:v>46100</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J38" s="15" t="s">
-        <x:v>146</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K38" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L38" s="18">
-        <x:v>46100.2987549074</x:v>
+        <x:v>46105.224634919</x:v>
       </x:c>
       <x:c r="M38" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="14" t="s">
-        <x:v>147</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D39" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E39" s="14" t="s">
-        <x:v>148</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F39" s="14" t="s">
-        <x:v>149</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G39" s="14" t="s">
-        <x:v>150</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H39" s="16">
-        <x:v>46105.2848483681</x:v>
+        <x:v>46090.3851441782</x:v>
       </x:c>
       <x:c r="I39" s="16">
-        <x:v>46105</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="J39" s="15" t="s">
-        <x:v>151</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K39" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L39" s="18">
-        <x:v>46105.3281210069</x:v>
+        <x:v>46105.22531625</x:v>
       </x:c>
       <x:c r="M39" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C40" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D40" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E40" s="14" t="s">
-        <x:v>153</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="14" t="s">
-        <x:v>154</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G40" s="14" t="s">
-        <x:v>155</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H40" s="16">
-        <x:v>46069.3341180556</x:v>
+        <x:v>46069.2869081713</x:v>
       </x:c>
       <x:c r="I40" s="16">
-        <x:v>46094</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J40" s="15" t="s">
-        <x:v>156</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K40" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L40" s="18">
-        <x:v>46097.244735544</x:v>
+        <x:v>46105.2599488542</x:v>
       </x:c>
       <x:c r="M40" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="14" t="s">
-        <x:v>157</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D41" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E41" s="14" t="s">
-        <x:v>158</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="14" t="s">
-        <x:v>159</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G41" s="14" t="s">
-        <x:v>160</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H41" s="16">
-        <x:v>46104.077202419</x:v>
+        <x:v>46069.2988094792</x:v>
       </x:c>
       <x:c r="I41" s="16">
-        <x:v>46106</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J41" s="15" t="s">
-        <x:v>161</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K41" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L41" s="18">
-        <x:v>46106.2743414352</x:v>
+        <x:v>46105.2995247917</x:v>
       </x:c>
       <x:c r="M41" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D42" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E42" s="14" t="s">
-        <x:v>163</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F42" s="14" t="s">
-        <x:v>164</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G42" s="14" t="s">
-        <x:v>165</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H42" s="16">
-        <x:v>46104.0901424306</x:v>
+        <x:v>46105.2817877199</x:v>
       </x:c>
       <x:c r="I42" s="16">
-        <x:v>46117</x:v>
+        <x:v>46634</x:v>
       </x:c>
       <x:c r="J42" s="15" t="s">
-        <x:v>166</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K42" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>8190</x:v>
       </x:c>
       <x:c r="L42" s="18">
-        <x:v>46106.2675132176</x:v>
+        <x:v>46105.3080007639</x:v>
       </x:c>
       <x:c r="M42" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
       <x:c r="B43" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D43" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E43" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="14" t="s">
-        <x:v>168</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G43" s="14" t="s">
-        <x:v>169</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H43" s="16">
-        <x:v>46104.0855029514</x:v>
+        <x:v>46069.3768614236</x:v>
       </x:c>
       <x:c r="I43" s="16">
-        <x:v>46117</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J43" s="15" t="s">
-        <x:v>170</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K43" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L43" s="18">
-        <x:v>46106.2705830787</x:v>
+        <x:v>46105.312268125</x:v>
       </x:c>
       <x:c r="M43" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
       <x:c r="B44" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D44" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E44" s="14" t="s">
-        <x:v>172</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="F44" s="14" t="s">
-        <x:v>173</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G44" s="14" t="s">
-        <x:v>174</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H44" s="16">
-        <x:v>46084.1513040509</x:v>
+        <x:v>46105.2848483681</x:v>
       </x:c>
       <x:c r="I44" s="16">
-        <x:v>46102</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="J44" s="15" t="s">
-        <x:v>175</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K44" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L44" s="18">
-        <x:v>46097.2494578472</x:v>
+        <x:v>46105.3281210069</x:v>
       </x:c>
       <x:c r="M44" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
       <x:c r="B45" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D45" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="14" t="s">
-        <x:v>177</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="14" t="s">
-        <x:v>178</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G45" s="14" t="s">
-        <x:v>179</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H45" s="16">
-        <x:v>46084.3311976389</x:v>
+        <x:v>46084.2548997222</x:v>
       </x:c>
       <x:c r="I45" s="16">
-        <x:v>46070</x:v>
+        <x:v>46084.2549156713</x:v>
       </x:c>
       <x:c r="J45" s="15" t="s">
-        <x:v>180</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K45" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L45" s="18">
-        <x:v>46093.3668852546</x:v>
+        <x:v>46105.4010316319</x:v>
       </x:c>
       <x:c r="M45" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
       <x:c r="B46" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C46" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D46" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="14" t="s">
-        <x:v>182</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G46" s="14" t="s">
-        <x:v>183</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H46" s="16">
-        <x:v>46069.2869081713</x:v>
+        <x:v>46084.2374126389</x:v>
       </x:c>
       <x:c r="I46" s="16">
-        <x:v>46070</x:v>
+        <x:v>46084.2374295139</x:v>
       </x:c>
       <x:c r="J46" s="15" t="s">
-        <x:v>184</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="K46" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L46" s="18">
-        <x:v>46105.2599488542</x:v>
+        <x:v>46105.4096900347</x:v>
       </x:c>
       <x:c r="M46" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="30" customHeight="1">
       <x:c r="B47" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C47" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D47" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E47" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F47" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G47" s="14" t="s">
-        <x:v>187</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H47" s="16">
-        <x:v>46073.1135088426</x:v>
+        <x:v>46097.0601290857</x:v>
       </x:c>
       <x:c r="I47" s="16">
-        <x:v>45751</x:v>
+        <x:v>46109</x:v>
       </x:c>
       <x:c r="J47" s="15" t="s">
-        <x:v>188</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K47" s="17" t="n">
-        <x:v>7530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L47" s="18">
-        <x:v>46097.2511403241</x:v>
+        <x:v>46106.1139344792</x:v>
       </x:c>
       <x:c r="M47" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
       <x:c r="B48" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C48" s="14" t="s">
-        <x:v>189</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D48" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E48" s="14" t="s">
-        <x:v>190</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F48" s="14" t="s">
-        <x:v>191</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G48" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H48" s="16">
-        <x:v>46092.1012814815</x:v>
+        <x:v>46105.191745625</x:v>
       </x:c>
       <x:c r="I48" s="16">
-        <x:v>46100</x:v>
+        <x:v>46105.1917622685</x:v>
       </x:c>
       <x:c r="J48" s="15" t="s">
-        <x:v>193</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K48" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L48" s="18">
-        <x:v>46097.1408234491</x:v>
+        <x:v>46106.1259714815</x:v>
       </x:c>
       <x:c r="M48" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="30" customHeight="1">
       <x:c r="B49" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C49" s="14" t="s">
-        <x:v>189</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D49" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E49" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F49" s="14" t="s">
-        <x:v>195</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G49" s="14" t="s">
-        <x:v>196</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H49" s="16">
-        <x:v>46097.4214954398</x:v>
+        <x:v>46100.3466235648</x:v>
       </x:c>
       <x:c r="I49" s="16">
-        <x:v>46100</x:v>
+        <x:v>46100.34664375</x:v>
       </x:c>
       <x:c r="J49" s="15" t="s">
-        <x:v>197</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K49" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L49" s="18">
-        <x:v>46100.2966699421</x:v>
+        <x:v>46106.1287182292</x:v>
       </x:c>
       <x:c r="M49" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
       <x:c r="B50" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C50" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D50" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E50" s="14" t="s">
-        <x:v>199</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F50" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G50" s="14" t="s">
-        <x:v>201</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H50" s="16">
-        <x:v>46069.1217257292</x:v>
+        <x:v>46105.2006856829</x:v>
       </x:c>
       <x:c r="I50" s="16">
-        <x:v>46157</x:v>
+        <x:v>46105.2007036921</x:v>
       </x:c>
       <x:c r="J50" s="15" t="s">
-        <x:v>202</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K50" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L50" s="18">
-        <x:v>46097.3375062153</x:v>
+        <x:v>46106.1315601157</x:v>
       </x:c>
       <x:c r="M50" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
       <x:c r="B51" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C51" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D51" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E51" s="14" t="s">
-        <x:v>204</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F51" s="14" t="s">
-        <x:v>205</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G51" s="14" t="s">
-        <x:v>206</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H51" s="16">
-        <x:v>46084.2548997222</x:v>
+        <x:v>46105.1989528125</x:v>
       </x:c>
       <x:c r="I51" s="16">
-        <x:v>46084.2549156713</x:v>
+        <x:v>46105.1989710069</x:v>
       </x:c>
       <x:c r="J51" s="15" t="s">
-        <x:v>207</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K51" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L51" s="18">
-        <x:v>46105.4010316319</x:v>
+        <x:v>46106.1359238194</x:v>
       </x:c>
       <x:c r="M51" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="30" customHeight="1">
       <x:c r="B52" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C52" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D52" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E52" s="14" t="s">
-        <x:v>208</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="14" t="s">
-        <x:v>209</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G52" s="14" t="s">
-        <x:v>210</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H52" s="16">
-        <x:v>46084.2374126389</x:v>
+        <x:v>46091.3318239931</x:v>
       </x:c>
       <x:c r="I52" s="16">
-        <x:v>46084.2374295139</x:v>
+        <x:v>45768</x:v>
       </x:c>
       <x:c r="J52" s="15" t="s">
-        <x:v>211</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="K52" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>7530</x:v>
       </x:c>
       <x:c r="L52" s="18">
-        <x:v>46105.4096900347</x:v>
+        <x:v>46106.2406020602</x:v>
       </x:c>
       <x:c r="M52" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
       <x:c r="B53" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C53" s="14" t="s">
-        <x:v>212</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D53" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E53" s="14" t="s">
-        <x:v>213</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="14" t="s">
-        <x:v>214</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G53" s="14" t="s">
-        <x:v>215</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H53" s="16">
-        <x:v>46084.3419451968</x:v>
+        <x:v>46091.3241459028</x:v>
       </x:c>
       <x:c r="I53" s="16">
-        <x:v>46084.3419617014</x:v>
+        <x:v>46090</x:v>
       </x:c>
       <x:c r="J53" s="15" t="s">
-        <x:v>216</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K53" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L53" s="18">
-        <x:v>46090.3480933681</x:v>
+        <x:v>46106.2491112732</x:v>
       </x:c>
       <x:c r="M53" s="14" t="s">
-        <x:v>217</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
       <x:c r="B54" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C54" s="14" t="s">
-        <x:v>219</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D54" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E54" s="14" t="s">
-        <x:v>220</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F54" s="14" t="s">
-        <x:v>221</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G54" s="14" t="s">
-        <x:v>222</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H54" s="16">
-        <x:v>46084.1579541898</x:v>
+        <x:v>46104.0901424306</x:v>
       </x:c>
       <x:c r="I54" s="16">
-        <x:v>46145</x:v>
+        <x:v>46117</x:v>
       </x:c>
       <x:c r="J54" s="15" t="s">
-        <x:v>223</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K54" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L54" s="18">
-        <x:v>46093.4169326042</x:v>
+        <x:v>46106.2675132176</x:v>
       </x:c>
       <x:c r="M54" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="30" customHeight="1">
       <x:c r="B55" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C55" s="14" t="s">
-        <x:v>224</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D55" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E55" s="14" t="s">
-        <x:v>225</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F55" s="14" t="s">
-        <x:v>226</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G55" s="14" t="s">
-        <x:v>227</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H55" s="16">
-        <x:v>46083.2228741435</x:v>
+        <x:v>46104.0855029514</x:v>
       </x:c>
       <x:c r="I55" s="16">
-        <x:v>46083</x:v>
+        <x:v>46117</x:v>
       </x:c>
       <x:c r="J55" s="15" t="s">
-        <x:v>228</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="K55" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L55" s="18">
-        <x:v>46111.2343215393</x:v>
+        <x:v>46106.2705830787</x:v>
       </x:c>
       <x:c r="M55" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="30" customHeight="1">
       <x:c r="B56" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C56" s="14" t="s">
-        <x:v>171</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D56" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E56" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F56" s="14" t="s">
-        <x:v>230</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G56" s="14" t="s">
-        <x:v>231</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H56" s="16">
-        <x:v>46084.1627466204</x:v>
+        <x:v>46104.077202419</x:v>
       </x:c>
       <x:c r="I56" s="16">
-        <x:v>46060</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="J56" s="15" t="s">
-        <x:v>232</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="K56" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L56" s="18">
-        <x:v>46100.392939537</x:v>
+        <x:v>46106.2743414352</x:v>
       </x:c>
       <x:c r="M56" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="30" customHeight="1">
       <x:c r="B57" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C57" s="14" t="s">
-        <x:v>234</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D57" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="14" t="s">
-        <x:v>235</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F57" s="14" t="s">
-        <x:v>236</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G57" s="14" t="s">
-        <x:v>237</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H57" s="16">
-        <x:v>46083.2276334028</x:v>
+        <x:v>46104.3254651157</x:v>
       </x:c>
       <x:c r="I57" s="16">
-        <x:v>46094</x:v>
+        <x:v>46104.325483287</x:v>
       </x:c>
       <x:c r="J57" s="15" t="s">
-        <x:v>238</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K57" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L57" s="18">
-        <x:v>46111.2358333681</x:v>
+        <x:v>46107.2521065509</x:v>
       </x:c>
       <x:c r="M57" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
       <x:c r="B58" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C58" s="14" t="s">
-        <x:v>239</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D58" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E58" s="14" t="s">
-        <x:v>240</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F58" s="14" t="s">
-        <x:v>241</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G58" s="14" t="s">
-        <x:v>242</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H58" s="16">
-        <x:v>46105.2817877199</x:v>
+        <x:v>46083.2228741435</x:v>
       </x:c>
       <x:c r="I58" s="16">
-        <x:v>46634</x:v>
+        <x:v>46083</x:v>
       </x:c>
       <x:c r="J58" s="15" t="s">
-        <x:v>243</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K58" s="17" t="n">
-        <x:v>8190</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L58" s="18">
-        <x:v>46105.3080007639</x:v>
+        <x:v>46111.2343215393</x:v>
       </x:c>
       <x:c r="M58" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
       <x:c r="B59" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C59" s="14" t="s">
-        <x:v>224</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D59" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E59" s="14" t="s">
-        <x:v>245</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F59" s="14" t="s">
-        <x:v>246</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G59" s="14" t="s">
-        <x:v>247</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H59" s="16">
-        <x:v>46092.9637875116</x:v>
+        <x:v>46083.2276334028</x:v>
       </x:c>
       <x:c r="I59" s="16">
         <x:v>46094</x:v>
       </x:c>
       <x:c r="J59" s="15" t="s">
-        <x:v>248</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="K59" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L59" s="18">
-        <x:v>46093.3109466551</x:v>
+        <x:v>46111.2358333681</x:v>
       </x:c>
       <x:c r="M59" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
       <x:c r="B62" s="19" t="s">
-        <x:v>249</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C62" s="20" t="s"/>
       <x:c r="D62" s="20" t="s"/>
@@ -3882,18 +3720,18 @@
     </x:row>
     <x:row r="63" spans="1:28" ht="22" customHeight="1">
       <x:c r="B63" s="22" t="s">
-        <x:v>250</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C63" s="23" t="s"/>
       <x:c r="D63" s="23" t="s"/>
       <x:c r="E63" s="23" t="s"/>
       <x:c r="F63" s="24" t="s">
-        <x:v>251</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:28" ht="18" customHeight="1">
       <x:c r="B64" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C64" s="26" t="s"/>
       <x:c r="D64" s="26" t="s"/>
@@ -3904,7 +3742,7 @@
     </x:row>
     <x:row r="65" spans="1:28" ht="18" customHeight="1">
       <x:c r="B65" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C65" s="26" t="s"/>
       <x:c r="D65" s="26" t="s"/>
@@ -3915,7 +3753,7 @@
     </x:row>
     <x:row r="66" spans="1:28" ht="18" customHeight="1">
       <x:c r="B66" s="25" t="s">
-        <x:v>203</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C66" s="26" t="s"/>
       <x:c r="D66" s="26" t="s"/>
@@ -3926,7 +3764,7 @@
     </x:row>
     <x:row r="67" spans="1:28" ht="18" customHeight="1">
       <x:c r="B67" s="25" t="s">
-        <x:v>218</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C67" s="26" t="s"/>
       <x:c r="D67" s="26" t="s"/>
@@ -3937,7 +3775,7 @@
     </x:row>
     <x:row r="68" spans="1:28" ht="18" customHeight="1">
       <x:c r="B68" s="25" t="s">
-        <x:v>233</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C68" s="26" t="s"/>
       <x:c r="D68" s="26" t="s"/>
@@ -3948,7 +3786,7 @@
     </x:row>
     <x:row r="69" spans="1:28" ht="28" customHeight="1">
       <x:c r="B69" s="28" t="s">
-        <x:v>252</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C69" s="29" t="s"/>
       <x:c r="D69" s="29" t="s"/>
@@ -5082,98 +4920,98 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>253</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>254</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>255</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>256</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46112.2780077662</x:v>
+        <x:v>46073.1304932986</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46112.2780258912</x:v>
+        <x:v>46034</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
-        <x:v>257</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46132.3858322685</x:v>
+        <x:v>46119.2877239352</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>258</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>259</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>260</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46112.2975525116</x:v>
+        <x:v>46069.272014213</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46112.2975902315</x:v>
+        <x:v>46067</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>261</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46133.115857338</x:v>
+        <x:v>46119.2995831134</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>262</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>263</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>264</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H10" s="16">
         <x:v>46112.3105175116</x:v>
@@ -5182,7 +5020,7 @@
         <x:v>46171</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>265</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
@@ -5191,255 +5029,255 @@
         <x:v>46128.1580781366</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>266</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>267</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>268</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46073.1304932986</x:v>
+        <x:v>46128.1990794213</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46034</x:v>
+        <x:v>46092</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>269</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46119.2877239352</x:v>
+        <x:v>46128.3062135532</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>270</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>271</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>272</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46112.337306331</x:v>
+        <x:v>46128.2227381019</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46177</x:v>
+        <x:v>46072</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>273</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.3625958333</x:v>
+        <x:v>46128.3098665394</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>274</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>275</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>276</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>277</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46134.4259644444</x:v>
+        <x:v>46112.337306331</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46179</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>278</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46141.2705907986</x:v>
+        <x:v>46128.3625958333</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>279</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>280</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>281</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46139.1392404861</x:v>
+        <x:v>46112.3204506829</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46136</x:v>
+        <x:v>46182</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>283</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46141.238019537</x:v>
+        <x:v>46132.3781534259</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>284</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>285</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>286</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>287</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46134.4505067245</x:v>
+        <x:v>46112.2780077662</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46156</x:v>
+        <x:v>46112.2780258912</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>288</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46141.2556749421</x:v>
+        <x:v>46132.3858322685</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>289</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>290</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>291</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>292</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46139.1324899537</x:v>
+        <x:v>46112.2975525116</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46136</x:v>
+        <x:v>46112.2975902315</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>293</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46141.3857011921</x:v>
+        <x:v>46133.115857338</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>162</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>294</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>295</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>296</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H17" s="16">
         <x:v>46127.1415970486</x:v>
@@ -5448,7 +5286,7 @@
         <x:v>46135</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>297</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
@@ -5457,42 +5295,42 @@
         <x:v>46133.2825861574</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>176</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>298</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>299</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46069.272014213</x:v>
+        <x:v>46135.740464213</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46067</x:v>
+        <x:v>46135.7404903472</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>301</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46119.2995831134</x:v>
+        <x:v>46139.3656545718</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
@@ -5500,60 +5338,60 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>302</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>303</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>304</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>305</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46134.4345563194</x:v>
+        <x:v>46139.1392404861</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46164</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>306</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46141.2618936806</x:v>
+        <x:v>46141.238019537</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>302</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>307</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>308</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>309</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="H20" s="16">
         <x:v>46134.4424908912</x:v>
@@ -5562,7 +5400,7 @@
         <x:v>46164</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>310</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
@@ -5571,166 +5409,166 @@
         <x:v>46141.2427502662</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>203</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>311</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>312</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>314</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46135.740464213</x:v>
+        <x:v>46134.4505067245</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46135.7404903472</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>315</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46139.3656545718</x:v>
+        <x:v>46141.2556749421</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
-        <x:v>217</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>218</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>316</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>317</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>318</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46112.3204506829</x:v>
+        <x:v>46134.4345563194</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46182</x:v>
+        <x:v>46164</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>319</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46132.3781534259</x:v>
+        <x:v>46141.2618936806</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>321</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>322</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>323</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46128.2227381019</x:v>
+        <x:v>46134.4259644444</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46072</x:v>
+        <x:v>46179</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>324</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46128.3098665394</x:v>
+        <x:v>46141.2705907986</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>233</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>325</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>326</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>327</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46128.1990794213</x:v>
+        <x:v>46139.1324899537</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46092</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>328</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
-        <x:v>2550</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46128.3062135532</x:v>
+        <x:v>46141.3857011921</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>244</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="19" t="s">
-        <x:v>249</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C27" s="20" t="s"/>
       <x:c r="D27" s="20" t="s"/>
@@ -5739,18 +5577,18 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="22" customHeight="1">
       <x:c r="B28" s="22" t="s">
-        <x:v>250</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C28" s="23" t="s"/>
       <x:c r="D28" s="23" t="s"/>
       <x:c r="E28" s="23" t="s"/>
       <x:c r="F28" s="24" t="s">
-        <x:v>251</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C29" s="26" t="s"/>
       <x:c r="D29" s="26" t="s"/>
@@ -5761,7 +5599,7 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
@@ -5772,7 +5610,7 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="25" t="s">
-        <x:v>203</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="26" t="s"/>
       <x:c r="D31" s="26" t="s"/>
@@ -5783,7 +5621,7 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="25" t="s">
-        <x:v>218</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C32" s="26" t="s"/>
       <x:c r="D32" s="26" t="s"/>
@@ -5794,7 +5632,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="25" t="s">
-        <x:v>233</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C33" s="26" t="s"/>
       <x:c r="D33" s="26" t="s"/>
@@ -5805,7 +5643,7 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="28" customHeight="1">
       <x:c r="B34" s="28" t="s">
-        <x:v>252</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C34" s="29" t="s"/>
       <x:c r="D34" s="29" t="s"/>
